--- a/my_results/Pre-Amp Calculator.xlsx
+++ b/my_results/Pre-Amp Calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\User Files\Documents\GitHub\autoeq-workspace\my_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C5BA9-C525-468E-BCDF-5EAE9EA5D50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A49A1DD-5FE3-4428-9C10-7BDCC38E4D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="912" windowWidth="17244" windowHeight="12048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="5352" windowWidth="17244" windowHeight="12048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Impulse" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>f \ equalisation</t>
   </si>
   <si>
-    <t>jm1 levels</t>
-  </si>
-  <si>
     <t>manual attenuation</t>
   </si>
   <si>
@@ -89,6 +86,9 @@
   </si>
   <si>
     <t>harman_over-ear_2018_wo_bass</t>
+  </si>
+  <si>
+    <t>jm1_8db_4db_adjusted</t>
   </si>
 </sst>
 </file>
@@ -454,13 +454,13 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -475,7 +475,7 @@
         <v>4</v>
       </c>
       <c r="K1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L1" t="s">
         <v>12</v>
@@ -492,7 +492,7 @@
         <v>-3.8</v>
       </c>
       <c r="D2">
-        <v>-1.87</v>
+        <v>4.55</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
@@ -532,7 +532,7 @@
         <v>-3.74</v>
       </c>
       <c r="D3">
-        <v>-1.89</v>
+        <v>4.55</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
@@ -572,33 +572,33 @@
         <v>-3.67</v>
       </c>
       <c r="D4">
-        <v>-1.91</v>
+        <v>4.55</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4">
         <f>SUM(D2:D696)</f>
-        <v>-618.24999999999943</v>
+        <v>906.90000000000123</v>
       </c>
       <c r="H4">
         <f>AVERAGE(D2:D696)</f>
-        <v>-0.88956834532374018</v>
+        <v>1.304892086330937</v>
       </c>
       <c r="I4">
         <f>MIN($D$2:$D$696)</f>
-        <v>-5.78</v>
+        <v>-11.26</v>
       </c>
       <c r="J4">
         <f>MAX($D$2:$D$696)</f>
-        <v>5.46</v>
+        <v>9.89</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
       </c>
       <c r="L4">
         <f>J4-K4-H4</f>
-        <v>6.3495683453237399</v>
+        <v>8.5851079136690629</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -612,7 +612,7 @@
         <v>-3.61</v>
       </c>
       <c r="D5">
-        <v>-1.93</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>-3.54</v>
       </c>
       <c r="D6">
-        <v>-1.95</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -640,7 +640,7 @@
         <v>-3.47</v>
       </c>
       <c r="D7">
-        <v>-1.97</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -654,7 +654,7 @@
         <v>-3.4</v>
       </c>
       <c r="D8">
-        <v>-1.99</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -668,7 +668,7 @@
         <v>-3.34</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>-3.27</v>
       </c>
       <c r="D10">
-        <v>-2.02</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -696,7 +696,7 @@
         <v>-3.21</v>
       </c>
       <c r="D11">
-        <v>-2.04</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -710,7 +710,7 @@
         <v>-3.14</v>
       </c>
       <c r="D12">
-        <v>-2.06</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -724,7 +724,7 @@
         <v>-3.08</v>
       </c>
       <c r="D13">
-        <v>-2.0699999999999998</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -738,7 +738,7 @@
         <v>-3.01</v>
       </c>
       <c r="D14">
-        <v>-2.09</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -752,7 +752,7 @@
         <v>-2.95</v>
       </c>
       <c r="D15">
-        <v>-2.11</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -766,7 +766,7 @@
         <v>-2.88</v>
       </c>
       <c r="D16">
-        <v>-2.13</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
         <v>-2.82</v>
       </c>
       <c r="D17">
-        <v>-2.15</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -794,7 +794,7 @@
         <v>-2.76</v>
       </c>
       <c r="D18">
-        <v>-2.16</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -808,7 +808,7 @@
         <v>-2.69</v>
       </c>
       <c r="D19">
-        <v>-2.1800000000000002</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>-2.63</v>
       </c>
       <c r="D20">
-        <v>-2.2000000000000002</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -836,7 +836,7 @@
         <v>-2.57</v>
       </c>
       <c r="D21">
-        <v>-2.21</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -850,7 +850,7 @@
         <v>-2.5099999999999998</v>
       </c>
       <c r="D22">
-        <v>-2.23</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -864,7 +864,7 @@
         <v>-2.4500000000000002</v>
       </c>
       <c r="D23">
-        <v>-2.2400000000000002</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -878,7 +878,7 @@
         <v>-2.39</v>
       </c>
       <c r="D24">
-        <v>-2.2599999999999998</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -892,7 +892,7 @@
         <v>-2.3199999999999998</v>
       </c>
       <c r="D25">
-        <v>-2.2799999999999998</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>-2.2599999999999998</v>
       </c>
       <c r="D26">
-        <v>-2.29</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -920,7 +920,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="D27">
-        <v>-2.31</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -934,7 +934,7 @@
         <v>-2.13</v>
       </c>
       <c r="D28">
-        <v>-2.33</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -948,7 +948,7 @@
         <v>-2.0699999999999998</v>
       </c>
       <c r="D29">
-        <v>-2.34</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -962,7 +962,7 @@
         <v>-2</v>
       </c>
       <c r="D30">
-        <v>-2.36</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -976,7 +976,7 @@
         <v>-1.92</v>
       </c>
       <c r="D31">
-        <v>-2.37</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -990,7 +990,7 @@
         <v>-1.85</v>
       </c>
       <c r="D32">
-        <v>-2.39</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1004,7 +1004,7 @@
         <v>-1.78</v>
       </c>
       <c r="D33">
-        <v>-2.4</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1018,7 +1018,7 @@
         <v>-1.71</v>
       </c>
       <c r="D34">
-        <v>-2.41</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1032,7 +1032,7 @@
         <v>-1.63</v>
       </c>
       <c r="D35">
-        <v>-2.4300000000000002</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>-1.56</v>
       </c>
       <c r="D36">
-        <v>-2.44</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1060,7 +1060,7 @@
         <v>-1.48</v>
       </c>
       <c r="D37">
-        <v>-2.4500000000000002</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1074,7 +1074,7 @@
         <v>-1.39</v>
       </c>
       <c r="D38">
-        <v>-2.4700000000000002</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>-1.31</v>
       </c>
       <c r="D39">
-        <v>-2.48</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1102,7 +1102,7 @@
         <v>-1.21</v>
       </c>
       <c r="D40">
-        <v>-2.5</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1116,7 +1116,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="D41">
-        <v>-2.5099999999999998</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1130,7 +1130,7 @@
         <v>-1.02</v>
       </c>
       <c r="D42">
-        <v>-2.5299999999999998</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1144,7 +1144,7 @@
         <v>-0.93</v>
       </c>
       <c r="D43">
-        <v>-2.54</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1158,7 +1158,7 @@
         <v>-0.85</v>
       </c>
       <c r="D44">
-        <v>-2.5499999999999998</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1172,7 +1172,7 @@
         <v>-0.78</v>
       </c>
       <c r="D45">
-        <v>-2.56</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1186,7 +1186,7 @@
         <v>-0.73</v>
       </c>
       <c r="D46">
-        <v>-2.57</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1200,7 +1200,7 @@
         <v>-0.69</v>
       </c>
       <c r="D47">
-        <v>-2.58</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1214,7 +1214,7 @@
         <v>-0.66</v>
       </c>
       <c r="D48">
-        <v>-2.59</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1228,7 +1228,7 @@
         <v>-0.65</v>
       </c>
       <c r="D49">
-        <v>-2.6</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1242,7 +1242,7 @@
         <v>-0.65</v>
       </c>
       <c r="D50">
-        <v>-2.61</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1256,7 +1256,7 @@
         <v>-0.66</v>
       </c>
       <c r="D51">
-        <v>-2.62</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1270,7 +1270,7 @@
         <v>-0.67</v>
       </c>
       <c r="D52">
-        <v>-2.64</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1284,7 +1284,7 @@
         <v>-0.68</v>
       </c>
       <c r="D53">
-        <v>-2.65</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1298,7 +1298,7 @@
         <v>-0.69</v>
       </c>
       <c r="D54">
-        <v>-2.67</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1312,7 +1312,7 @@
         <v>-0.7</v>
       </c>
       <c r="D55">
-        <v>-2.69</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1326,7 +1326,7 @@
         <v>-0.7</v>
       </c>
       <c r="D56">
-        <v>-2.7</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1340,7 +1340,7 @@
         <v>-0.71</v>
       </c>
       <c r="D57">
-        <v>-2.72</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1354,7 +1354,7 @@
         <v>-0.72</v>
       </c>
       <c r="D58">
-        <v>-2.73</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1368,7 +1368,7 @@
         <v>-0.72</v>
       </c>
       <c r="D59">
-        <v>-2.74</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1382,7 +1382,7 @@
         <v>-0.72</v>
       </c>
       <c r="D60">
-        <v>-2.75</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1396,7 +1396,7 @@
         <v>-0.73</v>
       </c>
       <c r="D61">
-        <v>-2.76</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1410,7 +1410,7 @@
         <v>-0.74</v>
       </c>
       <c r="D62">
-        <v>-2.77</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1424,7 +1424,7 @@
         <v>-0.75</v>
       </c>
       <c r="D63">
-        <v>-2.78</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1438,7 +1438,7 @@
         <v>-0.75</v>
       </c>
       <c r="D64">
-        <v>-2.78</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>-0.76</v>
       </c>
       <c r="D65">
-        <v>-2.79</v>
+        <v>4.5199999999999996</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1466,7 +1466,7 @@
         <v>-0.77</v>
       </c>
       <c r="D66">
-        <v>-2.79</v>
+        <v>4.5199999999999996</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1480,7 +1480,7 @@
         <v>-0.77</v>
       </c>
       <c r="D67">
-        <v>-2.8</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1494,7 +1494,7 @@
         <v>-0.78</v>
       </c>
       <c r="D68">
-        <v>-2.8</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1508,7 +1508,7 @@
         <v>-0.79</v>
       </c>
       <c r="D69">
-        <v>-2.8</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1522,7 +1522,7 @@
         <v>-0.79</v>
       </c>
       <c r="D70">
-        <v>-2.81</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1536,7 +1536,7 @@
         <v>-0.8</v>
       </c>
       <c r="D71">
-        <v>-2.81</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1550,7 +1550,7 @@
         <v>-0.81</v>
       </c>
       <c r="D72">
-        <v>-2.82</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1564,7 +1564,7 @@
         <v>-0.82</v>
       </c>
       <c r="D73">
-        <v>-2.82</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1578,7 +1578,7 @@
         <v>-0.82</v>
       </c>
       <c r="D74">
-        <v>-2.83</v>
+        <v>4.4800000000000004</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1592,7 +1592,7 @@
         <v>-0.82</v>
       </c>
       <c r="D75">
-        <v>-2.84</v>
+        <v>4.4800000000000004</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1606,7 +1606,7 @@
         <v>-0.82</v>
       </c>
       <c r="D76">
-        <v>-2.85</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1620,7 +1620,7 @@
         <v>-0.83</v>
       </c>
       <c r="D77">
-        <v>-2.85</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1634,7 +1634,7 @@
         <v>-0.84</v>
       </c>
       <c r="D78">
-        <v>-2.86</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1648,7 +1648,7 @@
         <v>-0.85</v>
       </c>
       <c r="D79">
-        <v>-2.87</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
         <v>-0.86</v>
       </c>
       <c r="D80">
-        <v>-2.88</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -1676,7 +1676,7 @@
         <v>-0.86</v>
       </c>
       <c r="D81">
-        <v>-2.89</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -1690,7 +1690,7 @@
         <v>-0.87</v>
       </c>
       <c r="D82">
-        <v>-2.9</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -1704,7 +1704,7 @@
         <v>-0.88</v>
       </c>
       <c r="D83">
-        <v>-2.91</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -1718,7 +1718,7 @@
         <v>-0.89</v>
       </c>
       <c r="D84">
-        <v>-2.92</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -1732,7 +1732,7 @@
         <v>-0.9</v>
       </c>
       <c r="D85">
-        <v>-2.92</v>
+        <v>4.3899999999999997</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -1746,7 +1746,7 @@
         <v>-0.91</v>
       </c>
       <c r="D86">
-        <v>-2.93</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1760,7 +1760,7 @@
         <v>-0.92</v>
       </c>
       <c r="D87">
-        <v>-2.94</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -1774,7 +1774,7 @@
         <v>-0.93</v>
       </c>
       <c r="D88">
-        <v>-2.95</v>
+        <v>4.3600000000000003</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -1788,7 +1788,7 @@
         <v>-0.94</v>
       </c>
       <c r="D89">
-        <v>-2.96</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -1802,7 +1802,7 @@
         <v>-0.95</v>
       </c>
       <c r="D90">
-        <v>-2.97</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -1816,7 +1816,7 @@
         <v>-0.96</v>
       </c>
       <c r="D91">
-        <v>-2.97</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -1830,7 +1830,7 @@
         <v>-0.97</v>
       </c>
       <c r="D92">
-        <v>-2.98</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -1844,7 +1844,7 @@
         <v>-0.99</v>
       </c>
       <c r="D93">
-        <v>-2.98</v>
+        <v>4.3099999999999996</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -1858,7 +1858,7 @@
         <v>-1</v>
       </c>
       <c r="D94">
-        <v>-2.98</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -1872,7 +1872,7 @@
         <v>-1.02</v>
       </c>
       <c r="D95">
-        <v>-2.98</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -1886,7 +1886,7 @@
         <v>-1.03</v>
       </c>
       <c r="D96">
-        <v>-2.98</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -1900,7 +1900,7 @@
         <v>-1.04</v>
       </c>
       <c r="D97">
-        <v>-2.98</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -1914,7 +1914,7 @@
         <v>-1.05</v>
       </c>
       <c r="D98">
-        <v>-2.99</v>
+        <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -1928,7 +1928,7 @@
         <v>-1.06</v>
       </c>
       <c r="D99">
-        <v>-2.99</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -1942,7 +1942,7 @@
         <v>-1.07</v>
       </c>
       <c r="D100">
-        <v>-3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -1956,7 +1956,7 @@
         <v>-1.08</v>
       </c>
       <c r="D101">
-        <v>-3.01</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -1970,7 +1970,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="D102">
-        <v>-3.02</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -1984,7 +1984,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="D103">
-        <v>-3.04</v>
+        <v>4.1500000000000004</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -1998,7 +1998,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="D104">
-        <v>-3.05</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -2012,7 +2012,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="D105">
-        <v>-3.07</v>
+        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -2026,7 +2026,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="D106">
-        <v>-3.09</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -2040,7 +2040,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="D107">
-        <v>-3.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -2054,7 +2054,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="D108">
-        <v>-3.12</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -2068,7 +2068,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="D109">
-        <v>-3.13</v>
+        <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -2082,7 +2082,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="D110">
-        <v>-3.14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -2096,7 +2096,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="D111">
-        <v>-3.15</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -2110,7 +2110,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="D112">
-        <v>-3.16</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2124,7 +2124,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="D113">
-        <v>-3.17</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2138,7 +2138,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="D114">
-        <v>-3.18</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2152,7 +2152,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="D115">
-        <v>-3.19</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2166,7 +2166,7 @@
         <v>-1.17</v>
       </c>
       <c r="D116">
-        <v>-3.21</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2180,7 +2180,7 @@
         <v>-1.18</v>
       </c>
       <c r="D117">
-        <v>-3.22</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2194,7 +2194,7 @@
         <v>-1.18</v>
       </c>
       <c r="D118">
-        <v>-3.24</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2208,7 +2208,7 @@
         <v>-1.18</v>
       </c>
       <c r="D119">
-        <v>-3.26</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2222,7 +2222,7 @@
         <v>-1.19</v>
       </c>
       <c r="D120">
-        <v>-3.28</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2236,7 +2236,7 @@
         <v>-1.19</v>
       </c>
       <c r="D121">
-        <v>-3.3</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2250,7 +2250,7 @@
         <v>-1.19</v>
       </c>
       <c r="D122">
-        <v>-3.32</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2264,7 +2264,7 @@
         <v>-1.19</v>
       </c>
       <c r="D123">
-        <v>-3.34</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2278,7 +2278,7 @@
         <v>-1.19</v>
       </c>
       <c r="D124">
-        <v>-3.37</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2292,7 +2292,7 @@
         <v>-1.18</v>
       </c>
       <c r="D125">
-        <v>-3.39</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2306,7 +2306,7 @@
         <v>-1.18</v>
       </c>
       <c r="D126">
-        <v>-3.42</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2320,7 +2320,7 @@
         <v>-1.19</v>
       </c>
       <c r="D127">
-        <v>-3.45</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -2334,7 +2334,7 @@
         <v>-1.19</v>
       </c>
       <c r="D128">
-        <v>-3.48</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -2348,7 +2348,7 @@
         <v>-1.18</v>
       </c>
       <c r="D129">
-        <v>-3.51</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>-1.18</v>
       </c>
       <c r="D130">
-        <v>-3.54</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -2376,7 +2376,7 @@
         <v>-1.18</v>
       </c>
       <c r="D131">
-        <v>-3.57</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -2390,7 +2390,7 @@
         <v>-1.17</v>
       </c>
       <c r="D132">
-        <v>-3.6</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -2404,7 +2404,7 @@
         <v>-1.17</v>
       </c>
       <c r="D133">
-        <v>-3.63</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -2418,7 +2418,7 @@
         <v>-1.17</v>
       </c>
       <c r="D134">
-        <v>-3.66</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -2432,7 +2432,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="D135">
-        <v>-3.69</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -2446,7 +2446,7 @@
         <v>-1.1599999999999999</v>
       </c>
       <c r="D136">
-        <v>-3.72</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -2460,7 +2460,7 @@
         <v>-1.1499999999999999</v>
       </c>
       <c r="D137">
-        <v>-3.76</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -2474,7 +2474,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="D138">
-        <v>-3.79</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -2488,7 +2488,7 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="D139">
-        <v>-3.83</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2502,7 +2502,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="D140">
-        <v>-3.86</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2516,7 +2516,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="D141">
-        <v>-3.9</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2530,7 +2530,7 @@
         <v>-1.0900000000000001</v>
       </c>
       <c r="D142">
-        <v>-3.93</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2544,7 +2544,7 @@
         <v>-1.08</v>
       </c>
       <c r="D143">
-        <v>-3.97</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2558,7 +2558,7 @@
         <v>-1.08</v>
       </c>
       <c r="D144">
-        <v>-4</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -2572,7 +2572,7 @@
         <v>-1.07</v>
       </c>
       <c r="D145">
-        <v>-4.04</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2586,7 +2586,7 @@
         <v>-1.06</v>
       </c>
       <c r="D146">
-        <v>-4.08</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -2600,7 +2600,7 @@
         <v>-1.04</v>
       </c>
       <c r="D147">
-        <v>-4.1100000000000003</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -2614,7 +2614,7 @@
         <v>-1.02</v>
       </c>
       <c r="D148">
-        <v>-4.1500000000000004</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -2628,7 +2628,7 @@
         <v>-1.01</v>
       </c>
       <c r="D149">
-        <v>-4.18</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -2642,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="D150">
-        <v>-4.21</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -2656,7 +2656,7 @@
         <v>-1</v>
       </c>
       <c r="D151">
-        <v>-4.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -2670,7 +2670,7 @@
         <v>-0.99</v>
       </c>
       <c r="D152">
-        <v>-4.28</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -2684,7 +2684,7 @@
         <v>-0.97</v>
       </c>
       <c r="D153">
-        <v>-4.32</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -2698,7 +2698,7 @@
         <v>-0.96</v>
       </c>
       <c r="D154">
-        <v>-4.3499999999999996</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -2712,7 +2712,7 @@
         <v>-0.95</v>
       </c>
       <c r="D155">
-        <v>-4.3899999999999997</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -2726,7 +2726,7 @@
         <v>-0.94</v>
       </c>
       <c r="D156">
-        <v>-4.43</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -2740,7 +2740,7 @@
         <v>-0.93</v>
       </c>
       <c r="D157">
-        <v>-4.47</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -2754,7 +2754,7 @@
         <v>-0.92</v>
       </c>
       <c r="D158">
-        <v>-4.5</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -2768,7 +2768,7 @@
         <v>-0.91</v>
       </c>
       <c r="D159">
-        <v>-4.54</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -2782,7 +2782,7 @@
         <v>-0.9</v>
       </c>
       <c r="D160">
-        <v>-4.58</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -2796,7 +2796,7 @@
         <v>-0.9</v>
       </c>
       <c r="D161">
-        <v>-4.6100000000000003</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -2810,7 +2810,7 @@
         <v>-0.88</v>
       </c>
       <c r="D162">
-        <v>-4.6500000000000004</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -2824,7 +2824,7 @@
         <v>-0.87</v>
       </c>
       <c r="D163">
-        <v>-4.6900000000000004</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -2838,7 +2838,7 @@
         <v>-0.87</v>
       </c>
       <c r="D164">
-        <v>-4.72</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -2852,7 +2852,7 @@
         <v>-0.86</v>
       </c>
       <c r="D165">
-        <v>-4.76</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -2866,7 +2866,7 @@
         <v>-0.85</v>
       </c>
       <c r="D166">
-        <v>-4.8</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -2880,7 +2880,7 @@
         <v>-0.84</v>
       </c>
       <c r="D167">
-        <v>-4.84</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -2894,7 +2894,7 @@
         <v>-0.83</v>
       </c>
       <c r="D168">
-        <v>-4.88</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -2908,7 +2908,7 @@
         <v>-0.82</v>
       </c>
       <c r="D169">
-        <v>-4.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -2922,7 +2922,7 @@
         <v>-0.81</v>
       </c>
       <c r="D170">
-        <v>-4.96</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -2936,7 +2936,7 @@
         <v>-0.8</v>
       </c>
       <c r="D171">
-        <v>-5</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -2950,7 +2950,7 @@
         <v>-0.79</v>
       </c>
       <c r="D172">
-        <v>-5.04</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -2964,7 +2964,7 @@
         <v>-0.78</v>
       </c>
       <c r="D173">
-        <v>-5.07</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -2978,7 +2978,7 @@
         <v>-0.78</v>
       </c>
       <c r="D174">
-        <v>-5.1100000000000003</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -2992,7 +2992,7 @@
         <v>-0.78</v>
       </c>
       <c r="D175">
-        <v>-5.15</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -3006,7 +3006,7 @@
         <v>-0.77</v>
       </c>
       <c r="D176">
-        <v>-5.18</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -3020,7 +3020,7 @@
         <v>-0.77</v>
       </c>
       <c r="D177">
-        <v>-5.21</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -3034,7 +3034,7 @@
         <v>-0.77</v>
       </c>
       <c r="D178">
-        <v>-5.25</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -3048,7 +3048,7 @@
         <v>-0.77</v>
       </c>
       <c r="D179">
-        <v>-5.28</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -3062,7 +3062,7 @@
         <v>-0.76</v>
       </c>
       <c r="D180">
-        <v>-5.32</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -3076,7 +3076,7 @@
         <v>-0.76</v>
       </c>
       <c r="D181">
-        <v>-5.35</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -3090,7 +3090,7 @@
         <v>-0.76</v>
       </c>
       <c r="D182">
-        <v>-5.38</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -3104,7 +3104,7 @@
         <v>-0.76</v>
       </c>
       <c r="D183">
-        <v>-5.41</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -3118,7 +3118,7 @@
         <v>-0.75</v>
       </c>
       <c r="D184">
-        <v>-5.44</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -3132,7 +3132,7 @@
         <v>-0.75</v>
       </c>
       <c r="D185">
-        <v>-5.46</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -3146,7 +3146,7 @@
         <v>-0.75</v>
       </c>
       <c r="D186">
-        <v>-5.49</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -3160,7 +3160,7 @@
         <v>-0.75</v>
       </c>
       <c r="D187">
-        <v>-5.51</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -3174,7 +3174,7 @@
         <v>-0.75</v>
       </c>
       <c r="D188">
-        <v>-5.54</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -3188,7 +3188,7 @@
         <v>-0.75</v>
       </c>
       <c r="D189">
-        <v>-5.56</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -3202,7 +3202,7 @@
         <v>-0.75</v>
       </c>
       <c r="D190">
-        <v>-5.58</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -3216,7 +3216,7 @@
         <v>-0.75</v>
       </c>
       <c r="D191">
-        <v>-5.61</v>
+        <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -3230,7 +3230,7 @@
         <v>-0.75</v>
       </c>
       <c r="D192">
-        <v>-5.63</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -3244,7 +3244,7 @@
         <v>-0.75</v>
       </c>
       <c r="D193">
-        <v>-5.65</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -3258,7 +3258,7 @@
         <v>-0.76</v>
       </c>
       <c r="D194">
-        <v>-5.67</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -3272,7 +3272,7 @@
         <v>-0.75</v>
       </c>
       <c r="D195">
-        <v>-5.68</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -3286,7 +3286,7 @@
         <v>-0.75</v>
       </c>
       <c r="D196">
-        <v>-5.7</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -3300,7 +3300,7 @@
         <v>-0.75</v>
       </c>
       <c r="D197">
-        <v>-5.71</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -3314,7 +3314,7 @@
         <v>-0.75</v>
       </c>
       <c r="D198">
-        <v>-5.73</v>
+        <v>-0.94</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -3328,7 +3328,7 @@
         <v>-0.74</v>
       </c>
       <c r="D199">
-        <v>-5.74</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -3342,7 +3342,7 @@
         <v>-0.74</v>
       </c>
       <c r="D200">
-        <v>-5.75</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -3356,7 +3356,7 @@
         <v>-0.74</v>
       </c>
       <c r="D201">
-        <v>-5.75</v>
+        <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -3370,7 +3370,7 @@
         <v>-0.73</v>
       </c>
       <c r="D202">
-        <v>-5.76</v>
+        <v>-1.1499999999999999</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -3384,7 +3384,7 @@
         <v>-0.73</v>
       </c>
       <c r="D203">
-        <v>-5.77</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -3398,7 +3398,7 @@
         <v>-0.73</v>
       </c>
       <c r="D204">
-        <v>-5.77</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -3412,7 +3412,7 @@
         <v>-0.73</v>
       </c>
       <c r="D205">
-        <v>-5.78</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -3426,7 +3426,7 @@
         <v>-0.74</v>
       </c>
       <c r="D206">
-        <v>-5.78</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -3440,7 +3440,7 @@
         <v>-0.74</v>
       </c>
       <c r="D207">
-        <v>-5.78</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -3454,7 +3454,7 @@
         <v>-0.74</v>
       </c>
       <c r="D208">
-        <v>-5.78</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -3468,7 +3468,7 @@
         <v>-0.75</v>
       </c>
       <c r="D209">
-        <v>-5.77</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -3482,7 +3482,7 @@
         <v>-0.76</v>
       </c>
       <c r="D210">
-        <v>-5.76</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -3496,7 +3496,7 @@
         <v>-0.76</v>
       </c>
       <c r="D211">
-        <v>-5.76</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -3510,7 +3510,7 @@
         <v>-0.78</v>
       </c>
       <c r="D212">
-        <v>-5.75</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -3524,7 +3524,7 @@
         <v>-0.78</v>
       </c>
       <c r="D213">
-        <v>-5.74</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -3538,7 +3538,7 @@
         <v>-0.79</v>
       </c>
       <c r="D214">
-        <v>-5.72</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -3552,7 +3552,7 @@
         <v>-0.8</v>
       </c>
       <c r="D215">
-        <v>-5.71</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -3566,7 +3566,7 @@
         <v>-0.81</v>
       </c>
       <c r="D216">
-        <v>-5.69</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -3580,7 +3580,7 @@
         <v>-0.81</v>
       </c>
       <c r="D217">
-        <v>-5.67</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -3594,7 +3594,7 @@
         <v>-0.83</v>
       </c>
       <c r="D218">
-        <v>-5.66</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -3608,7 +3608,7 @@
         <v>-0.84</v>
       </c>
       <c r="D219">
-        <v>-5.64</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -3622,7 +3622,7 @@
         <v>-0.85</v>
       </c>
       <c r="D220">
-        <v>-5.62</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -3636,7 +3636,7 @@
         <v>-0.87</v>
       </c>
       <c r="D221">
-        <v>-5.59</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -3650,7 +3650,7 @@
         <v>-0.88</v>
       </c>
       <c r="D222">
-        <v>-5.56</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -3664,7 +3664,7 @@
         <v>-0.89</v>
       </c>
       <c r="D223">
-        <v>-5.54</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -3678,7 +3678,7 @@
         <v>-0.91</v>
       </c>
       <c r="D224">
-        <v>-5.51</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -3692,7 +3692,7 @@
         <v>-0.92</v>
       </c>
       <c r="D225">
-        <v>-5.48</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -3706,7 +3706,7 @@
         <v>-0.94</v>
       </c>
       <c r="D226">
-        <v>-5.45</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -3720,7 +3720,7 @@
         <v>-0.95</v>
       </c>
       <c r="D227">
-        <v>-5.42</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -3734,7 +3734,7 @@
         <v>-0.97</v>
       </c>
       <c r="D228">
-        <v>-5.39</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -3748,7 +3748,7 @@
         <v>-0.98</v>
       </c>
       <c r="D229">
-        <v>-5.35</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
         <v>-0.99</v>
       </c>
       <c r="D230">
-        <v>-5.32</v>
+        <v>-2.0099999999999998</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -3776,7 +3776,7 @@
         <v>-1</v>
       </c>
       <c r="D231">
-        <v>-5.28</v>
+        <v>-2.0299999999999998</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -3790,7 +3790,7 @@
         <v>-1.01</v>
       </c>
       <c r="D232">
-        <v>-5.25</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -3804,7 +3804,7 @@
         <v>-1.02</v>
       </c>
       <c r="D233">
-        <v>-5.21</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -3818,7 +3818,7 @@
         <v>-1.03</v>
       </c>
       <c r="D234">
-        <v>-5.17</v>
+        <v>-2.0699999999999998</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -3832,7 +3832,7 @@
         <v>-1.03</v>
       </c>
       <c r="D235">
-        <v>-5.13</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -3846,7 +3846,7 @@
         <v>-1.03</v>
       </c>
       <c r="D236">
-        <v>-5.09</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -3860,7 +3860,7 @@
         <v>-1.03</v>
       </c>
       <c r="D237">
-        <v>-5.04</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -3874,7 +3874,7 @@
         <v>-1.03</v>
       </c>
       <c r="D238">
-        <v>-5</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -3888,7 +3888,7 @@
         <v>-1.04</v>
       </c>
       <c r="D239">
-        <v>-4.96</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -3902,7 +3902,7 @@
         <v>-1.04</v>
       </c>
       <c r="D240">
-        <v>-4.91</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -3916,7 +3916,7 @@
         <v>-1.04</v>
       </c>
       <c r="D241">
-        <v>-4.87</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -3930,7 +3930,7 @@
         <v>-1.03</v>
       </c>
       <c r="D242">
-        <v>-4.82</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -3944,7 +3944,7 @@
         <v>-1.02</v>
       </c>
       <c r="D243">
-        <v>-4.78</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -3958,7 +3958,7 @@
         <v>-1.01</v>
       </c>
       <c r="D244">
-        <v>-4.7300000000000004</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -3972,7 +3972,7 @@
         <v>-1</v>
       </c>
       <c r="D245">
-        <v>-4.68</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -3986,7 +3986,7 @@
         <v>-0.99</v>
       </c>
       <c r="D246">
-        <v>-4.6399999999999997</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -4000,7 +4000,7 @@
         <v>-0.99</v>
       </c>
       <c r="D247">
-        <v>-4.59</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -4014,7 +4014,7 @@
         <v>-0.97</v>
       </c>
       <c r="D248">
-        <v>-4.55</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
         <v>-0.96</v>
       </c>
       <c r="D249">
-        <v>-4.5</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -4042,7 +4042,7 @@
         <v>-0.95</v>
       </c>
       <c r="D250">
-        <v>-4.46</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -4056,7 +4056,7 @@
         <v>-0.93</v>
       </c>
       <c r="D251">
-        <v>-4.41</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -4070,7 +4070,7 @@
         <v>-0.91</v>
       </c>
       <c r="D252">
-        <v>-4.3600000000000003</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -4084,7 +4084,7 @@
         <v>-0.9</v>
       </c>
       <c r="D253">
-        <v>-4.3099999999999996</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -4098,7 +4098,7 @@
         <v>-0.88</v>
       </c>
       <c r="D254">
-        <v>-4.25</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -4112,7 +4112,7 @@
         <v>-0.86</v>
       </c>
       <c r="D255">
-        <v>-4.2</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -4126,7 +4126,7 @@
         <v>-0.84</v>
       </c>
       <c r="D256">
-        <v>-4.1399999999999997</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -4140,7 +4140,7 @@
         <v>-0.82</v>
       </c>
       <c r="D257">
-        <v>-4.08</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -4154,7 +4154,7 @@
         <v>-0.8</v>
       </c>
       <c r="D258">
-        <v>-4.0199999999999996</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -4168,7 +4168,7 @@
         <v>-0.77</v>
       </c>
       <c r="D259">
-        <v>-3.96</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -4182,7 +4182,7 @@
         <v>-0.74</v>
       </c>
       <c r="D260">
-        <v>-3.9</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -4196,7 +4196,7 @@
         <v>-0.72</v>
       </c>
       <c r="D261">
-        <v>-3.84</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -4210,7 +4210,7 @@
         <v>-0.69</v>
       </c>
       <c r="D262">
-        <v>-3.77</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -4224,7 +4224,7 @@
         <v>-0.67</v>
       </c>
       <c r="D263">
-        <v>-3.71</v>
+        <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -4238,7 +4238,7 @@
         <v>-0.64</v>
       </c>
       <c r="D264">
-        <v>-3.64</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -4252,7 +4252,7 @@
         <v>-0.62</v>
       </c>
       <c r="D265">
-        <v>-3.58</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -4266,7 +4266,7 @@
         <v>-0.59</v>
       </c>
       <c r="D266">
-        <v>-3.51</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
@@ -4280,7 +4280,7 @@
         <v>-0.56999999999999995</v>
       </c>
       <c r="D267">
-        <v>-3.44</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -4294,7 +4294,7 @@
         <v>-0.54</v>
       </c>
       <c r="D268">
-        <v>-3.38</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -4308,7 +4308,7 @@
         <v>-0.52</v>
       </c>
       <c r="D269">
-        <v>-3.31</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -4322,7 +4322,7 @@
         <v>-0.5</v>
       </c>
       <c r="D270">
-        <v>-3.24</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -4336,7 +4336,7 @@
         <v>-0.47</v>
       </c>
       <c r="D271">
-        <v>-3.17</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -4350,7 +4350,7 @@
         <v>-0.45</v>
       </c>
       <c r="D272">
-        <v>-3.1</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -4364,7 +4364,7 @@
         <v>-0.42</v>
       </c>
       <c r="D273">
-        <v>-3.03</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -4378,7 +4378,7 @@
         <v>-0.39</v>
       </c>
       <c r="D274">
-        <v>-2.96</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -4392,7 +4392,7 @@
         <v>-0.37</v>
       </c>
       <c r="D275">
-        <v>-2.89</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -4406,7 +4406,7 @@
         <v>-0.34</v>
       </c>
       <c r="D276">
-        <v>-2.82</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -4420,7 +4420,7 @@
         <v>-0.31</v>
       </c>
       <c r="D277">
-        <v>-2.76</v>
+        <v>-2.0699999999999998</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -4434,7 +4434,7 @@
         <v>-0.28999999999999998</v>
       </c>
       <c r="D278">
-        <v>-2.69</v>
+        <v>-2.0699999999999998</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -4448,7 +4448,7 @@
         <v>-0.26</v>
       </c>
       <c r="D279">
-        <v>-2.62</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>-0.23</v>
       </c>
       <c r="D280">
-        <v>-2.5499999999999998</v>
+        <v>-2.0499999999999998</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -4476,7 +4476,7 @@
         <v>-0.21</v>
       </c>
       <c r="D281">
-        <v>-2.48</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
@@ -4490,7 +4490,7 @@
         <v>-0.18</v>
       </c>
       <c r="D282">
-        <v>-2.41</v>
+        <v>-2.0299999999999998</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
@@ -4504,7 +4504,7 @@
         <v>-0.16</v>
       </c>
       <c r="D283">
-        <v>-2.34</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -4518,7 +4518,7 @@
         <v>-0.13</v>
       </c>
       <c r="D284">
-        <v>-2.27</v>
+        <v>-2.0099999999999998</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -4532,7 +4532,7 @@
         <v>-0.11</v>
       </c>
       <c r="D285">
-        <v>-2.2000000000000002</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -4546,7 +4546,7 @@
         <v>-0.09</v>
       </c>
       <c r="D286">
-        <v>-2.13</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -4560,7 +4560,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D287">
-        <v>-2.06</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -4574,7 +4574,7 @@
         <v>-0.05</v>
       </c>
       <c r="D288">
-        <v>-1.99</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -4588,7 +4588,7 @@
         <v>-0.03</v>
       </c>
       <c r="D289">
-        <v>-1.92</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>-1.85</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -4616,7 +4616,7 @@
         <v>0.02</v>
       </c>
       <c r="D291">
-        <v>-1.77</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -4630,7 +4630,7 @@
         <v>0.03</v>
       </c>
       <c r="D292">
-        <v>-1.7</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -4644,7 +4644,7 @@
         <v>0.05</v>
       </c>
       <c r="D293">
-        <v>-1.63</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -4658,7 +4658,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D294">
-        <v>-1.56</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -4672,7 +4672,7 @@
         <v>0.09</v>
       </c>
       <c r="D295">
-        <v>-1.48</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
@@ -4686,7 +4686,7 @@
         <v>0.11</v>
       </c>
       <c r="D296">
-        <v>-1.4</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -4700,7 +4700,7 @@
         <v>0.12</v>
       </c>
       <c r="D297">
-        <v>-1.33</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -4714,7 +4714,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="D298">
-        <v>-1.25</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -4728,7 +4728,7 @@
         <v>0.15</v>
       </c>
       <c r="D299">
-        <v>-1.17</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -4742,7 +4742,7 @@
         <v>0.16</v>
       </c>
       <c r="D300">
-        <v>-1.0900000000000001</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -4756,7 +4756,7 @@
         <v>0.17</v>
       </c>
       <c r="D301">
-        <v>-1.02</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
@@ -4770,7 +4770,7 @@
         <v>0.19</v>
       </c>
       <c r="D302">
-        <v>-0.94</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -4784,7 +4784,7 @@
         <v>0.2</v>
       </c>
       <c r="D303">
-        <v>-0.86</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
@@ -4798,7 +4798,7 @@
         <v>0.22</v>
       </c>
       <c r="D304">
-        <v>-0.79</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
@@ -4812,7 +4812,7 @@
         <v>0.23</v>
       </c>
       <c r="D305">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -4826,7 +4826,7 @@
         <v>0.24</v>
       </c>
       <c r="D306">
-        <v>-0.63</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -4840,7 +4840,7 @@
         <v>0.25</v>
       </c>
       <c r="D307">
-        <v>-0.56000000000000005</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -4854,7 +4854,7 @@
         <v>0.26</v>
       </c>
       <c r="D308">
-        <v>-0.48</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -4868,7 +4868,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="D309">
-        <v>-0.41</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -4882,7 +4882,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="D310">
-        <v>-0.33</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -4896,7 +4896,7 @@
         <v>0.3</v>
       </c>
       <c r="D311">
-        <v>-0.26</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -4910,7 +4910,7 @@
         <v>0.3</v>
       </c>
       <c r="D312">
-        <v>-0.18</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -4924,7 +4924,7 @@
         <v>0.31</v>
       </c>
       <c r="D313">
-        <v>-0.1</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
@@ -4938,7 +4938,7 @@
         <v>0.32</v>
       </c>
       <c r="D314">
-        <v>-0.03</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -4952,7 +4952,7 @@
         <v>0.35</v>
       </c>
       <c r="D315">
-        <v>0.05</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -4966,7 +4966,7 @@
         <v>0.37</v>
       </c>
       <c r="D316">
-        <v>0.13</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -4980,7 +4980,7 @@
         <v>0.38</v>
       </c>
       <c r="D317">
-        <v>0.21</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
@@ -4994,7 +4994,7 @@
         <v>0.4</v>
       </c>
       <c r="D318">
-        <v>0.28999999999999998</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
@@ -5008,7 +5008,7 @@
         <v>0.41</v>
       </c>
       <c r="D319">
-        <v>0.37</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -5022,7 +5022,7 @@
         <v>0.42</v>
       </c>
       <c r="D320">
-        <v>0.45</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -5036,7 +5036,7 @@
         <v>0.44</v>
       </c>
       <c r="D321">
-        <v>0.53</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -5050,7 +5050,7 @@
         <v>0.46</v>
       </c>
       <c r="D322">
-        <v>0.62</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -5064,7 +5064,7 @@
         <v>0.48</v>
       </c>
       <c r="D323">
-        <v>0.7</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -5078,7 +5078,7 @@
         <v>0.49</v>
       </c>
       <c r="D324">
-        <v>0.78</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
@@ -5092,7 +5092,7 @@
         <v>0.5</v>
       </c>
       <c r="D325">
-        <v>0.86</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -5106,7 +5106,7 @@
         <v>0.51</v>
       </c>
       <c r="D326">
-        <v>0.94</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
@@ -5120,7 +5120,7 @@
         <v>0.53</v>
       </c>
       <c r="D327">
-        <v>1.02</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -5134,7 +5134,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D328">
-        <v>1.0900000000000001</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
@@ -5148,7 +5148,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="D329">
-        <v>1.1599999999999999</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -5162,7 +5162,7 @@
         <v>0.6</v>
       </c>
       <c r="D330">
-        <v>1.24</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
@@ -5176,7 +5176,7 @@
         <v>0.61</v>
       </c>
       <c r="D331">
-        <v>1.31</v>
+        <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
@@ -5190,7 +5190,7 @@
         <v>0.63</v>
       </c>
       <c r="D332">
-        <v>1.39</v>
+        <v>-1.1200000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
@@ -5204,7 +5204,7 @@
         <v>0.64</v>
       </c>
       <c r="D333">
-        <v>1.46</v>
+        <v>-1.0900000000000001</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
@@ -5218,7 +5218,7 @@
         <v>0.66</v>
       </c>
       <c r="D334">
-        <v>1.54</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -5232,7 +5232,7 @@
         <v>0.67</v>
       </c>
       <c r="D335">
-        <v>1.61</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
@@ -5246,7 +5246,7 @@
         <v>0.69</v>
       </c>
       <c r="D336">
-        <v>1.69</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -5260,7 +5260,7 @@
         <v>0.71</v>
       </c>
       <c r="D337">
-        <v>1.77</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
@@ -5274,7 +5274,7 @@
         <v>0.73</v>
       </c>
       <c r="D338">
-        <v>1.84</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -5288,7 +5288,7 @@
         <v>0.74</v>
       </c>
       <c r="D339">
-        <v>1.91</v>
+        <v>-0.94</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
@@ -5302,7 +5302,7 @@
         <v>0.76</v>
       </c>
       <c r="D340">
-        <v>1.99</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -5316,7 +5316,7 @@
         <v>0.78</v>
       </c>
       <c r="D341">
-        <v>2.06</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -5330,7 +5330,7 @@
         <v>0.8</v>
       </c>
       <c r="D342">
-        <v>2.13</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
@@ -5344,7 +5344,7 @@
         <v>0.81</v>
       </c>
       <c r="D343">
-        <v>2.2000000000000002</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
@@ -5358,7 +5358,7 @@
         <v>0.82</v>
       </c>
       <c r="D344">
-        <v>2.27</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -5372,7 +5372,7 @@
         <v>0.84</v>
       </c>
       <c r="D345">
-        <v>2.34</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -5386,7 +5386,7 @@
         <v>0.86</v>
       </c>
       <c r="D346">
-        <v>2.41</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
@@ -5400,7 +5400,7 @@
         <v>0.88</v>
       </c>
       <c r="D347">
-        <v>2.48</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
@@ -5414,7 +5414,7 @@
         <v>0.9</v>
       </c>
       <c r="D348">
-        <v>2.5499999999999998</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
@@ -5428,7 +5428,7 @@
         <v>0.92</v>
       </c>
       <c r="D349">
-        <v>2.62</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
@@ -5442,7 +5442,7 @@
         <v>0.94</v>
       </c>
       <c r="D350">
-        <v>2.69</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
@@ -5456,7 +5456,7 @@
         <v>0.95</v>
       </c>
       <c r="D351">
-        <v>2.75</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
@@ -5470,7 +5470,7 @@
         <v>0.96</v>
       </c>
       <c r="D352">
-        <v>2.82</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
@@ -5484,7 +5484,7 @@
         <v>0.97</v>
       </c>
       <c r="D353">
-        <v>2.88</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
@@ -5498,7 +5498,7 @@
         <v>0.99</v>
       </c>
       <c r="D354">
-        <v>2.93</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
@@ -5512,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="D355">
-        <v>2.99</v>
+        <v>-0.57999999999999996</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
@@ -5526,7 +5526,7 @@
         <v>1.02</v>
       </c>
       <c r="D356">
-        <v>3.04</v>
+        <v>-0.55000000000000004</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
@@ -5540,7 +5540,7 @@
         <v>1.03</v>
       </c>
       <c r="D357">
-        <v>3.08</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
@@ -5554,7 +5554,7 @@
         <v>1.04</v>
       </c>
       <c r="D358">
-        <v>3.12</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
@@ -5568,7 +5568,7 @@
         <v>1.05</v>
       </c>
       <c r="D359">
-        <v>3.16</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
@@ -5582,7 +5582,7 @@
         <v>1.06</v>
       </c>
       <c r="D360">
-        <v>3.19</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
@@ -5596,7 +5596,7 @@
         <v>1.07</v>
       </c>
       <c r="D361">
-        <v>3.23</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
@@ -5610,7 +5610,7 @@
         <v>1.08</v>
       </c>
       <c r="D362">
-        <v>3.26</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
@@ -5624,7 +5624,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="D363">
-        <v>3.28</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
@@ -5638,7 +5638,7 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="D364">
-        <v>3.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
@@ -5652,7 +5652,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="D365">
-        <v>3.32</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
@@ -5666,7 +5666,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="D366">
-        <v>3.33</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
@@ -5680,7 +5680,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="D367">
-        <v>3.33</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
@@ -5694,7 +5694,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="D368">
-        <v>3.32</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
@@ -5708,7 +5708,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="D369">
-        <v>3.31</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
@@ -5722,7 +5722,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="D370">
-        <v>3.29</v>
+        <v>-0.28999999999999998</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
@@ -5736,7 +5736,7 @@
         <v>1.17</v>
       </c>
       <c r="D371">
-        <v>3.26</v>
+        <v>-0.28000000000000003</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
@@ -5750,7 +5750,7 @@
         <v>1.17</v>
       </c>
       <c r="D372">
-        <v>3.22</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
@@ -5764,7 +5764,7 @@
         <v>1.18</v>
       </c>
       <c r="D373">
-        <v>3.17</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
@@ -5778,7 +5778,7 @@
         <v>1.19</v>
       </c>
       <c r="D374">
-        <v>3.1</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
@@ -5792,7 +5792,7 @@
         <v>1.2</v>
       </c>
       <c r="D375">
-        <v>3.03</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
@@ -5806,7 +5806,7 @@
         <v>1.2</v>
       </c>
       <c r="D376">
-        <v>2.94</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
@@ -5820,7 +5820,7 @@
         <v>1.21</v>
       </c>
       <c r="D377">
-        <v>2.84</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
@@ -5834,7 +5834,7 @@
         <v>1.21</v>
       </c>
       <c r="D378">
-        <v>2.73</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
@@ -5848,7 +5848,7 @@
         <v>1.21</v>
       </c>
       <c r="D379">
-        <v>2.61</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
@@ -5862,7 +5862,7 @@
         <v>1.22</v>
       </c>
       <c r="D380">
-        <v>2.4700000000000002</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
@@ -5876,7 +5876,7 @@
         <v>1.23</v>
       </c>
       <c r="D381">
-        <v>2.33</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
@@ -5890,7 +5890,7 @@
         <v>1.23</v>
       </c>
       <c r="D382">
-        <v>2.17</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
@@ -5904,7 +5904,7 @@
         <v>1.24</v>
       </c>
       <c r="D383">
-        <v>2.0099999999999998</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
@@ -5918,7 +5918,7 @@
         <v>1.25</v>
       </c>
       <c r="D384">
-        <v>1.83</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
@@ -5932,7 +5932,7 @@
         <v>1.25</v>
       </c>
       <c r="D385">
-        <v>1.65</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
@@ -5946,7 +5946,7 @@
         <v>1.26</v>
       </c>
       <c r="D386">
-        <v>1.47</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
@@ -5960,7 +5960,7 @@
         <v>1.27</v>
       </c>
       <c r="D387">
-        <v>1.28</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
@@ -5974,7 +5974,7 @@
         <v>1.27</v>
       </c>
       <c r="D388">
-        <v>1.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
@@ -5988,7 +5988,7 @@
         <v>1.28</v>
       </c>
       <c r="D389">
-        <v>0.89</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
@@ -6002,7 +6002,7 @@
         <v>1.3</v>
       </c>
       <c r="D390">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
@@ -6016,7 +6016,7 @@
         <v>1.31</v>
       </c>
       <c r="D391">
-        <v>0.51</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
@@ -6030,7 +6030,7 @@
         <v>1.32</v>
       </c>
       <c r="D392">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
@@ -6044,7 +6044,7 @@
         <v>1.33</v>
       </c>
       <c r="D393">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
@@ -6058,7 +6058,7 @@
         <v>1.35</v>
       </c>
       <c r="D394">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
@@ -6072,7 +6072,7 @@
         <v>1.36</v>
       </c>
       <c r="D395">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
@@ -6086,7 +6086,7 @@
         <v>1.38</v>
       </c>
       <c r="D396">
-        <v>-0.35</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
@@ -6100,7 +6100,7 @@
         <v>1.4</v>
       </c>
       <c r="D397">
-        <v>-0.49</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
@@ -6114,7 +6114,7 @@
         <v>1.42</v>
       </c>
       <c r="D398">
-        <v>-0.64</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
@@ -6128,7 +6128,7 @@
         <v>1.44</v>
       </c>
       <c r="D399">
-        <v>-0.77</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>1.46</v>
       </c>
       <c r="D400">
-        <v>-0.9</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
@@ -6156,7 +6156,7 @@
         <v>1.49</v>
       </c>
       <c r="D401">
-        <v>-1.02</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
@@ -6170,7 +6170,7 @@
         <v>1.52</v>
       </c>
       <c r="D402">
-        <v>-1.1399999999999999</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
@@ -6184,7 +6184,7 @@
         <v>1.54</v>
       </c>
       <c r="D403">
-        <v>-1.26</v>
+        <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
@@ -6198,7 +6198,7 @@
         <v>1.57</v>
       </c>
       <c r="D404">
-        <v>-1.38</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
@@ -6212,7 +6212,7 @@
         <v>1.61</v>
       </c>
       <c r="D405">
-        <v>-1.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
@@ -6226,7 +6226,7 @@
         <v>1.64</v>
       </c>
       <c r="D406">
-        <v>-1.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
@@ -6240,7 +6240,7 @@
         <v>1.67</v>
       </c>
       <c r="D407">
-        <v>-1.73</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
@@ -6254,7 +6254,7 @@
         <v>1.71</v>
       </c>
       <c r="D408">
-        <v>-1.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
@@ -6268,7 +6268,7 @@
         <v>1.75</v>
       </c>
       <c r="D409">
-        <v>-1.97</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
@@ -6282,7 +6282,7 @@
         <v>1.79</v>
       </c>
       <c r="D410">
-        <v>-2.1</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
@@ -6296,7 +6296,7 @@
         <v>1.84</v>
       </c>
       <c r="D411">
-        <v>-2.23</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
@@ -6310,7 +6310,7 @@
         <v>1.9</v>
       </c>
       <c r="D412">
-        <v>-2.37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
@@ -6324,7 +6324,7 @@
         <v>1.95</v>
       </c>
       <c r="D413">
-        <v>-2.5099999999999998</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
@@ -6338,7 +6338,7 @@
         <v>2</v>
       </c>
       <c r="D414">
-        <v>-2.65</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
@@ -6352,7 +6352,7 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="D415">
-        <v>-2.8</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
@@ -6366,7 +6366,7 @@
         <v>2.1</v>
       </c>
       <c r="D416">
-        <v>-2.96</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
@@ -6380,7 +6380,7 @@
         <v>2.16</v>
       </c>
       <c r="D417">
-        <v>-3.12</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
@@ -6394,7 +6394,7 @@
         <v>2.21</v>
       </c>
       <c r="D418">
-        <v>-3.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.3">
@@ -6408,7 +6408,7 @@
         <v>2.2799999999999998</v>
       </c>
       <c r="D419">
-        <v>-3.46</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.3">
@@ -6422,7 +6422,7 @@
         <v>2.34</v>
       </c>
       <c r="D420">
-        <v>-3.63</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
@@ -6436,7 +6436,7 @@
         <v>2.4</v>
       </c>
       <c r="D421">
-        <v>-3.8</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
@@ -6450,7 +6450,7 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="D422">
-        <v>-3.98</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
@@ -6464,7 +6464,7 @@
         <v>2.54</v>
       </c>
       <c r="D423">
-        <v>-4.16</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
@@ -6478,7 +6478,7 @@
         <v>2.6</v>
       </c>
       <c r="D424">
-        <v>-4.34</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
@@ -6492,7 +6492,7 @@
         <v>2.68</v>
       </c>
       <c r="D425">
-        <v>-4.51</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
@@ -6506,7 +6506,7 @@
         <v>2.75</v>
       </c>
       <c r="D426">
-        <v>-4.68</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
@@ -6520,7 +6520,7 @@
         <v>2.82</v>
       </c>
       <c r="D427">
-        <v>-4.8499999999999996</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
@@ -6534,7 +6534,7 @@
         <v>2.89</v>
       </c>
       <c r="D428">
-        <v>-5.01</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
@@ -6548,7 +6548,7 @@
         <v>2.96</v>
       </c>
       <c r="D429">
-        <v>-5.15</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
@@ -6562,7 +6562,7 @@
         <v>3.03</v>
       </c>
       <c r="D430">
-        <v>-5.28</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
@@ -6576,7 +6576,7 @@
         <v>3.1</v>
       </c>
       <c r="D431">
-        <v>-5.4</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
@@ -6590,7 +6590,7 @@
         <v>3.18</v>
       </c>
       <c r="D432">
-        <v>-5.5</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
@@ -6604,7 +6604,7 @@
         <v>3.25</v>
       </c>
       <c r="D433">
-        <v>-5.58</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.3">
@@ -6618,7 +6618,7 @@
         <v>3.33</v>
       </c>
       <c r="D434">
-        <v>-5.64</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
@@ -6632,7 +6632,7 @@
         <v>3.4</v>
       </c>
       <c r="D435">
-        <v>-5.68</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
@@ -6646,7 +6646,7 @@
         <v>3.48</v>
       </c>
       <c r="D436">
-        <v>-5.69</v>
+        <v>2.5099999999999998</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
@@ -6660,7 +6660,7 @@
         <v>3.56</v>
       </c>
       <c r="D437">
-        <v>-5.67</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.3">
@@ -6674,7 +6674,7 @@
         <v>3.65</v>
       </c>
       <c r="D438">
-        <v>-5.62</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.3">
@@ -6688,7 +6688,7 @@
         <v>3.73</v>
       </c>
       <c r="D439">
-        <v>-5.55</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.3">
@@ -6702,7 +6702,7 @@
         <v>3.82</v>
       </c>
       <c r="D440">
-        <v>-5.45</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
@@ -6716,7 +6716,7 @@
         <v>3.92</v>
       </c>
       <c r="D441">
-        <v>-5.33</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
@@ -6730,7 +6730,7 @@
         <v>4.01</v>
       </c>
       <c r="D442">
-        <v>-5.19</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
@@ -6744,7 +6744,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="D443">
-        <v>-5.01</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
@@ -6758,7 +6758,7 @@
         <v>4.1900000000000004</v>
       </c>
       <c r="D444">
-        <v>-4.8099999999999996</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
@@ -6772,7 +6772,7 @@
         <v>4.29</v>
       </c>
       <c r="D445">
-        <v>-4.59</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
@@ -6786,7 +6786,7 @@
         <v>4.3899999999999997</v>
       </c>
       <c r="D446">
-        <v>-4.3600000000000003</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
@@ -6800,7 +6800,7 @@
         <v>4.5</v>
       </c>
       <c r="D447">
-        <v>-4.13</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
@@ -6814,7 +6814,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="D448">
-        <v>-3.87</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.3">
@@ -6828,7 +6828,7 @@
         <v>4.71</v>
       </c>
       <c r="D449">
-        <v>-3.61</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.3">
@@ -6842,7 +6842,7 @@
         <v>4.82</v>
       </c>
       <c r="D450">
-        <v>-3.33</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
@@ -6856,7 +6856,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="D451">
-        <v>-3.04</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
@@ -6870,7 +6870,7 @@
         <v>5.05</v>
       </c>
       <c r="D452">
-        <v>-2.75</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
@@ -6884,7 +6884,7 @@
         <v>5.17</v>
       </c>
       <c r="D453">
-        <v>-2.46</v>
+        <v>4.0199999999999996</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
@@ -6898,7 +6898,7 @@
         <v>5.29</v>
       </c>
       <c r="D454">
-        <v>-2.16</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
@@ -6912,7 +6912,7 @@
         <v>5.41</v>
       </c>
       <c r="D455">
-        <v>-1.86</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
@@ -6926,7 +6926,7 @@
         <v>5.53</v>
       </c>
       <c r="D456">
-        <v>-1.56</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
@@ -6940,7 +6940,7 @@
         <v>5.65</v>
       </c>
       <c r="D457">
-        <v>-1.25</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
@@ -6954,7 +6954,7 @@
         <v>5.77</v>
       </c>
       <c r="D458">
-        <v>-0.95</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
@@ -6968,7 +6968,7 @@
         <v>5.9</v>
       </c>
       <c r="D459">
-        <v>-0.66</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
@@ -6982,7 +6982,7 @@
         <v>6.02</v>
       </c>
       <c r="D460">
-        <v>-0.36</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
@@ -6996,7 +6996,7 @@
         <v>6.15</v>
       </c>
       <c r="D461">
-        <v>-0.06</v>
+        <v>4.9800000000000004</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
@@ -7010,7 +7010,7 @@
         <v>6.27</v>
       </c>
       <c r="D462">
-        <v>0.24</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.3">
@@ -7024,7 +7024,7 @@
         <v>6.4</v>
       </c>
       <c r="D463">
-        <v>0.54</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
@@ -7038,7 +7038,7 @@
         <v>6.52</v>
       </c>
       <c r="D464">
-        <v>0.83</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
@@ -7052,7 +7052,7 @@
         <v>6.63</v>
       </c>
       <c r="D465">
-        <v>1.1100000000000001</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.3">
@@ -7066,7 +7066,7 @@
         <v>6.75</v>
       </c>
       <c r="D466">
-        <v>1.38</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.3">
@@ -7080,7 +7080,7 @@
         <v>6.87</v>
       </c>
       <c r="D467">
-        <v>1.66</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.3">
@@ -7094,7 +7094,7 @@
         <v>6.97</v>
       </c>
       <c r="D468">
-        <v>1.93</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
@@ -7108,7 +7108,7 @@
         <v>7.08</v>
       </c>
       <c r="D469">
-        <v>2.19</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
@@ -7122,7 +7122,7 @@
         <v>7.19</v>
       </c>
       <c r="D470">
-        <v>2.44</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.3">
@@ -7136,7 +7136,7 @@
         <v>7.29</v>
       </c>
       <c r="D471">
-        <v>2.68</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.3">
@@ -7150,7 +7150,7 @@
         <v>7.39</v>
       </c>
       <c r="D472">
-        <v>2.92</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.3">
@@ -7164,7 +7164,7 @@
         <v>7.5</v>
       </c>
       <c r="D473">
-        <v>3.15</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
@@ -7178,7 +7178,7 @@
         <v>7.6</v>
       </c>
       <c r="D474">
-        <v>3.37</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
@@ -7192,7 +7192,7 @@
         <v>7.7</v>
       </c>
       <c r="D475">
-        <v>3.58</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.3">
@@ -7206,7 +7206,7 @@
         <v>7.8</v>
       </c>
       <c r="D476">
-        <v>3.78</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.3">
@@ -7220,7 +7220,7 @@
         <v>7.9</v>
       </c>
       <c r="D477">
-        <v>3.97</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.3">
@@ -7234,7 +7234,7 @@
         <v>8</v>
       </c>
       <c r="D478">
-        <v>4.16</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
@@ -7248,7 +7248,7 @@
         <v>8.1</v>
       </c>
       <c r="D479">
-        <v>4.34</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.3">
@@ -7262,7 +7262,7 @@
         <v>8.19</v>
       </c>
       <c r="D480">
-        <v>4.51</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.3">
@@ -7276,7 +7276,7 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="D481">
-        <v>4.66</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.3">
@@ -7290,7 +7290,7 @@
         <v>8.3699999999999992</v>
       </c>
       <c r="D482">
-        <v>4.79</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
@@ -7304,7 +7304,7 @@
         <v>8.4499999999999993</v>
       </c>
       <c r="D483">
-        <v>4.92</v>
+        <v>8.2100000000000009</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
@@ -7318,7 +7318,7 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="D484">
-        <v>5.03</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
@@ -7332,7 +7332,7 @@
         <v>8.6</v>
       </c>
       <c r="D485">
-        <v>5.14</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
@@ -7346,7 +7346,7 @@
         <v>8.68</v>
       </c>
       <c r="D486">
-        <v>5.23</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
@@ -7360,7 +7360,7 @@
         <v>8.75</v>
       </c>
       <c r="D487">
-        <v>5.3</v>
+        <v>8.7799999999999994</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.3">
@@ -7374,7 +7374,7 @@
         <v>8.82</v>
       </c>
       <c r="D488">
-        <v>5.36</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.3">
@@ -7388,7 +7388,7 @@
         <v>8.8800000000000008</v>
       </c>
       <c r="D489">
-        <v>5.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.3">
@@ -7402,7 +7402,7 @@
         <v>8.9499999999999993</v>
       </c>
       <c r="D490">
-        <v>5.44</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
@@ -7416,7 +7416,7 @@
         <v>9.01</v>
       </c>
       <c r="D491">
-        <v>5.46</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
@@ -7430,7 +7430,7 @@
         <v>9.07</v>
       </c>
       <c r="D492">
-        <v>5.46</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
@@ -7444,7 +7444,7 @@
         <v>9.1300000000000008</v>
       </c>
       <c r="D493">
-        <v>5.43</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.3">
@@ -7458,7 +7458,7 @@
         <v>9.19</v>
       </c>
       <c r="D494">
-        <v>5.39</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.3">
@@ -7472,7 +7472,7 @@
         <v>9.25</v>
       </c>
       <c r="D495">
-        <v>5.33</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.3">
@@ -7486,7 +7486,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="D496">
-        <v>5.25</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.3">
@@ -7500,7 +7500,7 @@
         <v>9.35</v>
       </c>
       <c r="D497">
-        <v>5.15</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.3">
@@ -7514,7 +7514,7 @@
         <v>9.4</v>
       </c>
       <c r="D498">
-        <v>5.04</v>
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.3">
@@ -7528,7 +7528,7 @@
         <v>9.44</v>
       </c>
       <c r="D499">
-        <v>4.91</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.3">
@@ -7542,7 +7542,7 @@
         <v>9.49</v>
       </c>
       <c r="D500">
-        <v>4.7699999999999996</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
@@ -7556,7 +7556,7 @@
         <v>9.5399999999999991</v>
       </c>
       <c r="D501">
-        <v>4.6100000000000003</v>
+        <v>9.7899999999999991</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.3">
@@ -7570,7 +7570,7 @@
         <v>9.57</v>
       </c>
       <c r="D502">
-        <v>4.4400000000000004</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.3">
@@ -7584,7 +7584,7 @@
         <v>9.61</v>
       </c>
       <c r="D503">
-        <v>4.25</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.3">
@@ -7598,7 +7598,7 @@
         <v>9.65</v>
       </c>
       <c r="D504">
-        <v>4.05</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
@@ -7612,7 +7612,7 @@
         <v>9.68</v>
       </c>
       <c r="D505">
-        <v>3.85</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.3">
@@ -7626,7 +7626,7 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="D506">
-        <v>3.64</v>
+        <v>9.89</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.3">
@@ -7640,7 +7640,7 @@
         <v>9.74</v>
       </c>
       <c r="D507">
-        <v>3.43</v>
+        <v>9.8800000000000008</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.3">
@@ -7654,7 +7654,7 @@
         <v>9.76</v>
       </c>
       <c r="D508">
-        <v>3.23</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
@@ -7668,7 +7668,7 @@
         <v>9.7899999999999991</v>
       </c>
       <c r="D509">
-        <v>3.02</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.3">
@@ -7682,7 +7682,7 @@
         <v>9.81</v>
       </c>
       <c r="D510">
-        <v>2.82</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.3">
@@ -7696,7 +7696,7 @@
         <v>9.83</v>
       </c>
       <c r="D511">
-        <v>2.61</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.3">
@@ -7710,7 +7710,7 @@
         <v>9.85</v>
       </c>
       <c r="D512">
-        <v>2.41</v>
+        <v>9.6300000000000008</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
@@ -7724,7 +7724,7 @@
         <v>9.8699999999999992</v>
       </c>
       <c r="D513">
-        <v>2.21</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
@@ -7738,7 +7738,7 @@
         <v>9.9</v>
       </c>
       <c r="D514">
-        <v>2.04</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
@@ -7752,7 +7752,7 @@
         <v>9.92</v>
       </c>
       <c r="D515">
-        <v>1.87</v>
+        <v>9.5299999999999994</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
@@ -7766,7 +7766,7 @@
         <v>9.93</v>
       </c>
       <c r="D516">
-        <v>1.73</v>
+        <v>9.4600000000000009</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
@@ -7780,7 +7780,7 @@
         <v>9.94</v>
       </c>
       <c r="D517">
-        <v>1.6</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
@@ -7794,7 +7794,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="D518">
-        <v>1.49</v>
+        <v>9.2100000000000009</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
@@ -7808,7 +7808,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="D519">
-        <v>1.39</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
@@ -7822,7 +7822,7 @@
         <v>9.9600000000000009</v>
       </c>
       <c r="D520">
-        <v>1.3</v>
+        <v>8.9499999999999993</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
@@ -7836,7 +7836,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="D521">
-        <v>1.23</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.3">
@@ -7850,7 +7850,7 @@
         <v>9.94</v>
       </c>
       <c r="D522">
-        <v>1.17</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
@@ -7864,7 +7864,7 @@
         <v>9.93</v>
       </c>
       <c r="D523">
-        <v>1.1399999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
@@ -7878,7 +7878,7 @@
         <v>9.91</v>
       </c>
       <c r="D524">
-        <v>1.1200000000000001</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
@@ -7892,7 +7892,7 @@
         <v>9.8800000000000008</v>
       </c>
       <c r="D525">
-        <v>1.1299999999999999</v>
+        <v>8.5399999999999991</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
@@ -7906,7 +7906,7 @@
         <v>9.85</v>
       </c>
       <c r="D526">
-        <v>1.17</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.3">
@@ -7920,7 +7920,7 @@
         <v>9.81</v>
       </c>
       <c r="D527">
-        <v>1.24</v>
+        <v>8.2100000000000009</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
@@ -7934,7 +7934,7 @@
         <v>9.77</v>
       </c>
       <c r="D528">
-        <v>1.36</v>
+        <v>8.0399999999999991</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.3">
@@ -7948,7 +7948,7 @@
         <v>9.74</v>
       </c>
       <c r="D529">
-        <v>1.51</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.3">
@@ -7962,7 +7962,7 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="D530">
-        <v>1.7</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.3">
@@ -7976,7 +7976,7 @@
         <v>9.69</v>
       </c>
       <c r="D531">
-        <v>1.91</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.3">
@@ -7990,7 +7990,7 @@
         <v>9.67</v>
       </c>
       <c r="D532">
-        <v>2.13</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.3">
@@ -8004,7 +8004,7 @@
         <v>9.64</v>
       </c>
       <c r="D533">
-        <v>2.36</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.3">
@@ -8018,7 +8018,7 @@
         <v>9.6</v>
       </c>
       <c r="D534">
-        <v>2.58</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.3">
@@ -8032,7 +8032,7 @@
         <v>9.5399999999999991</v>
       </c>
       <c r="D535">
-        <v>2.81</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.3">
@@ -8046,7 +8046,7 @@
         <v>9.4700000000000006</v>
       </c>
       <c r="D536">
-        <v>3.03</v>
+        <v>7</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.3">
@@ -8060,7 +8060,7 @@
         <v>9.4</v>
       </c>
       <c r="D537">
-        <v>3.25</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.3">
@@ -8074,7 +8074,7 @@
         <v>9.33</v>
       </c>
       <c r="D538">
-        <v>3.45</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
@@ -8088,7 +8088,7 @@
         <v>9.26</v>
       </c>
       <c r="D539">
-        <v>3.63</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
@@ -8102,7 +8102,7 @@
         <v>9.2100000000000009</v>
       </c>
       <c r="D540">
-        <v>3.79</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
@@ -8116,7 +8116,7 @@
         <v>9.16</v>
       </c>
       <c r="D541">
-        <v>3.94</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.3">
@@ -8130,7 +8130,7 @@
         <v>9.1</v>
       </c>
       <c r="D542">
-        <v>4.08</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
@@ -8144,7 +8144,7 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="D543">
-        <v>4.22</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
@@ -8158,7 +8158,7 @@
         <v>8.9600000000000009</v>
       </c>
       <c r="D544">
-        <v>4.3600000000000003</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
@@ -8172,7 +8172,7 @@
         <v>8.8800000000000008</v>
       </c>
       <c r="D545">
-        <v>4.49</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
@@ -8186,7 +8186,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="D546">
-        <v>4.5999999999999996</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
@@ -8200,7 +8200,7 @@
         <v>8.73</v>
       </c>
       <c r="D547">
-        <v>4.6900000000000004</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
@@ -8214,7 +8214,7 @@
         <v>8.66</v>
       </c>
       <c r="D548">
-        <v>4.78</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
@@ -8228,7 +8228,7 @@
         <v>8.58</v>
       </c>
       <c r="D549">
-        <v>4.8600000000000003</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
@@ -8242,7 +8242,7 @@
         <v>8.4700000000000006</v>
       </c>
       <c r="D550">
-        <v>4.9400000000000004</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
@@ -8256,7 +8256,7 @@
         <v>8.33</v>
       </c>
       <c r="D551">
-        <v>5.01</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
@@ -8270,7 +8270,7 @@
         <v>8.16</v>
       </c>
       <c r="D552">
-        <v>5.0599999999999996</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
@@ -8284,7 +8284,7 @@
         <v>7.96</v>
       </c>
       <c r="D553">
-        <v>5.1100000000000003</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.3">
@@ -8298,7 +8298,7 @@
         <v>7.71</v>
       </c>
       <c r="D554">
-        <v>5.14</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
@@ -8312,7 +8312,7 @@
         <v>7.44</v>
       </c>
       <c r="D555">
-        <v>5.16</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
@@ -8326,7 +8326,7 @@
         <v>7.17</v>
       </c>
       <c r="D556">
-        <v>5.16</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
@@ -8340,7 +8340,7 @@
         <v>6.89</v>
       </c>
       <c r="D557">
-        <v>5.14</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
@@ -8354,7 +8354,7 @@
         <v>6.65</v>
       </c>
       <c r="D558">
-        <v>5.0999999999999996</v>
+        <v>4.4800000000000004</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
@@ -8368,7 +8368,7 @@
         <v>6.44</v>
       </c>
       <c r="D559">
-        <v>5.05</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
@@ -8382,7 +8382,7 @@
         <v>6.27</v>
       </c>
       <c r="D560">
-        <v>4.9800000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
@@ -8396,7 +8396,7 @@
         <v>6.17</v>
       </c>
       <c r="D561">
-        <v>4.9000000000000004</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.3">
@@ -8410,7 +8410,7 @@
         <v>6.14</v>
       </c>
       <c r="D562">
-        <v>4.78</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.3">
@@ -8424,7 +8424,7 @@
         <v>6.13</v>
       </c>
       <c r="D563">
-        <v>4.6500000000000004</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
@@ -8438,7 +8438,7 @@
         <v>6.16</v>
       </c>
       <c r="D564">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
@@ -8452,7 +8452,7 @@
         <v>6.22</v>
       </c>
       <c r="D565">
-        <v>4.3099999999999996</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
@@ -8466,7 +8466,7 @@
         <v>6.27</v>
       </c>
       <c r="D566">
-        <v>4.0999999999999996</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
@@ -8480,7 +8480,7 @@
         <v>6.29</v>
       </c>
       <c r="D567">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
@@ -8494,7 +8494,7 @@
         <v>6.27</v>
       </c>
       <c r="D568">
-        <v>3.56</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
@@ -8508,7 +8508,7 @@
         <v>6.22</v>
       </c>
       <c r="D569">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
@@ -8522,7 +8522,7 @@
         <v>6.15</v>
       </c>
       <c r="D570">
-        <v>2.82</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
@@ -8536,7 +8536,7 @@
         <v>6.06</v>
       </c>
       <c r="D571">
-        <v>2.36</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
@@ -8550,7 +8550,7 @@
         <v>5.98</v>
       </c>
       <c r="D572">
-        <v>1.86</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
@@ -8564,7 +8564,7 @@
         <v>5.89</v>
       </c>
       <c r="D573">
-        <v>1.34</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
@@ -8578,7 +8578,7 @@
         <v>5.82</v>
       </c>
       <c r="D574">
-        <v>0.81</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
@@ -8592,7 +8592,7 @@
         <v>5.76</v>
       </c>
       <c r="D575">
-        <v>0.26</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
@@ -8606,7 +8606,7 @@
         <v>5.73</v>
       </c>
       <c r="D576">
-        <v>-0.3</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
@@ -8620,7 +8620,7 @@
         <v>5.72</v>
       </c>
       <c r="D577">
-        <v>-0.82</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
@@ -8634,7 +8634,7 @@
         <v>5.73</v>
       </c>
       <c r="D578">
-        <v>-1.27</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
@@ -8648,7 +8648,7 @@
         <v>5.78</v>
       </c>
       <c r="D579">
-        <v>-1.61</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
@@ -8662,7 +8662,7 @@
         <v>5.84</v>
       </c>
       <c r="D580">
-        <v>-1.85</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
@@ -8676,7 +8676,7 @@
         <v>5.89</v>
       </c>
       <c r="D581">
-        <v>-1.96</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
@@ -8690,7 +8690,7 @@
         <v>5.93</v>
       </c>
       <c r="D582">
-        <v>-1.96</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
@@ -8704,7 +8704,7 @@
         <v>5.92</v>
       </c>
       <c r="D583">
-        <v>-1.87</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
@@ -8718,7 +8718,7 @@
         <v>5.85</v>
       </c>
       <c r="D584">
-        <v>-1.71</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
@@ -8732,7 +8732,7 @@
         <v>5.77</v>
       </c>
       <c r="D585">
-        <v>-1.49</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
@@ -8746,7 +8746,7 @@
         <v>5.68</v>
       </c>
       <c r="D586">
-        <v>-1.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
@@ -8760,7 +8760,7 @@
         <v>5.58</v>
       </c>
       <c r="D587">
-        <v>-0.91</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
@@ -8774,7 +8774,7 @@
         <v>5.48</v>
       </c>
       <c r="D588">
-        <v>-0.62</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
@@ -8788,7 +8788,7 @@
         <v>5.36</v>
       </c>
       <c r="D589">
-        <v>-0.35</v>
+        <v>-2.2799999999999998</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
@@ -8802,7 +8802,7 @@
         <v>5.22</v>
       </c>
       <c r="D590">
-        <v>-0.09</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
@@ -8816,7 +8816,7 @@
         <v>5.08</v>
       </c>
       <c r="D591">
-        <v>0.17</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
@@ -8830,7 +8830,7 @@
         <v>4.96</v>
       </c>
       <c r="D592">
-        <v>0.43</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
@@ -8844,7 +8844,7 @@
         <v>4.84</v>
       </c>
       <c r="D593">
-        <v>0.69</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
@@ -8858,7 +8858,7 @@
         <v>4.74</v>
       </c>
       <c r="D594">
-        <v>0.95</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
@@ -8872,7 +8872,7 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="D595">
-        <v>1.2</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
@@ -8886,7 +8886,7 @@
         <v>4.55</v>
       </c>
       <c r="D596">
-        <v>1.46</v>
+        <v>-2.4700000000000002</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
@@ -8900,7 +8900,7 @@
         <v>4.45</v>
       </c>
       <c r="D597">
-        <v>1.72</v>
+        <v>-2.2400000000000002</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
@@ -8914,7 +8914,7 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="D598">
-        <v>1.98</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
@@ -8928,7 +8928,7 @@
         <v>4.24</v>
       </c>
       <c r="D599">
-        <v>2.2400000000000002</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
@@ -8942,7 +8942,7 @@
         <v>4.12</v>
       </c>
       <c r="D600">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
@@ -8956,7 +8956,7 @@
         <v>4</v>
       </c>
       <c r="D601">
-        <v>2.75</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
@@ -8970,7 +8970,7 @@
         <v>3.88</v>
       </c>
       <c r="D602">
-        <v>3.01</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
@@ -8984,7 +8984,7 @@
         <v>3.75</v>
       </c>
       <c r="D603">
-        <v>3.27</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
@@ -8998,7 +8998,7 @@
         <v>3.63</v>
       </c>
       <c r="D604">
-        <v>3.55</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
@@ -9012,7 +9012,7 @@
         <v>3.5</v>
       </c>
       <c r="D605">
-        <v>3.83</v>
+        <v>-0.28000000000000003</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
@@ -9026,7 +9026,7 @@
         <v>3.37</v>
       </c>
       <c r="D606">
-        <v>4.1100000000000003</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
@@ -9040,7 +9040,7 @@
         <v>3.23</v>
       </c>
       <c r="D607">
-        <v>4.3600000000000003</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
@@ -9054,7 +9054,7 @@
         <v>3.08</v>
       </c>
       <c r="D608">
-        <v>4.58</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
@@ -9068,7 +9068,7 @@
         <v>2.95</v>
       </c>
       <c r="D609">
-        <v>4.76</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
@@ -9082,7 +9082,7 @@
         <v>2.83</v>
       </c>
       <c r="D610">
-        <v>4.8899999999999997</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
@@ -9096,7 +9096,7 @@
         <v>2.71</v>
       </c>
       <c r="D611">
-        <v>4.96</v>
+        <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
@@ -9110,7 +9110,7 @@
         <v>2.6</v>
       </c>
       <c r="D612">
-        <v>4.99</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
@@ -9124,7 +9124,7 @@
         <v>2.5</v>
       </c>
       <c r="D613">
-        <v>4.97</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
@@ -9138,7 +9138,7 @@
         <v>2.38</v>
       </c>
       <c r="D614">
-        <v>4.91</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
@@ -9152,7 +9152,7 @@
         <v>2.25</v>
       </c>
       <c r="D615">
-        <v>4.82</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
@@ -9166,7 +9166,7 @@
         <v>2.12</v>
       </c>
       <c r="D616">
-        <v>4.71</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
@@ -9180,7 +9180,7 @@
         <v>1.98</v>
       </c>
       <c r="D617">
-        <v>4.6100000000000003</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
@@ -9194,7 +9194,7 @@
         <v>1.86</v>
       </c>
       <c r="D618">
-        <v>4.5199999999999996</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
@@ -9208,7 +9208,7 @@
         <v>1.74</v>
       </c>
       <c r="D619">
-        <v>4.4400000000000004</v>
+        <v>-0.28999999999999998</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
@@ -9222,7 +9222,7 @@
         <v>1.62</v>
       </c>
       <c r="D620">
-        <v>4.3600000000000003</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
@@ -9236,7 +9236,7 @@
         <v>1.52</v>
       </c>
       <c r="D621">
-        <v>4.28</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
@@ -9250,7 +9250,7 @@
         <v>1.43</v>
       </c>
       <c r="D622">
-        <v>4.2</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
@@ -9264,7 +9264,7 @@
         <v>1.33</v>
       </c>
       <c r="D623">
-        <v>4.12</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
@@ -9278,7 +9278,7 @@
         <v>1.22</v>
       </c>
       <c r="D624">
-        <v>4.04</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
@@ -9292,7 +9292,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="D625">
-        <v>3.96</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
@@ -9306,7 +9306,7 @@
         <v>0.94</v>
       </c>
       <c r="D626">
-        <v>3.89</v>
+        <v>-1.1200000000000001</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
@@ -9320,7 +9320,7 @@
         <v>0.77</v>
       </c>
       <c r="D627">
-        <v>3.82</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
@@ -9334,7 +9334,7 @@
         <v>0.67</v>
       </c>
       <c r="D628">
-        <v>3.76</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
@@ -9348,7 +9348,7 @@
         <v>0.54</v>
       </c>
       <c r="D629">
-        <v>3.69</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
@@ -9362,7 +9362,7 @@
         <v>0.39</v>
       </c>
       <c r="D630">
-        <v>3.63</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
@@ -9376,7 +9376,7 @@
         <v>0.22</v>
       </c>
       <c r="D631">
-        <v>3.57</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
@@ -9390,7 +9390,7 @@
         <v>0.03</v>
       </c>
       <c r="D632">
-        <v>3.51</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
@@ -9404,7 +9404,7 @@
         <v>-0.16</v>
       </c>
       <c r="D633">
-        <v>3.45</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
@@ -9418,7 +9418,7 @@
         <v>-0.36</v>
       </c>
       <c r="D634">
-        <v>3.39</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
@@ -9432,7 +9432,7 @@
         <v>-0.54</v>
       </c>
       <c r="D635">
-        <v>3.32</v>
+        <v>-2.2000000000000002</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
@@ -9446,7 +9446,7 @@
         <v>-0.73</v>
       </c>
       <c r="D636">
-        <v>3.25</v>
+        <v>-2.3199999999999998</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
@@ -9460,7 +9460,7 @@
         <v>-0.92</v>
       </c>
       <c r="D637">
-        <v>3.18</v>
+        <v>-2.4500000000000002</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
@@ -9474,7 +9474,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="D638">
-        <v>3.11</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
@@ -9488,7 +9488,7 @@
         <v>-1.31</v>
       </c>
       <c r="D639">
-        <v>3.03</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
@@ -9502,7 +9502,7 @@
         <v>-1.51</v>
       </c>
       <c r="D640">
-        <v>2.95</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
@@ -9516,7 +9516,7 @@
         <v>-1.71</v>
       </c>
       <c r="D641">
-        <v>2.88</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
@@ -9530,7 +9530,7 @@
         <v>-1.91</v>
       </c>
       <c r="D642">
-        <v>2.8</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
@@ -9544,7 +9544,7 @@
         <v>-2.12</v>
       </c>
       <c r="D643">
-        <v>2.71</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
@@ -9558,7 +9558,7 @@
         <v>-2.33</v>
       </c>
       <c r="D644">
-        <v>2.63</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
@@ -9572,7 +9572,7 @@
         <v>-2.54</v>
       </c>
       <c r="D645">
-        <v>2.54</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
@@ -9586,7 +9586,7 @@
         <v>-2.75</v>
       </c>
       <c r="D646">
-        <v>2.46</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
@@ -9600,7 +9600,7 @@
         <v>-2.96</v>
       </c>
       <c r="D647">
-        <v>2.37</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
@@ -9614,7 +9614,7 @@
         <v>-3.18</v>
       </c>
       <c r="D648">
-        <v>2.2799999999999998</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
@@ -9628,7 +9628,7 @@
         <v>-3.4</v>
       </c>
       <c r="D649">
-        <v>2.1800000000000002</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
@@ -9642,7 +9642,7 @@
         <v>-3.62</v>
       </c>
       <c r="D650">
-        <v>2.09</v>
+        <v>-4.1399999999999997</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
@@ -9656,7 +9656,7 @@
         <v>-3.85</v>
       </c>
       <c r="D651">
-        <v>1.99</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
@@ -9670,7 +9670,7 @@
         <v>-4.07</v>
       </c>
       <c r="D652">
-        <v>1.89</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
@@ -9684,7 +9684,7 @@
         <v>-4.3</v>
       </c>
       <c r="D653">
-        <v>1.79</v>
+        <v>-4.5599999999999996</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
@@ -9698,7 +9698,7 @@
         <v>-4.53</v>
       </c>
       <c r="D654">
-        <v>1.69</v>
+        <v>-4.6900000000000004</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
@@ -9712,7 +9712,7 @@
         <v>-4.7699999999999996</v>
       </c>
       <c r="D655">
-        <v>1.58</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
@@ -9726,7 +9726,7 @@
         <v>-5</v>
       </c>
       <c r="D656">
-        <v>1.48</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
@@ -9740,7 +9740,7 @@
         <v>-5.24</v>
       </c>
       <c r="D657">
-        <v>1.37</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
@@ -9754,7 +9754,7 @@
         <v>-5.48</v>
       </c>
       <c r="D658">
-        <v>1.26</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
@@ -9768,7 +9768,7 @@
         <v>-5.73</v>
       </c>
       <c r="D659">
-        <v>1.1499999999999999</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
@@ -9782,7 +9782,7 @@
         <v>-5.97</v>
       </c>
       <c r="D660">
-        <v>1.03</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
@@ -9796,7 +9796,7 @@
         <v>-6.22</v>
       </c>
       <c r="D661">
-        <v>0.92</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
@@ -9810,7 +9810,7 @@
         <v>-6.47</v>
       </c>
       <c r="D662">
-        <v>0.8</v>
+        <v>-5.83</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
@@ -9824,7 +9824,7 @@
         <v>-6.72</v>
       </c>
       <c r="D663">
-        <v>0.68</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.3">
@@ -9838,7 +9838,7 @@
         <v>-6.98</v>
       </c>
       <c r="D664">
-        <v>0.56000000000000005</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
@@ -9852,7 +9852,7 @@
         <v>-7.23</v>
       </c>
       <c r="D665">
-        <v>0.43</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
@@ -9866,7 +9866,7 @@
         <v>-7.49</v>
       </c>
       <c r="D666">
-        <v>0.31</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
@@ -9880,7 +9880,7 @@
         <v>-7.76</v>
       </c>
       <c r="D667">
-        <v>0.18</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
@@ -9894,7 +9894,7 @@
         <v>-8.02</v>
       </c>
       <c r="D668">
-        <v>0.05</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
@@ -9908,7 +9908,7 @@
         <v>-8.2899999999999991</v>
       </c>
       <c r="D669">
-        <v>-0.08</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
@@ -9922,7 +9922,7 @@
         <v>-8.56</v>
       </c>
       <c r="D670">
-        <v>-0.21</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
@@ -9936,7 +9936,7 @@
         <v>-8.83</v>
       </c>
       <c r="D671">
-        <v>-0.34</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.3">
@@ -9950,7 +9950,7 @@
         <v>-9.1</v>
       </c>
       <c r="D672">
-        <v>-0.48</v>
+        <v>-7.33</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.3">
@@ -9964,7 +9964,7 @@
         <v>-9.3800000000000008</v>
       </c>
       <c r="D673">
-        <v>-0.62</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.3">
@@ -9978,7 +9978,7 @@
         <v>-9.66</v>
       </c>
       <c r="D674">
-        <v>-0.76</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
@@ -9992,7 +9992,7 @@
         <v>-9.94</v>
       </c>
       <c r="D675">
-        <v>-0.9</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.3">
@@ -10006,7 +10006,7 @@
         <v>-10.220000000000001</v>
       </c>
       <c r="D676">
-        <v>-1.04</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.3">
@@ -10020,7 +10020,7 @@
         <v>-10.51</v>
       </c>
       <c r="D677">
-        <v>-1.19</v>
+        <v>-8.11</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
@@ -10034,7 +10034,7 @@
         <v>-10.8</v>
       </c>
       <c r="D678">
-        <v>-1.34</v>
+        <v>-8.27</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
@@ -10048,7 +10048,7 @@
         <v>-11.09</v>
       </c>
       <c r="D679">
-        <v>-1.49</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.3">
@@ -10062,7 +10062,7 @@
         <v>-11.38</v>
       </c>
       <c r="D680">
-        <v>-1.64</v>
+        <v>-8.59</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.3">
@@ -10076,7 +10076,7 @@
         <v>-11.68</v>
       </c>
       <c r="D681">
-        <v>-1.79</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
@@ -10090,7 +10090,7 @@
         <v>-11.97</v>
       </c>
       <c r="D682">
-        <v>-1.95</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
@@ -10104,7 +10104,7 @@
         <v>-12.27</v>
       </c>
       <c r="D683">
-        <v>-2.1</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.3">
@@ -10118,7 +10118,7 @@
         <v>-12.58</v>
       </c>
       <c r="D684">
-        <v>-2.2599999999999998</v>
+        <v>-9.24</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.3">
@@ -10132,7 +10132,7 @@
         <v>-12.88</v>
       </c>
       <c r="D685">
-        <v>-2.42</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.3">
@@ -10146,7 +10146,7 @@
         <v>-13.19</v>
       </c>
       <c r="D686">
-        <v>-2.58</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
@@ -10160,7 +10160,7 @@
         <v>-13.5</v>
       </c>
       <c r="D687">
-        <v>-2.75</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
@@ -10174,7 +10174,7 @@
         <v>-13.81</v>
       </c>
       <c r="D688">
-        <v>-2.91</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
@@ -10188,7 +10188,7 @@
         <v>-14.12</v>
       </c>
       <c r="D689">
-        <v>-3.08</v>
+        <v>-10.07</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
@@ -10202,7 +10202,7 @@
         <v>-14.44</v>
       </c>
       <c r="D690">
-        <v>-3.25</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
@@ -10216,7 +10216,7 @@
         <v>-14.76</v>
       </c>
       <c r="D691">
-        <v>-3.42</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
@@ -10230,7 +10230,7 @@
         <v>-15.08</v>
       </c>
       <c r="D692">
-        <v>-3.6</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
@@ -10244,7 +10244,7 @@
         <v>-15.4</v>
       </c>
       <c r="D693">
-        <v>-3.77</v>
+        <v>-10.74</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.3">
@@ -10258,7 +10258,7 @@
         <v>-15.73</v>
       </c>
       <c r="D694">
-        <v>-3.95</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.3">
@@ -10272,7 +10272,7 @@
         <v>-16.059999999999999</v>
       </c>
       <c r="D695">
-        <v>-4.13</v>
+        <v>-11.09</v>
       </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.3">
@@ -10286,7 +10286,7 @@
         <v>-16.39</v>
       </c>
       <c r="D696">
-        <v>-4.3099999999999996</v>
+        <v>-11.26</v>
       </c>
     </row>
   </sheetData>

--- a/my_results/Pre-Amp Calculator.xlsx
+++ b/my_results/Pre-Amp Calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\User Files\Documents\GitHub\autoeq-workspace\my_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A49A1DD-5FE3-4428-9C10-7BDCC38E4D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4DE15-0779-4BFE-8EC5-D949F909ED2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="5352" windowWidth="17244" windowHeight="12048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17244" windowHeight="12048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Impulse" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
         <v>6.67</v>
       </c>
       <c r="C2">
-        <v>-3.8</v>
+        <v>-4.53</v>
       </c>
       <c r="D2">
         <v>4.55</v>
@@ -529,7 +529,7 @@
         <v>6.67</v>
       </c>
       <c r="C3">
-        <v>-3.74</v>
+        <v>-4.4400000000000004</v>
       </c>
       <c r="D3">
         <v>4.55</v>
@@ -539,26 +539,26 @@
       </c>
       <c r="G3">
         <f>SUM(C2:C696)</f>
-        <v>654.83000000000004</v>
+        <v>489.64999999999941</v>
       </c>
       <c r="H3">
         <f>AVERAGE(C2:C696)</f>
-        <v>0.94220143884892094</v>
+        <v>0.70453237410071856</v>
       </c>
       <c r="I3">
         <f>MIN($C$2:$C$696)</f>
-        <v>-16.39</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="J3">
         <f>MAX($C$2:$C$696)</f>
-        <v>9.9600000000000009</v>
+        <v>9.77</v>
       </c>
       <c r="K3" s="2">
         <v>0</v>
       </c>
       <c r="L3">
         <f>J3-K3-H3</f>
-        <v>9.0177985611510802</v>
+        <v>9.0654676258992808</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -569,7 +569,7 @@
         <v>6.66</v>
       </c>
       <c r="C4">
-        <v>-3.67</v>
+        <v>-4.3600000000000003</v>
       </c>
       <c r="D4">
         <v>4.55</v>
@@ -609,7 +609,7 @@
         <v>6.66</v>
       </c>
       <c r="C5">
-        <v>-3.61</v>
+        <v>-4.2699999999999996</v>
       </c>
       <c r="D5">
         <v>4.55</v>
@@ -623,7 +623,7 @@
         <v>6.66</v>
       </c>
       <c r="C6">
-        <v>-3.54</v>
+        <v>-4.1900000000000004</v>
       </c>
       <c r="D6">
         <v>4.55</v>
@@ -637,7 +637,7 @@
         <v>6.66</v>
       </c>
       <c r="C7">
-        <v>-3.47</v>
+        <v>-4.1100000000000003</v>
       </c>
       <c r="D7">
         <v>4.55</v>
@@ -651,7 +651,7 @@
         <v>6.65</v>
       </c>
       <c r="C8">
-        <v>-3.4</v>
+        <v>-4.03</v>
       </c>
       <c r="D8">
         <v>4.55</v>
@@ -665,7 +665,7 @@
         <v>6.65</v>
       </c>
       <c r="C9">
-        <v>-3.34</v>
+        <v>-3.95</v>
       </c>
       <c r="D9">
         <v>4.55</v>
@@ -679,7 +679,7 @@
         <v>6.65</v>
       </c>
       <c r="C10">
-        <v>-3.27</v>
+        <v>-3.88</v>
       </c>
       <c r="D10">
         <v>4.55</v>
@@ -693,7 +693,7 @@
         <v>6.66</v>
       </c>
       <c r="C11">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
       <c r="D11">
         <v>4.55</v>
@@ -707,7 +707,7 @@
         <v>6.66</v>
       </c>
       <c r="C12">
-        <v>-3.14</v>
+        <v>-3.73</v>
       </c>
       <c r="D12">
         <v>4.55</v>
@@ -721,7 +721,7 @@
         <v>6.66</v>
       </c>
       <c r="C13">
-        <v>-3.08</v>
+        <v>-3.66</v>
       </c>
       <c r="D13">
         <v>4.5599999999999996</v>
@@ -735,7 +735,7 @@
         <v>6.65</v>
       </c>
       <c r="C14">
-        <v>-3.01</v>
+        <v>-3.59</v>
       </c>
       <c r="D14">
         <v>4.55</v>
@@ -749,7 +749,7 @@
         <v>6.65</v>
       </c>
       <c r="C15">
-        <v>-2.95</v>
+        <v>-3.52</v>
       </c>
       <c r="D15">
         <v>4.55</v>
@@ -763,7 +763,7 @@
         <v>6.65</v>
       </c>
       <c r="C16">
-        <v>-2.88</v>
+        <v>-3.46</v>
       </c>
       <c r="D16">
         <v>4.5599999999999996</v>
@@ -777,7 +777,7 @@
         <v>6.65</v>
       </c>
       <c r="C17">
-        <v>-2.82</v>
+        <v>-3.39</v>
       </c>
       <c r="D17">
         <v>4.5599999999999996</v>
@@ -791,7 +791,7 @@
         <v>6.66</v>
       </c>
       <c r="C18">
-        <v>-2.76</v>
+        <v>-3.33</v>
       </c>
       <c r="D18">
         <v>4.57</v>
@@ -805,7 +805,7 @@
         <v>6.65</v>
       </c>
       <c r="C19">
-        <v>-2.69</v>
+        <v>-3.27</v>
       </c>
       <c r="D19">
         <v>4.57</v>
@@ -819,7 +819,7 @@
         <v>6.65</v>
       </c>
       <c r="C20">
-        <v>-2.63</v>
+        <v>-3.21</v>
       </c>
       <c r="D20">
         <v>4.57</v>
@@ -833,7 +833,7 @@
         <v>6.64</v>
       </c>
       <c r="C21">
-        <v>-2.57</v>
+        <v>-3.15</v>
       </c>
       <c r="D21">
         <v>4.5599999999999996</v>
@@ -847,7 +847,7 @@
         <v>6.64</v>
       </c>
       <c r="C22">
-        <v>-2.5099999999999998</v>
+        <v>-3.1</v>
       </c>
       <c r="D22">
         <v>4.5599999999999996</v>
@@ -861,7 +861,7 @@
         <v>6.64</v>
       </c>
       <c r="C23">
-        <v>-2.4500000000000002</v>
+        <v>-3.04</v>
       </c>
       <c r="D23">
         <v>4.5599999999999996</v>
@@ -875,7 +875,7 @@
         <v>6.64</v>
       </c>
       <c r="C24">
-        <v>-2.39</v>
+        <v>-2.99</v>
       </c>
       <c r="D24">
         <v>4.57</v>
@@ -889,7 +889,7 @@
         <v>6.63</v>
       </c>
       <c r="C25">
-        <v>-2.3199999999999998</v>
+        <v>-2.93</v>
       </c>
       <c r="D25">
         <v>4.57</v>
@@ -903,7 +903,7 @@
         <v>6.63</v>
       </c>
       <c r="C26">
-        <v>-2.2599999999999998</v>
+        <v>-2.88</v>
       </c>
       <c r="D26">
         <v>4.5599999999999996</v>
@@ -917,7 +917,7 @@
         <v>6.62</v>
       </c>
       <c r="C27">
-        <v>-2.2000000000000002</v>
+        <v>-2.82</v>
       </c>
       <c r="D27">
         <v>4.5599999999999996</v>
@@ -931,7 +931,7 @@
         <v>6.61</v>
       </c>
       <c r="C28">
-        <v>-2.13</v>
+        <v>-2.76</v>
       </c>
       <c r="D28">
         <v>4.55</v>
@@ -945,7 +945,7 @@
         <v>6.61</v>
       </c>
       <c r="C29">
-        <v>-2.0699999999999998</v>
+        <v>-2.7</v>
       </c>
       <c r="D29">
         <v>4.5599999999999996</v>
@@ -959,7 +959,7 @@
         <v>6.61</v>
       </c>
       <c r="C30">
-        <v>-2</v>
+        <v>-2.65</v>
       </c>
       <c r="D30">
         <v>4.5599999999999996</v>
@@ -973,7 +973,7 @@
         <v>6.6</v>
       </c>
       <c r="C31">
-        <v>-1.92</v>
+        <v>-2.59</v>
       </c>
       <c r="D31">
         <v>4.5599999999999996</v>
@@ -987,7 +987,7 @@
         <v>6.6</v>
       </c>
       <c r="C32">
-        <v>-1.85</v>
+        <v>-2.5299999999999998</v>
       </c>
       <c r="D32">
         <v>4.5599999999999996</v>
@@ -1001,7 +1001,7 @@
         <v>6.6</v>
       </c>
       <c r="C33">
-        <v>-1.78</v>
+        <v>-2.4700000000000002</v>
       </c>
       <c r="D33">
         <v>4.5599999999999996</v>
@@ -1015,7 +1015,7 @@
         <v>6.59</v>
       </c>
       <c r="C34">
-        <v>-1.71</v>
+        <v>-2.42</v>
       </c>
       <c r="D34">
         <v>4.5599999999999996</v>
@@ -1029,7 +1029,7 @@
         <v>6.59</v>
       </c>
       <c r="C35">
-        <v>-1.63</v>
+        <v>-2.36</v>
       </c>
       <c r="D35">
         <v>4.5599999999999996</v>
@@ -1043,7 +1043,7 @@
         <v>6.58</v>
       </c>
       <c r="C36">
-        <v>-1.56</v>
+        <v>-2.29</v>
       </c>
       <c r="D36">
         <v>4.5599999999999996</v>
@@ -1057,7 +1057,7 @@
         <v>6.58</v>
       </c>
       <c r="C37">
-        <v>-1.48</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="D37">
         <v>4.5599999999999996</v>
@@ -1071,7 +1071,7 @@
         <v>6.57</v>
       </c>
       <c r="C38">
-        <v>-1.39</v>
+        <v>-2.15</v>
       </c>
       <c r="D38">
         <v>4.5599999999999996</v>
@@ -1085,7 +1085,7 @@
         <v>6.57</v>
       </c>
       <c r="C39">
-        <v>-1.31</v>
+        <v>-2.08</v>
       </c>
       <c r="D39">
         <v>4.5599999999999996</v>
@@ -1099,7 +1099,7 @@
         <v>6.56</v>
       </c>
       <c r="C40">
-        <v>-1.21</v>
+        <v>-2</v>
       </c>
       <c r="D40">
         <v>4.5599999999999996</v>
@@ -1113,7 +1113,7 @@
         <v>6.55</v>
       </c>
       <c r="C41">
-        <v>-1.1100000000000001</v>
+        <v>-1.92</v>
       </c>
       <c r="D41">
         <v>4.5599999999999996</v>
@@ -1127,7 +1127,7 @@
         <v>6.54</v>
       </c>
       <c r="C42">
-        <v>-1.02</v>
+        <v>-1.83</v>
       </c>
       <c r="D42">
         <v>4.55</v>
@@ -1141,7 +1141,7 @@
         <v>6.53</v>
       </c>
       <c r="C43">
-        <v>-0.93</v>
+        <v>-1.74</v>
       </c>
       <c r="D43">
         <v>4.5599999999999996</v>
@@ -1155,7 +1155,7 @@
         <v>6.53</v>
       </c>
       <c r="C44">
-        <v>-0.85</v>
+        <v>-1.65</v>
       </c>
       <c r="D44">
         <v>4.5599999999999996</v>
@@ -1169,7 +1169,7 @@
         <v>6.53</v>
       </c>
       <c r="C45">
-        <v>-0.78</v>
+        <v>-1.54</v>
       </c>
       <c r="D45">
         <v>4.57</v>
@@ -1183,7 +1183,7 @@
         <v>6.52</v>
       </c>
       <c r="C46">
-        <v>-0.73</v>
+        <v>-1.42</v>
       </c>
       <c r="D46">
         <v>4.57</v>
@@ -1197,7 +1197,7 @@
         <v>6.52</v>
       </c>
       <c r="C47">
-        <v>-0.69</v>
+        <v>-1.31</v>
       </c>
       <c r="D47">
         <v>4.57</v>
@@ -1211,7 +1211,7 @@
         <v>6.51</v>
       </c>
       <c r="C48">
-        <v>-0.66</v>
+        <v>-1.2</v>
       </c>
       <c r="D48">
         <v>4.57</v>
@@ -1225,7 +1225,7 @@
         <v>6.5</v>
       </c>
       <c r="C49">
-        <v>-0.65</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="D49">
         <v>4.5599999999999996</v>
@@ -1239,7 +1239,7 @@
         <v>6.49</v>
       </c>
       <c r="C50">
-        <v>-0.65</v>
+        <v>-1.02</v>
       </c>
       <c r="D50">
         <v>4.5599999999999996</v>
@@ -1253,7 +1253,7 @@
         <v>6.47</v>
       </c>
       <c r="C51">
-        <v>-0.66</v>
+        <v>-0.96</v>
       </c>
       <c r="D51">
         <v>4.5599999999999996</v>
@@ -1267,7 +1267,7 @@
         <v>6.46</v>
       </c>
       <c r="C52">
-        <v>-0.67</v>
+        <v>-0.91</v>
       </c>
       <c r="D52">
         <v>4.5599999999999996</v>
@@ -1281,7 +1281,7 @@
         <v>6.45</v>
       </c>
       <c r="C53">
-        <v>-0.68</v>
+        <v>-0.88</v>
       </c>
       <c r="D53">
         <v>4.55</v>
@@ -1295,7 +1295,7 @@
         <v>6.44</v>
       </c>
       <c r="C54">
-        <v>-0.69</v>
+        <v>-0.87</v>
       </c>
       <c r="D54">
         <v>4.55</v>
@@ -1309,7 +1309,7 @@
         <v>6.43</v>
       </c>
       <c r="C55">
-        <v>-0.7</v>
+        <v>-0.88</v>
       </c>
       <c r="D55">
         <v>4.55</v>
@@ -1323,7 +1323,7 @@
         <v>6.41</v>
       </c>
       <c r="C56">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="D56">
         <v>4.55</v>
@@ -1337,7 +1337,7 @@
         <v>6.4</v>
       </c>
       <c r="C57">
-        <v>-0.71</v>
+        <v>-0.92</v>
       </c>
       <c r="D57">
         <v>4.54</v>
@@ -1351,7 +1351,7 @@
         <v>6.39</v>
       </c>
       <c r="C58">
-        <v>-0.72</v>
+        <v>-0.94</v>
       </c>
       <c r="D58">
         <v>4.54</v>
@@ -1365,7 +1365,7 @@
         <v>6.38</v>
       </c>
       <c r="C59">
-        <v>-0.72</v>
+        <v>-0.94</v>
       </c>
       <c r="D59">
         <v>4.55</v>
@@ -1379,7 +1379,7 @@
         <v>6.37</v>
       </c>
       <c r="C60">
-        <v>-0.72</v>
+        <v>-0.94</v>
       </c>
       <c r="D60">
         <v>4.54</v>
@@ -1393,7 +1393,7 @@
         <v>6.35</v>
       </c>
       <c r="C61">
-        <v>-0.73</v>
+        <v>-0.93</v>
       </c>
       <c r="D61">
         <v>4.54</v>
@@ -1407,7 +1407,7 @@
         <v>6.34</v>
       </c>
       <c r="C62">
-        <v>-0.74</v>
+        <v>-0.93</v>
       </c>
       <c r="D62">
         <v>4.54</v>
@@ -1421,7 +1421,7 @@
         <v>6.32</v>
       </c>
       <c r="C63">
-        <v>-0.75</v>
+        <v>-0.94</v>
       </c>
       <c r="D63">
         <v>4.53</v>
@@ -1435,7 +1435,7 @@
         <v>6.3</v>
       </c>
       <c r="C64">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D64">
         <v>4.53</v>
@@ -1449,7 +1449,7 @@
         <v>6.28</v>
       </c>
       <c r="C65">
-        <v>-0.76</v>
+        <v>-0.98</v>
       </c>
       <c r="D65">
         <v>4.5199999999999996</v>
@@ -1463,7 +1463,7 @@
         <v>6.26</v>
       </c>
       <c r="C66">
-        <v>-0.77</v>
+        <v>-0.99</v>
       </c>
       <c r="D66">
         <v>4.5199999999999996</v>
@@ -1477,7 +1477,7 @@
         <v>6.24</v>
       </c>
       <c r="C67">
-        <v>-0.77</v>
+        <v>-0.99</v>
       </c>
       <c r="D67">
         <v>4.51</v>
@@ -1491,7 +1491,7 @@
         <v>6.22</v>
       </c>
       <c r="C68">
-        <v>-0.78</v>
+        <v>-0.99</v>
       </c>
       <c r="D68">
         <v>4.51</v>
@@ -1505,7 +1505,7 @@
         <v>6.2</v>
       </c>
       <c r="C69">
-        <v>-0.79</v>
+        <v>-0.99</v>
       </c>
       <c r="D69">
         <v>4.51</v>
@@ -1519,7 +1519,7 @@
         <v>6.18</v>
       </c>
       <c r="C70">
-        <v>-0.79</v>
+        <v>-1</v>
       </c>
       <c r="D70">
         <v>4.5</v>
@@ -1533,7 +1533,7 @@
         <v>6.16</v>
       </c>
       <c r="C71">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="D71">
         <v>4.5</v>
@@ -1547,7 +1547,7 @@
         <v>6.13</v>
       </c>
       <c r="C72">
-        <v>-0.81</v>
+        <v>-1.01</v>
       </c>
       <c r="D72">
         <v>4.49</v>
@@ -1561,7 +1561,7 @@
         <v>6.11</v>
       </c>
       <c r="C73">
-        <v>-0.82</v>
+        <v>-1.02</v>
       </c>
       <c r="D73">
         <v>4.49</v>
@@ -1575,7 +1575,7 @@
         <v>6.08</v>
       </c>
       <c r="C74">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="D74">
         <v>4.4800000000000004</v>
@@ -1589,7 +1589,7 @@
         <v>6.06</v>
       </c>
       <c r="C75">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="D75">
         <v>4.4800000000000004</v>
@@ -1603,7 +1603,7 @@
         <v>6.03</v>
       </c>
       <c r="C76">
-        <v>-0.82</v>
+        <v>-1.04</v>
       </c>
       <c r="D76">
         <v>4.47</v>
@@ -1617,7 +1617,7 @@
         <v>6</v>
       </c>
       <c r="C77">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
       <c r="D77">
         <v>4.46</v>
@@ -1631,7 +1631,7 @@
         <v>5.97</v>
       </c>
       <c r="C78">
-        <v>-0.84</v>
+        <v>-1.05</v>
       </c>
       <c r="D78">
         <v>4.45</v>
@@ -1645,7 +1645,7 @@
         <v>5.94</v>
       </c>
       <c r="C79">
-        <v>-0.85</v>
+        <v>-1.06</v>
       </c>
       <c r="D79">
         <v>4.45</v>
@@ -1659,7 +1659,7 @@
         <v>5.91</v>
       </c>
       <c r="C80">
-        <v>-0.86</v>
+        <v>-1.06</v>
       </c>
       <c r="D80">
         <v>4.4400000000000004</v>
@@ -1673,7 +1673,7 @@
         <v>5.88</v>
       </c>
       <c r="C81">
-        <v>-0.86</v>
+        <v>-1.07</v>
       </c>
       <c r="D81">
         <v>4.43</v>
@@ -1687,7 +1687,7 @@
         <v>5.85</v>
       </c>
       <c r="C82">
-        <v>-0.87</v>
+        <v>-1.08</v>
       </c>
       <c r="D82">
         <v>4.42</v>
@@ -1701,7 +1701,7 @@
         <v>5.82</v>
       </c>
       <c r="C83">
-        <v>-0.88</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="D83">
         <v>4.41</v>
@@ -1715,7 +1715,7 @@
         <v>5.78</v>
       </c>
       <c r="C84">
-        <v>-0.89</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D84">
         <v>4.4000000000000004</v>
@@ -1729,7 +1729,7 @@
         <v>5.75</v>
       </c>
       <c r="C85">
-        <v>-0.9</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="D85">
         <v>4.3899999999999997</v>
@@ -1743,7 +1743,7 @@
         <v>5.71</v>
       </c>
       <c r="C86">
-        <v>-0.91</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="D86">
         <v>4.38</v>
@@ -1757,7 +1757,7 @@
         <v>5.67</v>
       </c>
       <c r="C87">
-        <v>-0.92</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="D87">
         <v>4.37</v>
@@ -1771,7 +1771,7 @@
         <v>5.63</v>
       </c>
       <c r="C88">
-        <v>-0.93</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="D88">
         <v>4.3600000000000003</v>
@@ -1785,7 +1785,7 @@
         <v>5.6</v>
       </c>
       <c r="C89">
-        <v>-0.94</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="D89">
         <v>4.3499999999999996</v>
@@ -1799,7 +1799,7 @@
         <v>5.56</v>
       </c>
       <c r="C90">
-        <v>-0.95</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="D90">
         <v>4.34</v>
@@ -1813,7 +1813,7 @@
         <v>5.52</v>
       </c>
       <c r="C91">
-        <v>-0.96</v>
+        <v>-1.17</v>
       </c>
       <c r="D91">
         <v>4.33</v>
@@ -1827,7 +1827,7 @@
         <v>5.48</v>
       </c>
       <c r="C92">
-        <v>-0.97</v>
+        <v>-1.19</v>
       </c>
       <c r="D92">
         <v>4.32</v>
@@ -1841,7 +1841,7 @@
         <v>5.44</v>
       </c>
       <c r="C93">
-        <v>-0.99</v>
+        <v>-1.2</v>
       </c>
       <c r="D93">
         <v>4.3099999999999996</v>
@@ -1855,7 +1855,7 @@
         <v>5.39</v>
       </c>
       <c r="C94">
-        <v>-1</v>
+        <v>-1.21</v>
       </c>
       <c r="D94">
         <v>4.3</v>
@@ -1869,7 +1869,7 @@
         <v>5.34</v>
       </c>
       <c r="C95">
-        <v>-1.02</v>
+        <v>-1.23</v>
       </c>
       <c r="D95">
         <v>4.28</v>
@@ -1883,7 +1883,7 @@
         <v>5.29</v>
       </c>
       <c r="C96">
-        <v>-1.03</v>
+        <v>-1.24</v>
       </c>
       <c r="D96">
         <v>4.26</v>
@@ -1897,7 +1897,7 @@
         <v>5.24</v>
       </c>
       <c r="C97">
-        <v>-1.04</v>
+        <v>-1.25</v>
       </c>
       <c r="D97">
         <v>4.25</v>
@@ -1911,7 +1911,7 @@
         <v>5.19</v>
       </c>
       <c r="C98">
-        <v>-1.05</v>
+        <v>-1.26</v>
       </c>
       <c r="D98">
         <v>4.2300000000000004</v>
@@ -1925,7 +1925,7 @@
         <v>5.14</v>
       </c>
       <c r="C99">
-        <v>-1.06</v>
+        <v>-1.27</v>
       </c>
       <c r="D99">
         <v>4.22</v>
@@ -1939,7 +1939,7 @@
         <v>5.09</v>
       </c>
       <c r="C100">
-        <v>-1.07</v>
+        <v>-1.28</v>
       </c>
       <c r="D100">
         <v>4.2</v>
@@ -1953,7 +1953,7 @@
         <v>5.04</v>
       </c>
       <c r="C101">
-        <v>-1.08</v>
+        <v>-1.29</v>
       </c>
       <c r="D101">
         <v>4.18</v>
@@ -1967,7 +1967,7 @@
         <v>4.99</v>
       </c>
       <c r="C102">
-        <v>-1.0900000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="D102">
         <v>4.17</v>
@@ -1981,7 +1981,7 @@
         <v>4.93</v>
       </c>
       <c r="C103">
-        <v>-1.1000000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="D103">
         <v>4.1500000000000004</v>
@@ -1995,7 +1995,7 @@
         <v>4.87</v>
       </c>
       <c r="C104">
-        <v>-1.1100000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="D104">
         <v>4.13</v>
@@ -2009,7 +2009,7 @@
         <v>4.8099999999999996</v>
       </c>
       <c r="C105">
-        <v>-1.1100000000000001</v>
+        <v>-1.32</v>
       </c>
       <c r="D105">
         <v>4.1100000000000003</v>
@@ -2023,7 +2023,7 @@
         <v>4.76</v>
       </c>
       <c r="C106">
-        <v>-1.1200000000000001</v>
+        <v>-1.33</v>
       </c>
       <c r="D106">
         <v>4.09</v>
@@ -2037,7 +2037,7 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="C107">
-        <v>-1.1299999999999999</v>
+        <v>-1.33</v>
       </c>
       <c r="D107">
         <v>4.07</v>
@@ -2051,7 +2051,7 @@
         <v>4.63</v>
       </c>
       <c r="C108">
-        <v>-1.1299999999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="D108">
         <v>4.05</v>
@@ -2065,7 +2065,7 @@
         <v>4.57</v>
       </c>
       <c r="C109">
-        <v>-1.1299999999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="D109">
         <v>4.0199999999999996</v>
@@ -2079,7 +2079,7 @@
         <v>4.5</v>
       </c>
       <c r="C110">
-        <v>-1.1399999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -2093,7 +2093,7 @@
         <v>4.43</v>
       </c>
       <c r="C111">
-        <v>-1.1399999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="D111">
         <v>3.97</v>
@@ -2107,7 +2107,7 @@
         <v>4.3600000000000003</v>
       </c>
       <c r="C112">
-        <v>-1.1399999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="D112">
         <v>3.94</v>
@@ -2121,7 +2121,7 @@
         <v>4.29</v>
       </c>
       <c r="C113">
-        <v>-1.1499999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="D113">
         <v>3.91</v>
@@ -2135,7 +2135,7 @@
         <v>4.22</v>
       </c>
       <c r="C114">
-        <v>-1.1599999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="D114">
         <v>3.89</v>
@@ -2149,7 +2149,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="C115">
-        <v>-1.1599999999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="D115">
         <v>3.86</v>
@@ -2163,7 +2163,7 @@
         <v>4.08</v>
       </c>
       <c r="C116">
-        <v>-1.17</v>
+        <v>-1.38</v>
       </c>
       <c r="D116">
         <v>3.83</v>
@@ -2177,7 +2177,7 @@
         <v>4.01</v>
       </c>
       <c r="C117">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="D117">
         <v>3.8</v>
@@ -2191,7 +2191,7 @@
         <v>3.94</v>
       </c>
       <c r="C118">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="D118">
         <v>3.77</v>
@@ -2205,7 +2205,7 @@
         <v>3.86</v>
       </c>
       <c r="C119">
-        <v>-1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="D119">
         <v>3.73</v>
@@ -2219,7 +2219,7 @@
         <v>3.79</v>
       </c>
       <c r="C120">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="D120">
         <v>3.7</v>
@@ -2233,7 +2233,7 @@
         <v>3.71</v>
       </c>
       <c r="C121">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="D121">
         <v>3.67</v>
@@ -2247,7 +2247,7 @@
         <v>3.63</v>
       </c>
       <c r="C122">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="D122">
         <v>3.63</v>
@@ -2261,7 +2261,7 @@
         <v>3.55</v>
       </c>
       <c r="C123">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="D123">
         <v>3.6</v>
@@ -2275,7 +2275,7 @@
         <v>3.47</v>
       </c>
       <c r="C124">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="D124">
         <v>3.56</v>
@@ -2289,7 +2289,7 @@
         <v>3.39</v>
       </c>
       <c r="C125">
-        <v>-1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="D125">
         <v>3.52</v>
@@ -2303,7 +2303,7 @@
         <v>3.31</v>
       </c>
       <c r="C126">
-        <v>-1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="D126">
         <v>3.48</v>
@@ -2317,7 +2317,7 @@
         <v>3.23</v>
       </c>
       <c r="C127">
-        <v>-1.19</v>
+        <v>-1.39</v>
       </c>
       <c r="D127">
         <v>3.44</v>
@@ -2331,7 +2331,7 @@
         <v>3.14</v>
       </c>
       <c r="C128">
-        <v>-1.19</v>
+        <v>-1.39</v>
       </c>
       <c r="D128">
         <v>3.4</v>
@@ -2345,7 +2345,7 @@
         <v>3.06</v>
       </c>
       <c r="C129">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="D129">
         <v>3.36</v>
@@ -2359,7 +2359,7 @@
         <v>2.98</v>
       </c>
       <c r="C130">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="D130">
         <v>3.31</v>
@@ -2373,7 +2373,7 @@
         <v>2.89</v>
       </c>
       <c r="C131">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="D131">
         <v>3.27</v>
@@ -2387,7 +2387,7 @@
         <v>2.8</v>
       </c>
       <c r="C132">
-        <v>-1.17</v>
+        <v>-1.38</v>
       </c>
       <c r="D132">
         <v>3.22</v>
@@ -2401,7 +2401,7 @@
         <v>2.71</v>
       </c>
       <c r="C133">
-        <v>-1.17</v>
+        <v>-1.38</v>
       </c>
       <c r="D133">
         <v>3.17</v>
@@ -2415,7 +2415,7 @@
         <v>2.62</v>
       </c>
       <c r="C134">
-        <v>-1.17</v>
+        <v>-1.38</v>
       </c>
       <c r="D134">
         <v>3.12</v>
@@ -2429,7 +2429,7 @@
         <v>2.54</v>
       </c>
       <c r="C135">
-        <v>-1.1599999999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="D135">
         <v>3.07</v>
@@ -2443,7 +2443,7 @@
         <v>2.46</v>
       </c>
       <c r="C136">
-        <v>-1.1599999999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="D136">
         <v>3.02</v>
@@ -2457,7 +2457,7 @@
         <v>2.37</v>
       </c>
       <c r="C137">
-        <v>-1.1499999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="D137">
         <v>2.97</v>
@@ -2471,7 +2471,7 @@
         <v>2.2799999999999998</v>
       </c>
       <c r="C138">
-        <v>-1.1399999999999999</v>
+        <v>-1.35</v>
       </c>
       <c r="D138">
         <v>2.92</v>
@@ -2485,7 +2485,7 @@
         <v>2.19</v>
       </c>
       <c r="C139">
-        <v>-1.1299999999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="D139">
         <v>2.86</v>
@@ -2499,7 +2499,7 @@
         <v>2.1</v>
       </c>
       <c r="C140">
-        <v>-1.1200000000000001</v>
+        <v>-1.33</v>
       </c>
       <c r="D140">
         <v>2.81</v>
@@ -2513,7 +2513,7 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="C141">
-        <v>-1.1000000000000001</v>
+        <v>-1.32</v>
       </c>
       <c r="D141">
         <v>2.75</v>
@@ -2527,7 +2527,7 @@
         <v>1.92</v>
       </c>
       <c r="C142">
-        <v>-1.0900000000000001</v>
+        <v>-1.3</v>
       </c>
       <c r="D142">
         <v>2.69</v>
@@ -2541,7 +2541,7 @@
         <v>1.84</v>
       </c>
       <c r="C143">
-        <v>-1.08</v>
+        <v>-1.29</v>
       </c>
       <c r="D143">
         <v>2.64</v>
@@ -2555,7 +2555,7 @@
         <v>1.75</v>
       </c>
       <c r="C144">
-        <v>-1.08</v>
+        <v>-1.28</v>
       </c>
       <c r="D144">
         <v>2.58</v>
@@ -2569,7 +2569,7 @@
         <v>1.67</v>
       </c>
       <c r="C145">
-        <v>-1.07</v>
+        <v>-1.27</v>
       </c>
       <c r="D145">
         <v>2.52</v>
@@ -2583,7 +2583,7 @@
         <v>1.58</v>
       </c>
       <c r="C146">
-        <v>-1.06</v>
+        <v>-1.27</v>
       </c>
       <c r="D146">
         <v>2.46</v>
@@ -2597,7 +2597,7 @@
         <v>1.49</v>
       </c>
       <c r="C147">
-        <v>-1.04</v>
+        <v>-1.25</v>
       </c>
       <c r="D147">
         <v>2.4</v>
@@ -2611,7 +2611,7 @@
         <v>1.41</v>
       </c>
       <c r="C148">
-        <v>-1.02</v>
+        <v>-1.24</v>
       </c>
       <c r="D148">
         <v>2.34</v>
@@ -2625,7 +2625,7 @@
         <v>1.32</v>
       </c>
       <c r="C149">
-        <v>-1.01</v>
+        <v>-1.23</v>
       </c>
       <c r="D149">
         <v>2.27</v>
@@ -2639,7 +2639,7 @@
         <v>1.24</v>
       </c>
       <c r="C150">
-        <v>-1</v>
+        <v>-1.21</v>
       </c>
       <c r="D150">
         <v>2.21</v>
@@ -2653,7 +2653,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="C151">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="D151">
         <v>2.15</v>
@@ -2667,7 +2667,7 @@
         <v>1.07</v>
       </c>
       <c r="C152">
-        <v>-0.99</v>
+        <v>-1.19</v>
       </c>
       <c r="D152">
         <v>2.09</v>
@@ -2681,7 +2681,7 @@
         <v>0.99</v>
       </c>
       <c r="C153">
-        <v>-0.97</v>
+        <v>-1.18</v>
       </c>
       <c r="D153">
         <v>2.02</v>
@@ -2695,7 +2695,7 @@
         <v>0.9</v>
       </c>
       <c r="C154">
-        <v>-0.96</v>
+        <v>-1.17</v>
       </c>
       <c r="D154">
         <v>1.96</v>
@@ -2709,7 +2709,7 @@
         <v>0.82</v>
       </c>
       <c r="C155">
-        <v>-0.95</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="D155">
         <v>1.89</v>
@@ -2723,7 +2723,7 @@
         <v>0.74</v>
       </c>
       <c r="C156">
-        <v>-0.94</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="D156">
         <v>1.82</v>
@@ -2737,7 +2737,7 @@
         <v>0.66</v>
       </c>
       <c r="C157">
-        <v>-0.93</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="D157">
         <v>1.75</v>
@@ -2751,7 +2751,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="C158">
-        <v>-0.92</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="D158">
         <v>1.69</v>
@@ -2765,7 +2765,7 @@
         <v>0.5</v>
       </c>
       <c r="C159">
-        <v>-0.91</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="D159">
         <v>1.62</v>
@@ -2779,7 +2779,7 @@
         <v>0.42</v>
       </c>
       <c r="C160">
-        <v>-0.9</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="D160">
         <v>1.55</v>
@@ -2793,7 +2793,7 @@
         <v>0.35</v>
       </c>
       <c r="C161">
-        <v>-0.9</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D161">
         <v>1.48</v>
@@ -2807,7 +2807,7 @@
         <v>0.27</v>
       </c>
       <c r="C162">
-        <v>-0.88</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D162">
         <v>1.41</v>
@@ -2821,7 +2821,7 @@
         <v>0.2</v>
       </c>
       <c r="C163">
-        <v>-0.87</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="D163">
         <v>1.34</v>
@@ -2835,7 +2835,7 @@
         <v>0.12</v>
       </c>
       <c r="C164">
-        <v>-0.87</v>
+        <v>-1.08</v>
       </c>
       <c r="D164">
         <v>1.27</v>
@@ -2849,7 +2849,7 @@
         <v>0.04</v>
       </c>
       <c r="C165">
-        <v>-0.86</v>
+        <v>-1.07</v>
       </c>
       <c r="D165">
         <v>1.19</v>
@@ -2863,7 +2863,7 @@
         <v>-0.03</v>
       </c>
       <c r="C166">
-        <v>-0.85</v>
+        <v>-1.06</v>
       </c>
       <c r="D166">
         <v>1.1200000000000001</v>
@@ -2877,7 +2877,7 @@
         <v>-0.1</v>
       </c>
       <c r="C167">
-        <v>-0.84</v>
+        <v>-1.05</v>
       </c>
       <c r="D167">
         <v>1.05</v>
@@ -2891,7 +2891,7 @@
         <v>-0.17</v>
       </c>
       <c r="C168">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
       <c r="D168">
         <v>0.98</v>
@@ -2905,7 +2905,7 @@
         <v>-0.24</v>
       </c>
       <c r="C169">
-        <v>-0.82</v>
+        <v>-1.03</v>
       </c>
       <c r="D169">
         <v>0.91</v>
@@ -2919,7 +2919,7 @@
         <v>-0.31</v>
       </c>
       <c r="C170">
-        <v>-0.81</v>
+        <v>-1.02</v>
       </c>
       <c r="D170">
         <v>0.84</v>
@@ -2933,7 +2933,7 @@
         <v>-0.38</v>
       </c>
       <c r="C171">
-        <v>-0.8</v>
+        <v>-1.01</v>
       </c>
       <c r="D171">
         <v>0.76</v>
@@ -2947,7 +2947,7 @@
         <v>-0.44</v>
       </c>
       <c r="C172">
-        <v>-0.79</v>
+        <v>-1</v>
       </c>
       <c r="D172">
         <v>0.69</v>
@@ -2961,7 +2961,7 @@
         <v>-0.51</v>
       </c>
       <c r="C173">
-        <v>-0.78</v>
+        <v>-0.99</v>
       </c>
       <c r="D173">
         <v>0.62</v>
@@ -2975,7 +2975,7 @@
         <v>-0.56999999999999995</v>
       </c>
       <c r="C174">
-        <v>-0.78</v>
+        <v>-0.99</v>
       </c>
       <c r="D174">
         <v>0.56000000000000005</v>
@@ -2989,7 +2989,7 @@
         <v>-0.63</v>
       </c>
       <c r="C175">
-        <v>-0.78</v>
+        <v>-0.98</v>
       </c>
       <c r="D175">
         <v>0.49</v>
@@ -3003,7 +3003,7 @@
         <v>-0.69</v>
       </c>
       <c r="C176">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="D176">
         <v>0.42</v>
@@ -3017,7 +3017,7 @@
         <v>-0.75</v>
       </c>
       <c r="C177">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="D177">
         <v>0.35</v>
@@ -3031,7 +3031,7 @@
         <v>-0.81</v>
       </c>
       <c r="C178">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="D178">
         <v>0.28000000000000003</v>
@@ -3045,7 +3045,7 @@
         <v>-0.87</v>
       </c>
       <c r="C179">
-        <v>-0.77</v>
+        <v>-0.97</v>
       </c>
       <c r="D179">
         <v>0.21</v>
@@ -3059,7 +3059,7 @@
         <v>-0.92</v>
       </c>
       <c r="C180">
-        <v>-0.76</v>
+        <v>-0.97</v>
       </c>
       <c r="D180">
         <v>0.14000000000000001</v>
@@ -3073,7 +3073,7 @@
         <v>-0.97</v>
       </c>
       <c r="C181">
-        <v>-0.76</v>
+        <v>-0.97</v>
       </c>
       <c r="D181">
         <v>0.08</v>
@@ -3087,7 +3087,7 @@
         <v>-1.03</v>
       </c>
       <c r="C182">
-        <v>-0.76</v>
+        <v>-0.96</v>
       </c>
       <c r="D182">
         <v>0.01</v>
@@ -3101,7 +3101,7 @@
         <v>-1.08</v>
       </c>
       <c r="C183">
-        <v>-0.76</v>
+        <v>-0.96</v>
       </c>
       <c r="D183">
         <v>-0.05</v>
@@ -3115,7 +3115,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="C184">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D184">
         <v>-0.12</v>
@@ -3129,7 +3129,7 @@
         <v>-1.17</v>
       </c>
       <c r="C185">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D185">
         <v>-0.18</v>
@@ -3143,7 +3143,7 @@
         <v>-1.22</v>
       </c>
       <c r="C186">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D186">
         <v>-0.25</v>
@@ -3157,7 +3157,7 @@
         <v>-1.27</v>
       </c>
       <c r="C187">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D187">
         <v>-0.31</v>
@@ -3171,7 +3171,7 @@
         <v>-1.32</v>
       </c>
       <c r="C188">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D188">
         <v>-0.38</v>
@@ -3185,7 +3185,7 @@
         <v>-1.36</v>
       </c>
       <c r="C189">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D189">
         <v>-0.44</v>
@@ -3199,7 +3199,7 @@
         <v>-1.4</v>
       </c>
       <c r="C190">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D190">
         <v>-0.5</v>
@@ -3213,7 +3213,7 @@
         <v>-1.44</v>
       </c>
       <c r="C191">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D191">
         <v>-0.56000000000000005</v>
@@ -3227,7 +3227,7 @@
         <v>-1.48</v>
       </c>
       <c r="C192">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D192">
         <v>-0.61</v>
@@ -3241,7 +3241,7 @@
         <v>-1.52</v>
       </c>
       <c r="C193">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D193">
         <v>-0.67</v>
@@ -3255,7 +3255,7 @@
         <v>-1.56</v>
       </c>
       <c r="C194">
-        <v>-0.76</v>
+        <v>-0.96</v>
       </c>
       <c r="D194">
         <v>-0.73</v>
@@ -3269,7 +3269,7 @@
         <v>-1.6</v>
       </c>
       <c r="C195">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D195">
         <v>-0.78</v>
@@ -3283,7 +3283,7 @@
         <v>-1.63</v>
       </c>
       <c r="C196">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D196">
         <v>-0.84</v>
@@ -3297,7 +3297,7 @@
         <v>-1.67</v>
       </c>
       <c r="C197">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D197">
         <v>-0.89</v>
@@ -3311,7 +3311,7 @@
         <v>-1.7</v>
       </c>
       <c r="C198">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D198">
         <v>-0.94</v>
@@ -3325,7 +3325,7 @@
         <v>-1.73</v>
       </c>
       <c r="C199">
-        <v>-0.74</v>
+        <v>-0.95</v>
       </c>
       <c r="D199">
         <v>-1</v>
@@ -3339,7 +3339,7 @@
         <v>-1.76</v>
       </c>
       <c r="C200">
-        <v>-0.74</v>
+        <v>-0.95</v>
       </c>
       <c r="D200">
         <v>-1.05</v>
@@ -3353,7 +3353,7 @@
         <v>-1.79</v>
       </c>
       <c r="C201">
-        <v>-0.74</v>
+        <v>-0.94</v>
       </c>
       <c r="D201">
         <v>-1.1000000000000001</v>
@@ -3367,7 +3367,7 @@
         <v>-1.82</v>
       </c>
       <c r="C202">
-        <v>-0.73</v>
+        <v>-0.94</v>
       </c>
       <c r="D202">
         <v>-1.1499999999999999</v>
@@ -3381,7 +3381,7 @@
         <v>-1.84</v>
       </c>
       <c r="C203">
-        <v>-0.73</v>
+        <v>-0.94</v>
       </c>
       <c r="D203">
         <v>-1.19</v>
@@ -3395,7 +3395,7 @@
         <v>-1.87</v>
       </c>
       <c r="C204">
-        <v>-0.73</v>
+        <v>-0.94</v>
       </c>
       <c r="D204">
         <v>-1.23</v>
@@ -3409,7 +3409,7 @@
         <v>-1.89</v>
       </c>
       <c r="C205">
-        <v>-0.73</v>
+        <v>-0.94</v>
       </c>
       <c r="D205">
         <v>-1.28</v>
@@ -3423,7 +3423,7 @@
         <v>-1.92</v>
       </c>
       <c r="C206">
-        <v>-0.74</v>
+        <v>-0.95</v>
       </c>
       <c r="D206">
         <v>-1.32</v>
@@ -3437,7 +3437,7 @@
         <v>-1.95</v>
       </c>
       <c r="C207">
-        <v>-0.74</v>
+        <v>-0.95</v>
       </c>
       <c r="D207">
         <v>-1.37</v>
@@ -3451,7 +3451,7 @@
         <v>-1.97</v>
       </c>
       <c r="C208">
-        <v>-0.74</v>
+        <v>-0.96</v>
       </c>
       <c r="D208">
         <v>-1.41</v>
@@ -3465,7 +3465,7 @@
         <v>-1.99</v>
       </c>
       <c r="C209">
-        <v>-0.75</v>
+        <v>-0.96</v>
       </c>
       <c r="D209">
         <v>-1.45</v>
@@ -3479,7 +3479,7 @@
         <v>-2.0099999999999998</v>
       </c>
       <c r="C210">
-        <v>-0.76</v>
+        <v>-0.97</v>
       </c>
       <c r="D210">
         <v>-1.49</v>
@@ -3493,7 +3493,7 @@
         <v>-2.0299999999999998</v>
       </c>
       <c r="C211">
-        <v>-0.76</v>
+        <v>-0.98</v>
       </c>
       <c r="D211">
         <v>-1.52</v>
@@ -3507,7 +3507,7 @@
         <v>-2.0499999999999998</v>
       </c>
       <c r="C212">
-        <v>-0.78</v>
+        <v>-0.98</v>
       </c>
       <c r="D212">
         <v>-1.56</v>
@@ -3521,7 +3521,7 @@
         <v>-2.0699999999999998</v>
       </c>
       <c r="C213">
-        <v>-0.78</v>
+        <v>-0.99</v>
       </c>
       <c r="D213">
         <v>-1.6</v>
@@ -3535,7 +3535,7 @@
         <v>-2.08</v>
       </c>
       <c r="C214">
-        <v>-0.79</v>
+        <v>-1</v>
       </c>
       <c r="D214">
         <v>-1.63</v>
@@ -3549,7 +3549,7 @@
         <v>-2.1</v>
       </c>
       <c r="C215">
-        <v>-0.8</v>
+        <v>-1.01</v>
       </c>
       <c r="D215">
         <v>-1.66</v>
@@ -3563,7 +3563,7 @@
         <v>-2.11</v>
       </c>
       <c r="C216">
-        <v>-0.81</v>
+        <v>-1.02</v>
       </c>
       <c r="D216">
         <v>-1.69</v>
@@ -3577,7 +3577,7 @@
         <v>-2.12</v>
       </c>
       <c r="C217">
-        <v>-0.81</v>
+        <v>-1.03</v>
       </c>
       <c r="D217">
         <v>-1.72</v>
@@ -3591,7 +3591,7 @@
         <v>-2.13</v>
       </c>
       <c r="C218">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
       <c r="D218">
         <v>-1.75</v>
@@ -3605,7 +3605,7 @@
         <v>-2.14</v>
       </c>
       <c r="C219">
-        <v>-0.84</v>
+        <v>-1.05</v>
       </c>
       <c r="D219">
         <v>-1.78</v>
@@ -3619,7 +3619,7 @@
         <v>-2.15</v>
       </c>
       <c r="C220">
-        <v>-0.85</v>
+        <v>-1.06</v>
       </c>
       <c r="D220">
         <v>-1.8</v>
@@ -3633,7 +3633,7 @@
         <v>-2.16</v>
       </c>
       <c r="C221">
-        <v>-0.87</v>
+        <v>-1.08</v>
       </c>
       <c r="D221">
         <v>-1.83</v>
@@ -3647,7 +3647,7 @@
         <v>-2.17</v>
       </c>
       <c r="C222">
-        <v>-0.88</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="D222">
         <v>-1.85</v>
@@ -3661,7 +3661,7 @@
         <v>-2.1800000000000002</v>
       </c>
       <c r="C223">
-        <v>-0.89</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D223">
         <v>-1.87</v>
@@ -3675,7 +3675,7 @@
         <v>-2.1800000000000002</v>
       </c>
       <c r="C224">
-        <v>-0.91</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="D224">
         <v>-1.89</v>
@@ -3689,7 +3689,7 @@
         <v>-2.19</v>
       </c>
       <c r="C225">
-        <v>-0.92</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="D225">
         <v>-1.91</v>
@@ -3703,7 +3703,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="C226">
-        <v>-0.94</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="D226">
         <v>-1.94</v>
@@ -3717,7 +3717,7 @@
         <v>-2.21</v>
       </c>
       <c r="C227">
-        <v>-0.95</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="D227">
         <v>-1.96</v>
@@ -3731,7 +3731,7 @@
         <v>-2.21</v>
       </c>
       <c r="C228">
-        <v>-0.97</v>
+        <v>-1.18</v>
       </c>
       <c r="D228">
         <v>-1.97</v>
@@ -3745,7 +3745,7 @@
         <v>-2.2200000000000002</v>
       </c>
       <c r="C229">
-        <v>-0.98</v>
+        <v>-1.19</v>
       </c>
       <c r="D229">
         <v>-1.99</v>
@@ -3759,7 +3759,7 @@
         <v>-2.2200000000000002</v>
       </c>
       <c r="C230">
-        <v>-0.99</v>
+        <v>-1.2</v>
       </c>
       <c r="D230">
         <v>-2.0099999999999998</v>
@@ -3773,7 +3773,7 @@
         <v>-2.23</v>
       </c>
       <c r="C231">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="D231">
         <v>-2.0299999999999998</v>
@@ -3787,7 +3787,7 @@
         <v>-2.23</v>
       </c>
       <c r="C232">
-        <v>-1.01</v>
+        <v>-1.21</v>
       </c>
       <c r="D232">
         <v>-2.04</v>
@@ -3801,7 +3801,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C233">
-        <v>-1.02</v>
+        <v>-1.22</v>
       </c>
       <c r="D233">
         <v>-2.06</v>
@@ -3815,7 +3815,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C234">
-        <v>-1.03</v>
+        <v>-1.23</v>
       </c>
       <c r="D234">
         <v>-2.0699999999999998</v>
@@ -3829,7 +3829,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C235">
-        <v>-1.03</v>
+        <v>-1.24</v>
       </c>
       <c r="D235">
         <v>-2.08</v>
@@ -3843,7 +3843,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C236">
-        <v>-1.03</v>
+        <v>-1.25</v>
       </c>
       <c r="D236">
         <v>-2.1</v>
@@ -3857,7 +3857,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C237">
-        <v>-1.03</v>
+        <v>-1.25</v>
       </c>
       <c r="D237">
         <v>-2.11</v>
@@ -3871,7 +3871,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C238">
-        <v>-1.03</v>
+        <v>-1.25</v>
       </c>
       <c r="D238">
         <v>-2.12</v>
@@ -3885,7 +3885,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C239">
-        <v>-1.04</v>
+        <v>-1.25</v>
       </c>
       <c r="D239">
         <v>-2.13</v>
@@ -3899,7 +3899,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C240">
-        <v>-1.04</v>
+        <v>-1.25</v>
       </c>
       <c r="D240">
         <v>-2.14</v>
@@ -3913,7 +3913,7 @@
         <v>-2.2400000000000002</v>
       </c>
       <c r="C241">
-        <v>-1.04</v>
+        <v>-1.24</v>
       </c>
       <c r="D241">
         <v>-2.14</v>
@@ -3927,7 +3927,7 @@
         <v>-2.23</v>
       </c>
       <c r="C242">
-        <v>-1.03</v>
+        <v>-1.24</v>
       </c>
       <c r="D242">
         <v>-2.15</v>
@@ -3941,7 +3941,7 @@
         <v>-2.23</v>
       </c>
       <c r="C243">
-        <v>-1.02</v>
+        <v>-1.23</v>
       </c>
       <c r="D243">
         <v>-2.15</v>
@@ -3955,7 +3955,7 @@
         <v>-2.23</v>
       </c>
       <c r="C244">
-        <v>-1.01</v>
+        <v>-1.22</v>
       </c>
       <c r="D244">
         <v>-2.16</v>
@@ -3969,7 +3969,7 @@
         <v>-2.23</v>
       </c>
       <c r="C245">
-        <v>-1</v>
+        <v>-1.22</v>
       </c>
       <c r="D245">
         <v>-2.17</v>
@@ -3983,7 +3983,7 @@
         <v>-2.23</v>
       </c>
       <c r="C246">
-        <v>-0.99</v>
+        <v>-1.21</v>
       </c>
       <c r="D246">
         <v>-2.1800000000000002</v>
@@ -3997,7 +3997,7 @@
         <v>-2.23</v>
       </c>
       <c r="C247">
-        <v>-0.99</v>
+        <v>-1.19</v>
       </c>
       <c r="D247">
         <v>-2.1800000000000002</v>
@@ -4011,7 +4011,7 @@
         <v>-2.23</v>
       </c>
       <c r="C248">
-        <v>-0.97</v>
+        <v>-1.18</v>
       </c>
       <c r="D248">
         <v>-2.1800000000000002</v>
@@ -4025,7 +4025,7 @@
         <v>-2.23</v>
       </c>
       <c r="C249">
-        <v>-0.96</v>
+        <v>-1.17</v>
       </c>
       <c r="D249">
         <v>-2.19</v>
@@ -4039,7 +4039,7 @@
         <v>-2.2200000000000002</v>
       </c>
       <c r="C250">
-        <v>-0.95</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="D250">
         <v>-2.19</v>
@@ -4053,7 +4053,7 @@
         <v>-2.2200000000000002</v>
       </c>
       <c r="C251">
-        <v>-0.93</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="D251">
         <v>-2.2000000000000002</v>
@@ -4067,7 +4067,7 @@
         <v>-2.21</v>
       </c>
       <c r="C252">
-        <v>-0.91</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="D252">
         <v>-2.2000000000000002</v>
@@ -4081,7 +4081,7 @@
         <v>-2.21</v>
       </c>
       <c r="C253">
-        <v>-0.9</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="D253">
         <v>-2.2000000000000002</v>
@@ -4095,7 +4095,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="C254">
-        <v>-0.88</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="D254">
         <v>-2.2000000000000002</v>
@@ -4109,7 +4109,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="C255">
-        <v>-0.86</v>
+        <v>-1.07</v>
       </c>
       <c r="D255">
         <v>-2.2000000000000002</v>
@@ -4123,7 +4123,7 @@
         <v>-2.19</v>
       </c>
       <c r="C256">
-        <v>-0.84</v>
+        <v>-1.04</v>
       </c>
       <c r="D256">
         <v>-2.2000000000000002</v>
@@ -4137,7 +4137,7 @@
         <v>-2.19</v>
       </c>
       <c r="C257">
-        <v>-0.82</v>
+        <v>-1.02</v>
       </c>
       <c r="D257">
         <v>-2.2000000000000002</v>
@@ -4151,7 +4151,7 @@
         <v>-2.1800000000000002</v>
       </c>
       <c r="C258">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="D258">
         <v>-2.2000000000000002</v>
@@ -4165,7 +4165,7 @@
         <v>-2.17</v>
       </c>
       <c r="C259">
-        <v>-0.77</v>
+        <v>-0.98</v>
       </c>
       <c r="D259">
         <v>-2.19</v>
@@ -4179,7 +4179,7 @@
         <v>-2.16</v>
       </c>
       <c r="C260">
-        <v>-0.74</v>
+        <v>-0.96</v>
       </c>
       <c r="D260">
         <v>-2.19</v>
@@ -4193,7 +4193,7 @@
         <v>-2.15</v>
       </c>
       <c r="C261">
-        <v>-0.72</v>
+        <v>-0.94</v>
       </c>
       <c r="D261">
         <v>-2.19</v>
@@ -4207,7 +4207,7 @@
         <v>-2.15</v>
       </c>
       <c r="C262">
-        <v>-0.69</v>
+        <v>-0.91</v>
       </c>
       <c r="D262">
         <v>-2.1800000000000002</v>
@@ -4221,7 +4221,7 @@
         <v>-2.14</v>
       </c>
       <c r="C263">
-        <v>-0.67</v>
+        <v>-0.88</v>
       </c>
       <c r="D263">
         <v>-2.1800000000000002</v>
@@ -4235,7 +4235,7 @@
         <v>-2.13</v>
       </c>
       <c r="C264">
-        <v>-0.64</v>
+        <v>-0.85</v>
       </c>
       <c r="D264">
         <v>-2.17</v>
@@ -4249,7 +4249,7 @@
         <v>-2.12</v>
       </c>
       <c r="C265">
-        <v>-0.62</v>
+        <v>-0.82</v>
       </c>
       <c r="D265">
         <v>-2.17</v>
@@ -4263,7 +4263,7 @@
         <v>-2.11</v>
       </c>
       <c r="C266">
-        <v>-0.59</v>
+        <v>-0.79</v>
       </c>
       <c r="D266">
         <v>-2.16</v>
@@ -4277,7 +4277,7 @@
         <v>-2.1</v>
       </c>
       <c r="C267">
-        <v>-0.56999999999999995</v>
+        <v>-0.77</v>
       </c>
       <c r="D267">
         <v>-2.15</v>
@@ -4291,7 +4291,7 @@
         <v>-2.09</v>
       </c>
       <c r="C268">
-        <v>-0.54</v>
+        <v>-0.75</v>
       </c>
       <c r="D268">
         <v>-2.15</v>
@@ -4305,7 +4305,7 @@
         <v>-2.08</v>
       </c>
       <c r="C269">
-        <v>-0.52</v>
+        <v>-0.73</v>
       </c>
       <c r="D269">
         <v>-2.14</v>
@@ -4319,7 +4319,7 @@
         <v>-2.0699999999999998</v>
       </c>
       <c r="C270">
-        <v>-0.5</v>
+        <v>-0.71</v>
       </c>
       <c r="D270">
         <v>-2.13</v>
@@ -4333,7 +4333,7 @@
         <v>-2.06</v>
       </c>
       <c r="C271">
-        <v>-0.47</v>
+        <v>-0.68</v>
       </c>
       <c r="D271">
         <v>-2.13</v>
@@ -4347,7 +4347,7 @@
         <v>-2.0499999999999998</v>
       </c>
       <c r="C272">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="D272">
         <v>-2.12</v>
@@ -4361,7 +4361,7 @@
         <v>-2.0299999999999998</v>
       </c>
       <c r="C273">
-        <v>-0.42</v>
+        <v>-0.63</v>
       </c>
       <c r="D273">
         <v>-2.11</v>
@@ -4375,7 +4375,7 @@
         <v>-2.02</v>
       </c>
       <c r="C274">
-        <v>-0.39</v>
+        <v>-0.61</v>
       </c>
       <c r="D274">
         <v>-2.1</v>
@@ -4389,7 +4389,7 @@
         <v>-2.0099999999999998</v>
       </c>
       <c r="C275">
-        <v>-0.37</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="D275">
         <v>-2.09</v>
@@ -4403,7 +4403,7 @@
         <v>-2</v>
       </c>
       <c r="C276">
-        <v>-0.34</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="D276">
         <v>-2.08</v>
@@ -4417,7 +4417,7 @@
         <v>-1.99</v>
       </c>
       <c r="C277">
-        <v>-0.31</v>
+        <v>-0.52</v>
       </c>
       <c r="D277">
         <v>-2.0699999999999998</v>
@@ -4431,7 +4431,7 @@
         <v>-1.98</v>
       </c>
       <c r="C278">
-        <v>-0.28999999999999998</v>
+        <v>-0.49</v>
       </c>
       <c r="D278">
         <v>-2.0699999999999998</v>
@@ -4445,7 +4445,7 @@
         <v>-1.97</v>
       </c>
       <c r="C279">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="D279">
         <v>-2.06</v>
@@ -4459,7 +4459,7 @@
         <v>-1.96</v>
       </c>
       <c r="C280">
-        <v>-0.23</v>
+        <v>-0.44</v>
       </c>
       <c r="D280">
         <v>-2.0499999999999998</v>
@@ -4473,7 +4473,7 @@
         <v>-1.94</v>
       </c>
       <c r="C281">
-        <v>-0.21</v>
+        <v>-0.42</v>
       </c>
       <c r="D281">
         <v>-2.04</v>
@@ -4487,7 +4487,7 @@
         <v>-1.93</v>
       </c>
       <c r="C282">
-        <v>-0.18</v>
+        <v>-0.4</v>
       </c>
       <c r="D282">
         <v>-2.0299999999999998</v>
@@ -4501,7 +4501,7 @@
         <v>-1.92</v>
       </c>
       <c r="C283">
-        <v>-0.16</v>
+        <v>-0.38</v>
       </c>
       <c r="D283">
         <v>-2.02</v>
@@ -4515,7 +4515,7 @@
         <v>-1.91</v>
       </c>
       <c r="C284">
-        <v>-0.13</v>
+        <v>-0.35</v>
       </c>
       <c r="D284">
         <v>-2.0099999999999998</v>
@@ -4529,7 +4529,7 @@
         <v>-1.9</v>
       </c>
       <c r="C285">
-        <v>-0.11</v>
+        <v>-0.32</v>
       </c>
       <c r="D285">
         <v>-2</v>
@@ -4543,7 +4543,7 @@
         <v>-1.88</v>
       </c>
       <c r="C286">
-        <v>-0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="D286">
         <v>-1.99</v>
@@ -4557,7 +4557,7 @@
         <v>-1.87</v>
       </c>
       <c r="C287">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.27</v>
       </c>
       <c r="D287">
         <v>-1.98</v>
@@ -4571,7 +4571,7 @@
         <v>-1.86</v>
       </c>
       <c r="C288">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="D288">
         <v>-1.97</v>
@@ -4585,7 +4585,7 @@
         <v>-1.84</v>
       </c>
       <c r="C289">
-        <v>-0.03</v>
+        <v>-0.24</v>
       </c>
       <c r="D289">
         <v>-1.95</v>
@@ -4599,7 +4599,7 @@
         <v>-1.83</v>
       </c>
       <c r="C290">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="D290">
         <v>-1.94</v>
@@ -4613,7 +4613,7 @@
         <v>-1.81</v>
       </c>
       <c r="C291">
-        <v>0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="D291">
         <v>-1.93</v>
@@ -4627,7 +4627,7 @@
         <v>-1.8</v>
       </c>
       <c r="C292">
-        <v>0.03</v>
+        <v>-0.18</v>
       </c>
       <c r="D292">
         <v>-1.92</v>
@@ -4641,7 +4641,7 @@
         <v>-1.79</v>
       </c>
       <c r="C293">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="D293">
         <v>-1.9</v>
@@ -4655,7 +4655,7 @@
         <v>-1.77</v>
       </c>
       <c r="C294">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.13</v>
       </c>
       <c r="D294">
         <v>-1.89</v>
@@ -4669,7 +4669,7 @@
         <v>-1.76</v>
       </c>
       <c r="C295">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="D295">
         <v>-1.88</v>
@@ -4683,7 +4683,7 @@
         <v>-1.74</v>
       </c>
       <c r="C296">
-        <v>0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="D296">
         <v>-1.86</v>
@@ -4697,7 +4697,7 @@
         <v>-1.73</v>
       </c>
       <c r="C297">
-        <v>0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="D297">
         <v>-1.85</v>
@@ -4711,7 +4711,7 @@
         <v>-1.71</v>
       </c>
       <c r="C298">
-        <v>0.14000000000000001</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D298">
         <v>-1.83</v>
@@ -4725,7 +4725,7 @@
         <v>-1.69</v>
       </c>
       <c r="C299">
-        <v>0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="D299">
         <v>-1.82</v>
@@ -4739,7 +4739,7 @@
         <v>-1.68</v>
       </c>
       <c r="C300">
-        <v>0.16</v>
+        <v>-0.05</v>
       </c>
       <c r="D300">
         <v>-1.8</v>
@@ -4753,7 +4753,7 @@
         <v>-1.66</v>
       </c>
       <c r="C301">
-        <v>0.17</v>
+        <v>-0.03</v>
       </c>
       <c r="D301">
         <v>-1.79</v>
@@ -4767,7 +4767,7 @@
         <v>-1.64</v>
       </c>
       <c r="C302">
-        <v>0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="D302">
         <v>-1.77</v>
@@ -4781,7 +4781,7 @@
         <v>-1.62</v>
       </c>
       <c r="C303">
-        <v>0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="D303">
         <v>-1.75</v>
@@ -4795,7 +4795,7 @@
         <v>-1.6</v>
       </c>
       <c r="C304">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="D304">
         <v>-1.73</v>
@@ -4809,7 +4809,7 @@
         <v>-1.58</v>
       </c>
       <c r="C305">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="D305">
         <v>-1.7</v>
@@ -4823,7 +4823,7 @@
         <v>-1.55</v>
       </c>
       <c r="C306">
-        <v>0.24</v>
+        <v>0.03</v>
       </c>
       <c r="D306">
         <v>-1.68</v>
@@ -4837,7 +4837,7 @@
         <v>-1.53</v>
       </c>
       <c r="C307">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="D307">
         <v>-1.66</v>
@@ -4851,7 +4851,7 @@
         <v>-1.52</v>
       </c>
       <c r="C308">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="D308">
         <v>-1.65</v>
@@ -4865,7 +4865,7 @@
         <v>-1.5</v>
       </c>
       <c r="C309">
-        <v>0.28000000000000003</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D309">
         <v>-1.63</v>
@@ -4879,7 +4879,7 @@
         <v>-1.48</v>
       </c>
       <c r="C310">
-        <v>0.28999999999999998</v>
+        <v>0.08</v>
       </c>
       <c r="D310">
         <v>-1.61</v>
@@ -4893,7 +4893,7 @@
         <v>-1.46</v>
       </c>
       <c r="C311">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="D311">
         <v>-1.59</v>
@@ -4907,7 +4907,7 @@
         <v>-1.44</v>
       </c>
       <c r="C312">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D312">
         <v>-1.57</v>
@@ -4921,7 +4921,7 @@
         <v>-1.42</v>
       </c>
       <c r="C313">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="D313">
         <v>-1.55</v>
@@ -4935,7 +4935,7 @@
         <v>-1.4</v>
       </c>
       <c r="C314">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="D314">
         <v>-1.54</v>
@@ -4949,7 +4949,7 @@
         <v>-1.38</v>
       </c>
       <c r="C315">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="D315">
         <v>-1.52</v>
@@ -4963,7 +4963,7 @@
         <v>-1.36</v>
       </c>
       <c r="C316">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="D316">
         <v>-1.49</v>
@@ -4977,7 +4977,7 @@
         <v>-1.34</v>
       </c>
       <c r="C317">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="D317">
         <v>-1.47</v>
@@ -4991,7 +4991,7 @@
         <v>-1.31</v>
       </c>
       <c r="C318">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="D318">
         <v>-1.45</v>
@@ -5005,7 +5005,7 @@
         <v>-1.29</v>
       </c>
       <c r="C319">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="D319">
         <v>-1.43</v>
@@ -5019,7 +5019,7 @@
         <v>-1.27</v>
       </c>
       <c r="C320">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="D320">
         <v>-1.41</v>
@@ -5033,7 +5033,7 @@
         <v>-1.24</v>
       </c>
       <c r="C321">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="D321">
         <v>-1.38</v>
@@ -5047,7 +5047,7 @@
         <v>-1.22</v>
       </c>
       <c r="C322">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="D322">
         <v>-1.35</v>
@@ -5061,7 +5061,7 @@
         <v>-1.19</v>
       </c>
       <c r="C323">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
       <c r="D323">
         <v>-1.33</v>
@@ -5075,7 +5075,7 @@
         <v>-1.17</v>
       </c>
       <c r="C324">
-        <v>0.49</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D324">
         <v>-1.31</v>
@@ -5089,7 +5089,7 @@
         <v>-1.1399999999999999</v>
       </c>
       <c r="C325">
-        <v>0.5</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D325">
         <v>-1.28</v>
@@ -5103,7 +5103,7 @@
         <v>-1.1200000000000001</v>
       </c>
       <c r="C326">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="D326">
         <v>-1.26</v>
@@ -5117,7 +5117,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="C327">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="D327">
         <v>-1.24</v>
@@ -5131,7 +5131,7 @@
         <v>-1.07</v>
       </c>
       <c r="C328">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="D328">
         <v>-1.21</v>
@@ -5145,7 +5145,7 @@
         <v>-1.05</v>
       </c>
       <c r="C329">
-        <v>0.56999999999999995</v>
+        <v>0.37</v>
       </c>
       <c r="D329">
         <v>-1.19</v>
@@ -5159,7 +5159,7 @@
         <v>-1.02</v>
       </c>
       <c r="C330">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="D330">
         <v>-1.17</v>
@@ -5173,7 +5173,7 @@
         <v>-1</v>
       </c>
       <c r="C331">
-        <v>0.61</v>
+        <v>0.4</v>
       </c>
       <c r="D331">
         <v>-1.1399999999999999</v>
@@ -5187,7 +5187,7 @@
         <v>-0.97</v>
       </c>
       <c r="C332">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="D332">
         <v>-1.1200000000000001</v>
@@ -5201,7 +5201,7 @@
         <v>-0.95</v>
       </c>
       <c r="C333">
-        <v>0.64</v>
+        <v>0.43</v>
       </c>
       <c r="D333">
         <v>-1.0900000000000001</v>
@@ -5215,7 +5215,7 @@
         <v>-0.92</v>
       </c>
       <c r="C334">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="D334">
         <v>-1.06</v>
@@ -5229,7 +5229,7 @@
         <v>-0.89</v>
       </c>
       <c r="C335">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="D335">
         <v>-1.04</v>
@@ -5243,7 +5243,7 @@
         <v>-0.87</v>
       </c>
       <c r="C336">
-        <v>0.69</v>
+        <v>0.48</v>
       </c>
       <c r="D336">
         <v>-1.01</v>
@@ -5257,7 +5257,7 @@
         <v>-0.84</v>
       </c>
       <c r="C337">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="D337">
         <v>-0.99</v>
@@ -5271,7 +5271,7 @@
         <v>-0.82</v>
       </c>
       <c r="C338">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="D338">
         <v>-0.96</v>
@@ -5285,7 +5285,7 @@
         <v>-0.79</v>
       </c>
       <c r="C339">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="D339">
         <v>-0.94</v>
@@ -5299,7 +5299,7 @@
         <v>-0.77</v>
       </c>
       <c r="C340">
-        <v>0.76</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D340">
         <v>-0.91</v>
@@ -5313,7 +5313,7 @@
         <v>-0.74</v>
       </c>
       <c r="C341">
-        <v>0.78</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D341">
         <v>-0.88</v>
@@ -5327,7 +5327,7 @@
         <v>-0.71</v>
       </c>
       <c r="C342">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="D342">
         <v>-0.86</v>
@@ -5341,7 +5341,7 @@
         <v>-0.69</v>
       </c>
       <c r="C343">
-        <v>0.81</v>
+        <v>0.6</v>
       </c>
       <c r="D343">
         <v>-0.84</v>
@@ -5355,7 +5355,7 @@
         <v>-0.67</v>
       </c>
       <c r="C344">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="D344">
         <v>-0.82</v>
@@ -5369,7 +5369,7 @@
         <v>-0.65</v>
       </c>
       <c r="C345">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="D345">
         <v>-0.8</v>
@@ -5383,7 +5383,7 @@
         <v>-0.62</v>
       </c>
       <c r="C346">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="D346">
         <v>-0.77</v>
@@ -5397,7 +5397,7 @@
         <v>-0.6</v>
       </c>
       <c r="C347">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="D347">
         <v>-0.75</v>
@@ -5411,7 +5411,7 @@
         <v>-0.56999999999999995</v>
       </c>
       <c r="C348">
-        <v>0.9</v>
+        <v>0.69</v>
       </c>
       <c r="D348">
         <v>-0.72</v>
@@ -5425,7 +5425,7 @@
         <v>-0.55000000000000004</v>
       </c>
       <c r="C349">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="D349">
         <v>-0.7</v>
@@ -5439,7 +5439,7 @@
         <v>-0.52</v>
       </c>
       <c r="C350">
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
       <c r="D350">
         <v>-0.67</v>
@@ -5453,7 +5453,7 @@
         <v>-0.5</v>
       </c>
       <c r="C351">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="D351">
         <v>-0.65</v>
@@ -5467,7 +5467,7 @@
         <v>-0.48</v>
       </c>
       <c r="C352">
-        <v>0.96</v>
+        <v>0.74</v>
       </c>
       <c r="D352">
         <v>-0.62</v>
@@ -5481,7 +5481,7 @@
         <v>-0.46</v>
       </c>
       <c r="C353">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="D353">
         <v>-0.61</v>
@@ -5495,7 +5495,7 @@
         <v>-0.45</v>
       </c>
       <c r="C354">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="D354">
         <v>-0.59</v>
@@ -5509,7 +5509,7 @@
         <v>-0.43</v>
       </c>
       <c r="C355">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D355">
         <v>-0.57999999999999996</v>
@@ -5523,7 +5523,7 @@
         <v>-0.4</v>
       </c>
       <c r="C356">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
       <c r="D356">
         <v>-0.55000000000000004</v>
@@ -5537,7 +5537,7 @@
         <v>-0.38</v>
       </c>
       <c r="C357">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="D357">
         <v>-0.53</v>
@@ -5551,7 +5551,7 @@
         <v>-0.35</v>
       </c>
       <c r="C358">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="D358">
         <v>-0.5</v>
@@ -5565,7 +5565,7 @@
         <v>-0.34</v>
       </c>
       <c r="C359">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="D359">
         <v>-0.49</v>
@@ -5579,7 +5579,7 @@
         <v>-0.32</v>
       </c>
       <c r="C360">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="D360">
         <v>-0.47</v>
@@ -5593,7 +5593,7 @@
         <v>-0.3</v>
       </c>
       <c r="C361">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="D361">
         <v>-0.45</v>
@@ -5607,7 +5607,7 @@
         <v>-0.28000000000000003</v>
       </c>
       <c r="C362">
-        <v>1.08</v>
+        <v>0.87</v>
       </c>
       <c r="D362">
         <v>-0.43</v>
@@ -5621,7 +5621,7 @@
         <v>-0.26</v>
       </c>
       <c r="C363">
-        <v>1.0900000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="D363">
         <v>-0.41</v>
@@ -5635,7 +5635,7 @@
         <v>-0.25</v>
       </c>
       <c r="C364">
-        <v>1.1100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="D364">
         <v>-0.4</v>
@@ -5649,7 +5649,7 @@
         <v>-0.24</v>
       </c>
       <c r="C365">
-        <v>1.1200000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D365">
         <v>-0.39</v>
@@ -5663,7 +5663,7 @@
         <v>-0.22</v>
       </c>
       <c r="C366">
-        <v>1.1299999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D366">
         <v>-0.37</v>
@@ -5677,7 +5677,7 @@
         <v>-0.2</v>
       </c>
       <c r="C367">
-        <v>1.1399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="D367">
         <v>-0.35</v>
@@ -5691,7 +5691,7 @@
         <v>-0.17</v>
       </c>
       <c r="C368">
-        <v>1.1499999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="D368">
         <v>-0.32</v>
@@ -5705,7 +5705,7 @@
         <v>-0.15</v>
       </c>
       <c r="C369">
-        <v>1.1499999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="D369">
         <v>-0.3</v>
@@ -5719,7 +5719,7 @@
         <v>-0.13</v>
       </c>
       <c r="C370">
-        <v>1.1599999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="D370">
         <v>-0.28999999999999998</v>
@@ -5733,7 +5733,7 @@
         <v>-0.13</v>
       </c>
       <c r="C371">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="D371">
         <v>-0.28000000000000003</v>
@@ -5747,7 +5747,7 @@
         <v>-0.11</v>
       </c>
       <c r="C372">
-        <v>1.17</v>
+        <v>0.97</v>
       </c>
       <c r="D372">
         <v>-0.26</v>
@@ -5761,7 +5761,7 @@
         <v>-0.08</v>
       </c>
       <c r="C373">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="D373">
         <v>-0.23</v>
@@ -5775,7 +5775,7 @@
         <v>-0.06</v>
       </c>
       <c r="C374">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
       <c r="D374">
         <v>-0.21</v>
@@ -5789,7 +5789,7 @@
         <v>-0.05</v>
       </c>
       <c r="C375">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="D375">
         <v>-0.2</v>
@@ -5803,7 +5803,7 @@
         <v>-0.05</v>
       </c>
       <c r="C376">
-        <v>1.2</v>
+        <v>0.99</v>
       </c>
       <c r="D376">
         <v>-0.2</v>
@@ -5817,7 +5817,7 @@
         <v>-0.03</v>
       </c>
       <c r="C377">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="D377">
         <v>-0.18</v>
@@ -5831,7 +5831,7 @@
         <v>-0.01</v>
       </c>
       <c r="C378">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="D378">
         <v>-0.16</v>
@@ -5845,7 +5845,7 @@
         <v>0.02</v>
       </c>
       <c r="C379">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="D379">
         <v>-0.13</v>
@@ -5859,7 +5859,7 @@
         <v>0.03</v>
       </c>
       <c r="C380">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="D380">
         <v>-0.11</v>
@@ -5873,7 +5873,7 @@
         <v>0.04</v>
       </c>
       <c r="C381">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="D381">
         <v>-0.1</v>
@@ -5887,7 +5887,7 @@
         <v>0.06</v>
       </c>
       <c r="C382">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="D382">
         <v>-0.09</v>
@@ -5901,7 +5901,7 @@
         <v>0.08</v>
       </c>
       <c r="C383">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="D383">
         <v>-7.0000000000000007E-2</v>
@@ -5915,7 +5915,7 @@
         <v>0.11</v>
       </c>
       <c r="C384">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="D384">
         <v>-0.04</v>
@@ -5929,7 +5929,7 @@
         <v>0.13</v>
       </c>
       <c r="C385">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="D385">
         <v>-0.01</v>
@@ -5943,7 +5943,7 @@
         <v>0.15</v>
       </c>
       <c r="C386">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="D386">
         <v>0.01</v>
@@ -5957,7 +5957,7 @@
         <v>0.17</v>
       </c>
       <c r="C387">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="D387">
         <v>0.03</v>
@@ -5971,7 +5971,7 @@
         <v>0.2</v>
       </c>
       <c r="C388">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="D388">
         <v>0.05</v>
@@ -5985,7 +5985,7 @@
         <v>0.22</v>
       </c>
       <c r="C389">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="D389">
         <v>7.0000000000000007E-2</v>
@@ -5999,7 +5999,7 @@
         <v>0.25</v>
       </c>
       <c r="C390">
-        <v>1.3</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="D390">
         <v>0.1</v>
@@ -6013,7 +6013,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="C391">
-        <v>1.31</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D391">
         <v>0.13</v>
@@ -6027,7 +6027,7 @@
         <v>0.31</v>
       </c>
       <c r="C392">
-        <v>1.32</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D392">
         <v>0.16</v>
@@ -6041,7 +6041,7 @@
         <v>0.33</v>
       </c>
       <c r="C393">
-        <v>1.33</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D393">
         <v>0.18</v>
@@ -6055,7 +6055,7 @@
         <v>0.36</v>
       </c>
       <c r="C394">
-        <v>1.35</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D394">
         <v>0.21</v>
@@ -6069,7 +6069,7 @@
         <v>0.39</v>
       </c>
       <c r="C395">
-        <v>1.36</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D395">
         <v>0.24</v>
@@ -6083,7 +6083,7 @@
         <v>0.43</v>
       </c>
       <c r="C396">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="D396">
         <v>0.28000000000000003</v>
@@ -6097,7 +6097,7 @@
         <v>0.47</v>
       </c>
       <c r="C397">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="D397">
         <v>0.32</v>
@@ -6111,7 +6111,7 @@
         <v>0.51</v>
       </c>
       <c r="C398">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="D398">
         <v>0.36</v>
@@ -6125,7 +6125,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="C399">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="D399">
         <v>0.4</v>
@@ -6139,7 +6139,7 @@
         <v>0.59</v>
       </c>
       <c r="C400">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="D400">
         <v>0.44</v>
@@ -6153,7 +6153,7 @@
         <v>0.63</v>
       </c>
       <c r="C401">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="D401">
         <v>0.49</v>
@@ -6167,7 +6167,7 @@
         <v>0.68</v>
       </c>
       <c r="C402">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="D402">
         <v>0.53</v>
@@ -6181,7 +6181,7 @@
         <v>0.72</v>
       </c>
       <c r="C403">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="D403">
         <v>0.56999999999999995</v>
@@ -6195,7 +6195,7 @@
         <v>0.77</v>
       </c>
       <c r="C404">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="D404">
         <v>0.62</v>
@@ -6209,7 +6209,7 @@
         <v>0.81</v>
       </c>
       <c r="C405">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="D405">
         <v>0.66</v>
@@ -6223,7 +6223,7 @@
         <v>0.85</v>
       </c>
       <c r="C406">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="D406">
         <v>0.7</v>
@@ -6237,7 +6237,7 @@
         <v>0.9</v>
       </c>
       <c r="C407">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="D407">
         <v>0.75</v>
@@ -6251,7 +6251,7 @@
         <v>0.95</v>
       </c>
       <c r="C408">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="D408">
         <v>0.8</v>
@@ -6265,7 +6265,7 @@
         <v>1.01</v>
       </c>
       <c r="C409">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="D409">
         <v>0.86</v>
@@ -6279,7 +6279,7 @@
         <v>1.06</v>
       </c>
       <c r="C410">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="D410">
         <v>0.91</v>
@@ -6293,7 +6293,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C411">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="D411">
         <v>0.95</v>
@@ -6307,7 +6307,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="C412">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="D412">
         <v>1</v>
@@ -6321,7 +6321,7 @@
         <v>1.21</v>
       </c>
       <c r="C413">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="D413">
         <v>1.06</v>
@@ -6335,7 +6335,7 @@
         <v>1.27</v>
       </c>
       <c r="C414">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="D414">
         <v>1.1200000000000001</v>
@@ -6349,7 +6349,7 @@
         <v>1.33</v>
       </c>
       <c r="C415">
-        <v>2.0499999999999998</v>
+        <v>1.84</v>
       </c>
       <c r="D415">
         <v>1.18</v>
@@ -6363,7 +6363,7 @@
         <v>1.38</v>
       </c>
       <c r="C416">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="D416">
         <v>1.23</v>
@@ -6377,7 +6377,7 @@
         <v>1.44</v>
       </c>
       <c r="C417">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="D417">
         <v>1.29</v>
@@ -6391,7 +6391,7 @@
         <v>1.49</v>
       </c>
       <c r="C418">
-        <v>2.21</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D418">
         <v>1.34</v>
@@ -6405,7 +6405,7 @@
         <v>1.56</v>
       </c>
       <c r="C419">
-        <v>2.2799999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D419">
         <v>1.41</v>
@@ -6419,7 +6419,7 @@
         <v>1.62</v>
       </c>
       <c r="C420">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="D420">
         <v>1.47</v>
@@ -6433,7 +6433,7 @@
         <v>1.69</v>
       </c>
       <c r="C421">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="D421">
         <v>1.54</v>
@@ -6447,7 +6447,7 @@
         <v>1.75</v>
       </c>
       <c r="C422">
-        <v>2.4700000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="D422">
         <v>1.6</v>
@@ -6461,7 +6461,7 @@
         <v>1.8</v>
       </c>
       <c r="C423">
-        <v>2.54</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D423">
         <v>1.65</v>
@@ -6475,7 +6475,7 @@
         <v>1.86</v>
       </c>
       <c r="C424">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D424">
         <v>1.71</v>
@@ -6489,7 +6489,7 @@
         <v>1.93</v>
       </c>
       <c r="C425">
-        <v>2.68</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="D425">
         <v>1.78</v>
@@ -6503,7 +6503,7 @@
         <v>2</v>
       </c>
       <c r="C426">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="D426">
         <v>1.85</v>
@@ -6517,7 +6517,7 @@
         <v>2.06</v>
       </c>
       <c r="C427">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="D427">
         <v>1.91</v>
@@ -6531,7 +6531,7 @@
         <v>2.12</v>
       </c>
       <c r="C428">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="D428">
         <v>1.97</v>
@@ -6545,7 +6545,7 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="C429">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="D429">
         <v>2.0299999999999998</v>
@@ -6559,7 +6559,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="C430">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="D430">
         <v>2.09</v>
@@ -6573,7 +6573,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="C431">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D431">
         <v>2.17</v>
@@ -6587,7 +6587,7 @@
         <v>2.41</v>
       </c>
       <c r="C432">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="D432">
         <v>2.2599999999999998</v>
@@ -6601,7 +6601,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="C433">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="D433">
         <v>2.34</v>
@@ -6615,7 +6615,7 @@
         <v>2.5499999999999998</v>
       </c>
       <c r="C434">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="D434">
         <v>2.4</v>
@@ -6629,7 +6629,7 @@
         <v>2.6</v>
       </c>
       <c r="C435">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D435">
         <v>2.4500000000000002</v>
@@ -6643,7 +6643,7 @@
         <v>2.66</v>
       </c>
       <c r="C436">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="D436">
         <v>2.5099999999999998</v>
@@ -6657,7 +6657,7 @@
         <v>2.74</v>
       </c>
       <c r="C437">
-        <v>3.56</v>
+        <v>3.33</v>
       </c>
       <c r="D437">
         <v>2.59</v>
@@ -6671,7 +6671,7 @@
         <v>2.85</v>
       </c>
       <c r="C438">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="D438">
         <v>2.7</v>
@@ -6685,7 +6685,7 @@
         <v>2.95</v>
       </c>
       <c r="C439">
-        <v>3.73</v>
+        <v>3.49</v>
       </c>
       <c r="D439">
         <v>2.8</v>
@@ -6699,7 +6699,7 @@
         <v>3.02</v>
       </c>
       <c r="C440">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="D440">
         <v>2.87</v>
@@ -6713,7 +6713,7 @@
         <v>3.07</v>
       </c>
       <c r="C441">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="D441">
         <v>2.92</v>
@@ -6727,7 +6727,7 @@
         <v>3.12</v>
       </c>
       <c r="C442">
-        <v>4.01</v>
+        <v>3.81</v>
       </c>
       <c r="D442">
         <v>2.97</v>
@@ -6741,7 +6741,7 @@
         <v>3.2</v>
       </c>
       <c r="C443">
-        <v>4.0999999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="D443">
         <v>3.05</v>
@@ -6755,7 +6755,7 @@
         <v>3.31</v>
       </c>
       <c r="C444">
-        <v>4.1900000000000004</v>
+        <v>4.01</v>
       </c>
       <c r="D444">
         <v>3.16</v>
@@ -6769,7 +6769,7 @@
         <v>3.42</v>
       </c>
       <c r="C445">
-        <v>4.29</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D445">
         <v>3.27</v>
@@ -6783,7 +6783,7 @@
         <v>3.51</v>
       </c>
       <c r="C446">
-        <v>4.3899999999999997</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D446">
         <v>3.36</v>
@@ -6797,7 +6797,7 @@
         <v>3.59</v>
       </c>
       <c r="C447">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="D447">
         <v>3.44</v>
@@ -6811,7 +6811,7 @@
         <v>3.66</v>
       </c>
       <c r="C448">
-        <v>4.5999999999999996</v>
+        <v>4.38</v>
       </c>
       <c r="D448">
         <v>3.51</v>
@@ -6825,7 +6825,7 @@
         <v>3.74</v>
       </c>
       <c r="C449">
-        <v>4.71</v>
+        <v>4.49</v>
       </c>
       <c r="D449">
         <v>3.59</v>
@@ -6839,7 +6839,7 @@
         <v>3.85</v>
       </c>
       <c r="C450">
-        <v>4.82</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D450">
         <v>3.7</v>
@@ -6853,7 +6853,7 @@
         <v>3.96</v>
       </c>
       <c r="C451">
-        <v>4.9400000000000004</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="D451">
         <v>3.81</v>
@@ -6867,7 +6867,7 @@
         <v>4.07</v>
       </c>
       <c r="C452">
-        <v>5.05</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="D452">
         <v>3.92</v>
@@ -6881,7 +6881,7 @@
         <v>4.17</v>
       </c>
       <c r="C453">
-        <v>5.17</v>
+        <v>4.97</v>
       </c>
       <c r="D453">
         <v>4.0199999999999996</v>
@@ -6895,7 +6895,7 @@
         <v>4.28</v>
       </c>
       <c r="C454">
-        <v>5.29</v>
+        <v>5.09</v>
       </c>
       <c r="D454">
         <v>4.13</v>
@@ -6909,7 +6909,7 @@
         <v>4.3899999999999997</v>
       </c>
       <c r="C455">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="D455">
         <v>4.24</v>
@@ -6923,7 +6923,7 @@
         <v>4.5</v>
       </c>
       <c r="C456">
-        <v>5.53</v>
+        <v>5.32</v>
       </c>
       <c r="D456">
         <v>4.3499999999999996</v>
@@ -6937,7 +6937,7 @@
         <v>4.62</v>
       </c>
       <c r="C457">
-        <v>5.65</v>
+        <v>5.44</v>
       </c>
       <c r="D457">
         <v>4.47</v>
@@ -6951,7 +6951,7 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="C458">
-        <v>5.77</v>
+        <v>5.56</v>
       </c>
       <c r="D458">
         <v>4.58</v>
@@ -6965,7 +6965,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="C459">
-        <v>5.9</v>
+        <v>5.69</v>
       </c>
       <c r="D459">
         <v>4.7</v>
@@ -6979,7 +6979,7 @@
         <v>4.99</v>
       </c>
       <c r="C460">
-        <v>6.02</v>
+        <v>5.81</v>
       </c>
       <c r="D460">
         <v>4.83</v>
@@ -6993,7 +6993,7 @@
         <v>5.13</v>
       </c>
       <c r="C461">
-        <v>6.15</v>
+        <v>5.94</v>
       </c>
       <c r="D461">
         <v>4.9800000000000004</v>
@@ -7007,7 +7007,7 @@
         <v>5.28</v>
       </c>
       <c r="C462">
-        <v>6.27</v>
+        <v>6.06</v>
       </c>
       <c r="D462">
         <v>5.13</v>
@@ -7021,7 +7021,7 @@
         <v>5.42</v>
       </c>
       <c r="C463">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="D463">
         <v>5.27</v>
@@ -7035,7 +7035,7 @@
         <v>5.56</v>
       </c>
       <c r="C464">
-        <v>6.52</v>
+        <v>6.3</v>
       </c>
       <c r="D464">
         <v>5.41</v>
@@ -7049,7 +7049,7 @@
         <v>5.69</v>
       </c>
       <c r="C465">
-        <v>6.63</v>
+        <v>6.42</v>
       </c>
       <c r="D465">
         <v>5.54</v>
@@ -7063,7 +7063,7 @@
         <v>5.82</v>
       </c>
       <c r="C466">
-        <v>6.75</v>
+        <v>6.53</v>
       </c>
       <c r="D466">
         <v>5.67</v>
@@ -7077,7 +7077,7 @@
         <v>5.97</v>
       </c>
       <c r="C467">
-        <v>6.87</v>
+        <v>6.65</v>
       </c>
       <c r="D467">
         <v>5.82</v>
@@ -7091,7 +7091,7 @@
         <v>6.13</v>
       </c>
       <c r="C468">
-        <v>6.97</v>
+        <v>6.77</v>
       </c>
       <c r="D468">
         <v>5.98</v>
@@ -7105,7 +7105,7 @@
         <v>6.3</v>
       </c>
       <c r="C469">
-        <v>7.08</v>
+        <v>6.88</v>
       </c>
       <c r="D469">
         <v>6.15</v>
@@ -7119,7 +7119,7 @@
         <v>6.47</v>
       </c>
       <c r="C470">
-        <v>7.19</v>
+        <v>6.99</v>
       </c>
       <c r="D470">
         <v>6.32</v>
@@ -7133,7 +7133,7 @@
         <v>6.63</v>
       </c>
       <c r="C471">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
       <c r="D471">
         <v>6.48</v>
@@ -7147,7 +7147,7 @@
         <v>6.78</v>
       </c>
       <c r="C472">
-        <v>7.39</v>
+        <v>7.18</v>
       </c>
       <c r="D472">
         <v>6.63</v>
@@ -7161,7 +7161,7 @@
         <v>6.92</v>
       </c>
       <c r="C473">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="D473">
         <v>6.77</v>
@@ -7175,7 +7175,7 @@
         <v>7.06</v>
       </c>
       <c r="C474">
-        <v>7.6</v>
+        <v>7.38</v>
       </c>
       <c r="D474">
         <v>6.91</v>
@@ -7189,7 +7189,7 @@
         <v>7.2</v>
       </c>
       <c r="C475">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="D475">
         <v>7.05</v>
@@ -7203,7 +7203,7 @@
         <v>7.36</v>
       </c>
       <c r="C476">
-        <v>7.8</v>
+        <v>7.61</v>
       </c>
       <c r="D476">
         <v>7.21</v>
@@ -7217,7 +7217,7 @@
         <v>7.52</v>
       </c>
       <c r="C477">
-        <v>7.9</v>
+        <v>7.71</v>
       </c>
       <c r="D477">
         <v>7.37</v>
@@ -7231,7 +7231,7 @@
         <v>7.69</v>
       </c>
       <c r="C478">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="D478">
         <v>7.54</v>
@@ -7245,7 +7245,7 @@
         <v>7.86</v>
       </c>
       <c r="C479">
-        <v>8.1</v>
+        <v>7.88</v>
       </c>
       <c r="D479">
         <v>7.71</v>
@@ -7259,7 +7259,7 @@
         <v>8</v>
       </c>
       <c r="C480">
-        <v>8.19</v>
+        <v>7.95</v>
       </c>
       <c r="D480">
         <v>7.85</v>
@@ -7273,7 +7273,7 @@
         <v>8.1300000000000008</v>
       </c>
       <c r="C481">
-        <v>8.2799999999999994</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="D481">
         <v>7.98</v>
@@ -7287,7 +7287,7 @@
         <v>8.24</v>
       </c>
       <c r="C482">
-        <v>8.3699999999999992</v>
+        <v>8.15</v>
       </c>
       <c r="D482">
         <v>8.09</v>
@@ -7301,7 +7301,7 @@
         <v>8.36</v>
       </c>
       <c r="C483">
-        <v>8.4499999999999993</v>
+        <v>8.25</v>
       </c>
       <c r="D483">
         <v>8.2100000000000009</v>
@@ -7315,7 +7315,7 @@
         <v>8.49</v>
       </c>
       <c r="C484">
-        <v>8.5299999999999994</v>
+        <v>8.34</v>
       </c>
       <c r="D484">
         <v>8.34</v>
@@ -7329,7 +7329,7 @@
         <v>8.64</v>
       </c>
       <c r="C485">
-        <v>8.6</v>
+        <v>8.41</v>
       </c>
       <c r="D485">
         <v>8.49</v>
@@ -7343,7 +7343,7 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="C486">
-        <v>8.68</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="D486">
         <v>8.64</v>
@@ -7357,7 +7357,7 @@
         <v>8.93</v>
       </c>
       <c r="C487">
-        <v>8.75</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="D487">
         <v>8.7799999999999994</v>
@@ -7371,7 +7371,7 @@
         <v>9.0500000000000007</v>
       </c>
       <c r="C488">
-        <v>8.82</v>
+        <v>8.59</v>
       </c>
       <c r="D488">
         <v>8.9</v>
@@ -7385,7 +7385,7 @@
         <v>9.15</v>
       </c>
       <c r="C489">
-        <v>8.8800000000000008</v>
+        <v>8.67</v>
       </c>
       <c r="D489">
         <v>9</v>
@@ -7399,7 +7399,7 @@
         <v>9.24</v>
       </c>
       <c r="C490">
-        <v>8.9499999999999993</v>
+        <v>8.74</v>
       </c>
       <c r="D490">
         <v>9.09</v>
@@ -7413,7 +7413,7 @@
         <v>9.32</v>
       </c>
       <c r="C491">
-        <v>9.01</v>
+        <v>8.81</v>
       </c>
       <c r="D491">
         <v>9.16</v>
@@ -7427,7 +7427,7 @@
         <v>9.39</v>
       </c>
       <c r="C492">
-        <v>9.07</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="D492">
         <v>9.24</v>
@@ -7441,7 +7441,7 @@
         <v>9.48</v>
       </c>
       <c r="C493">
-        <v>9.1300000000000008</v>
+        <v>8.93</v>
       </c>
       <c r="D493">
         <v>9.32</v>
@@ -7455,7 +7455,7 @@
         <v>9.57</v>
       </c>
       <c r="C494">
-        <v>9.19</v>
+        <v>8.99</v>
       </c>
       <c r="D494">
         <v>9.42</v>
@@ -7469,7 +7469,7 @@
         <v>9.67</v>
       </c>
       <c r="C495">
-        <v>9.25</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="D495">
         <v>9.51</v>
@@ -7483,7 +7483,7 @@
         <v>9.75</v>
       </c>
       <c r="C496">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="D496">
         <v>9.6</v>
@@ -7497,7 +7497,7 @@
         <v>9.81</v>
       </c>
       <c r="C497">
-        <v>9.35</v>
+        <v>9.15</v>
       </c>
       <c r="D497">
         <v>9.66</v>
@@ -7511,7 +7511,7 @@
         <v>9.85</v>
       </c>
       <c r="C498">
-        <v>9.4</v>
+        <v>9.19</v>
       </c>
       <c r="D498">
         <v>9.6999999999999993</v>
@@ -7525,7 +7525,7 @@
         <v>9.89</v>
       </c>
       <c r="C499">
-        <v>9.44</v>
+        <v>9.23</v>
       </c>
       <c r="D499">
         <v>9.74</v>
@@ -7539,7 +7539,7 @@
         <v>9.91</v>
       </c>
       <c r="C500">
-        <v>9.49</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="D500">
         <v>9.76</v>
@@ -7553,7 +7553,7 @@
         <v>9.94</v>
       </c>
       <c r="C501">
-        <v>9.5399999999999991</v>
+        <v>9.32</v>
       </c>
       <c r="D501">
         <v>9.7899999999999991</v>
@@ -7567,7 +7567,7 @@
         <v>9.98</v>
       </c>
       <c r="C502">
-        <v>9.57</v>
+        <v>9.35</v>
       </c>
       <c r="D502">
         <v>9.83</v>
@@ -7581,7 +7581,7 @@
         <v>10</v>
       </c>
       <c r="C503">
-        <v>9.61</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="D503">
         <v>9.85</v>
@@ -7595,7 +7595,7 @@
         <v>10.029999999999999</v>
       </c>
       <c r="C504">
-        <v>9.65</v>
+        <v>9.42</v>
       </c>
       <c r="D504">
         <v>9.8800000000000008</v>
@@ -7609,7 +7609,7 @@
         <v>10.039999999999999</v>
       </c>
       <c r="C505">
-        <v>9.68</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="D505">
         <v>9.89</v>
@@ -7623,7 +7623,7 @@
         <v>10.039999999999999</v>
       </c>
       <c r="C506">
-        <v>9.7100000000000009</v>
+        <v>9.52</v>
       </c>
       <c r="D506">
         <v>9.89</v>
@@ -7637,7 +7637,7 @@
         <v>10.029999999999999</v>
       </c>
       <c r="C507">
-        <v>9.74</v>
+        <v>9.57</v>
       </c>
       <c r="D507">
         <v>9.8800000000000008</v>
@@ -7651,7 +7651,7 @@
         <v>10</v>
       </c>
       <c r="C508">
-        <v>9.76</v>
+        <v>9.59</v>
       </c>
       <c r="D508">
         <v>9.85</v>
@@ -7665,7 +7665,7 @@
         <v>9.9600000000000009</v>
       </c>
       <c r="C509">
-        <v>9.7899999999999991</v>
+        <v>9.59</v>
       </c>
       <c r="D509">
         <v>9.81</v>
@@ -7679,7 +7679,7 @@
         <v>9.9</v>
       </c>
       <c r="C510">
-        <v>9.81</v>
+        <v>9.58</v>
       </c>
       <c r="D510">
         <v>9.75</v>
@@ -7693,7 +7693,7 @@
         <v>9.83</v>
       </c>
       <c r="C511">
-        <v>9.83</v>
+        <v>9.59</v>
       </c>
       <c r="D511">
         <v>9.68</v>
@@ -7707,7 +7707,7 @@
         <v>9.7799999999999994</v>
       </c>
       <c r="C512">
-        <v>9.85</v>
+        <v>9.61</v>
       </c>
       <c r="D512">
         <v>9.6300000000000008</v>
@@ -7721,7 +7721,7 @@
         <v>9.73</v>
       </c>
       <c r="C513">
-        <v>9.8699999999999992</v>
+        <v>9.65</v>
       </c>
       <c r="D513">
         <v>9.58</v>
@@ -7735,7 +7735,7 @@
         <v>9.7200000000000006</v>
       </c>
       <c r="C514">
-        <v>9.9</v>
+        <v>9.68</v>
       </c>
       <c r="D514">
         <v>9.56</v>
@@ -7749,7 +7749,7 @@
         <v>9.68</v>
       </c>
       <c r="C515">
-        <v>9.92</v>
+        <v>9.7100000000000009</v>
       </c>
       <c r="D515">
         <v>9.5299999999999994</v>
@@ -7763,7 +7763,7 @@
         <v>9.61</v>
       </c>
       <c r="C516">
-        <v>9.93</v>
+        <v>9.73</v>
       </c>
       <c r="D516">
         <v>9.4600000000000009</v>
@@ -7777,7 +7777,7 @@
         <v>9.5</v>
       </c>
       <c r="C517">
-        <v>9.94</v>
+        <v>9.75</v>
       </c>
       <c r="D517">
         <v>9.35</v>
@@ -7791,7 +7791,7 @@
         <v>9.36</v>
       </c>
       <c r="C518">
-        <v>9.9499999999999993</v>
+        <v>9.77</v>
       </c>
       <c r="D518">
         <v>9.2100000000000009</v>
@@ -7805,7 +7805,7 @@
         <v>9.2200000000000006</v>
       </c>
       <c r="C519">
-        <v>9.9499999999999993</v>
+        <v>9.77</v>
       </c>
       <c r="D519">
         <v>9.07</v>
@@ -7819,7 +7819,7 @@
         <v>9.1</v>
       </c>
       <c r="C520">
-        <v>9.9600000000000009</v>
+        <v>9.76</v>
       </c>
       <c r="D520">
         <v>8.9499999999999993</v>
@@ -7833,7 +7833,7 @@
         <v>8.99</v>
       </c>
       <c r="C521">
-        <v>9.9499999999999993</v>
+        <v>9.74</v>
       </c>
       <c r="D521">
         <v>8.84</v>
@@ -7847,7 +7847,7 @@
         <v>8.91</v>
       </c>
       <c r="C522">
-        <v>9.94</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="D522">
         <v>8.76</v>
@@ -7861,7 +7861,7 @@
         <v>8.85</v>
       </c>
       <c r="C523">
-        <v>9.93</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="D523">
         <v>8.6999999999999993</v>
@@ -7875,7 +7875,7 @@
         <v>8.7899999999999991</v>
       </c>
       <c r="C524">
-        <v>9.91</v>
+        <v>9.69</v>
       </c>
       <c r="D524">
         <v>8.64</v>
@@ -7889,7 +7889,7 @@
         <v>8.69</v>
       </c>
       <c r="C525">
-        <v>9.8800000000000008</v>
+        <v>9.68</v>
       </c>
       <c r="D525">
         <v>8.5399999999999991</v>
@@ -7903,7 +7903,7 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="C526">
-        <v>9.85</v>
+        <v>9.66</v>
       </c>
       <c r="D526">
         <v>8.39</v>
@@ -7917,7 +7917,7 @@
         <v>8.36</v>
       </c>
       <c r="C527">
-        <v>9.81</v>
+        <v>9.61</v>
       </c>
       <c r="D527">
         <v>8.2100000000000009</v>
@@ -7931,7 +7931,7 @@
         <v>8.19</v>
       </c>
       <c r="C528">
-        <v>9.77</v>
+        <v>9.56</v>
       </c>
       <c r="D528">
         <v>8.0399999999999991</v>
@@ -7945,7 +7945,7 @@
         <v>8.06</v>
       </c>
       <c r="C529">
-        <v>9.74</v>
+        <v>9.51</v>
       </c>
       <c r="D529">
         <v>7.91</v>
@@ -7959,7 +7959,7 @@
         <v>7.97</v>
       </c>
       <c r="C530">
-        <v>9.7100000000000009</v>
+        <v>9.48</v>
       </c>
       <c r="D530">
         <v>7.81</v>
@@ -7973,7 +7973,7 @@
         <v>7.87</v>
       </c>
       <c r="C531">
-        <v>9.69</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="D531">
         <v>7.72</v>
@@ -7987,7 +7987,7 @@
         <v>7.76</v>
       </c>
       <c r="C532">
-        <v>9.67</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="D532">
         <v>7.6</v>
@@ -8001,7 +8001,7 @@
         <v>7.61</v>
       </c>
       <c r="C533">
-        <v>9.64</v>
+        <v>9.44</v>
       </c>
       <c r="D533">
         <v>7.46</v>
@@ -8015,7 +8015,7 @@
         <v>7.44</v>
       </c>
       <c r="C534">
-        <v>9.6</v>
+        <v>9.39</v>
       </c>
       <c r="D534">
         <v>7.29</v>
@@ -8029,7 +8029,7 @@
         <v>7.28</v>
       </c>
       <c r="C535">
-        <v>9.5399999999999991</v>
+        <v>9.33</v>
       </c>
       <c r="D535">
         <v>7.13</v>
@@ -8043,7 +8043,7 @@
         <v>7.15</v>
       </c>
       <c r="C536">
-        <v>9.4700000000000006</v>
+        <v>9.26</v>
       </c>
       <c r="D536">
         <v>7</v>
@@ -8057,7 +8057,7 @@
         <v>7.04</v>
       </c>
       <c r="C537">
-        <v>9.4</v>
+        <v>9.19</v>
       </c>
       <c r="D537">
         <v>6.89</v>
@@ -8071,7 +8071,7 @@
         <v>6.93</v>
       </c>
       <c r="C538">
-        <v>9.33</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="D538">
         <v>6.78</v>
@@ -8085,7 +8085,7 @@
         <v>6.81</v>
       </c>
       <c r="C539">
-        <v>9.26</v>
+        <v>9.06</v>
       </c>
       <c r="D539">
         <v>6.66</v>
@@ -8099,7 +8099,7 @@
         <v>6.68</v>
       </c>
       <c r="C540">
-        <v>9.2100000000000009</v>
+        <v>9.01</v>
       </c>
       <c r="D540">
         <v>6.53</v>
@@ -8113,7 +8113,7 @@
         <v>6.53</v>
       </c>
       <c r="C541">
-        <v>9.16</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="D541">
         <v>6.38</v>
@@ -8127,7 +8127,7 @@
         <v>6.4</v>
       </c>
       <c r="C542">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="D542">
         <v>6.25</v>
@@ -8141,7 +8141,7 @@
         <v>6.29</v>
       </c>
       <c r="C543">
-        <v>9.0299999999999994</v>
+        <v>8.85</v>
       </c>
       <c r="D543">
         <v>6.14</v>
@@ -8155,7 +8155,7 @@
         <v>6.19</v>
       </c>
       <c r="C544">
-        <v>8.9600000000000009</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="D544">
         <v>6.04</v>
@@ -8169,7 +8169,7 @@
         <v>6.08</v>
       </c>
       <c r="C545">
-        <v>8.8800000000000008</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="D545">
         <v>5.93</v>
@@ -8183,7 +8183,7 @@
         <v>5.95</v>
       </c>
       <c r="C546">
-        <v>8.8000000000000007</v>
+        <v>8.59</v>
       </c>
       <c r="D546">
         <v>5.8</v>
@@ -8197,7 +8197,7 @@
         <v>5.81</v>
       </c>
       <c r="C547">
-        <v>8.73</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="D547">
         <v>5.65</v>
@@ -8211,7 +8211,7 @@
         <v>5.67</v>
       </c>
       <c r="C548">
-        <v>8.66</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="D548">
         <v>5.52</v>
@@ -8225,7 +8225,7 @@
         <v>5.55</v>
       </c>
       <c r="C549">
-        <v>8.58</v>
+        <v>8.15</v>
       </c>
       <c r="D549">
         <v>5.4</v>
@@ -8239,7 +8239,7 @@
         <v>5.46</v>
       </c>
       <c r="C550">
-        <v>8.4700000000000006</v>
+        <v>7.98</v>
       </c>
       <c r="D550">
         <v>5.31</v>
@@ -8253,7 +8253,7 @@
         <v>5.38</v>
       </c>
       <c r="C551">
-        <v>8.33</v>
+        <v>7.8</v>
       </c>
       <c r="D551">
         <v>5.23</v>
@@ -8267,7 +8267,7 @@
         <v>5.3</v>
       </c>
       <c r="C552">
-        <v>8.16</v>
+        <v>7.57</v>
       </c>
       <c r="D552">
         <v>5.15</v>
@@ -8281,7 +8281,7 @@
         <v>5.2</v>
       </c>
       <c r="C553">
-        <v>7.96</v>
+        <v>7.31</v>
       </c>
       <c r="D553">
         <v>5.05</v>
@@ -8295,7 +8295,7 @@
         <v>5.08</v>
       </c>
       <c r="C554">
-        <v>7.71</v>
+        <v>7.05</v>
       </c>
       <c r="D554">
         <v>4.93</v>
@@ -8309,7 +8309,7 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="C555">
-        <v>7.44</v>
+        <v>6.78</v>
       </c>
       <c r="D555">
         <v>4.79</v>
@@ -8323,7 +8323,7 @@
         <v>4.8</v>
       </c>
       <c r="C556">
-        <v>7.17</v>
+        <v>6.53</v>
       </c>
       <c r="D556">
         <v>4.6500000000000004</v>
@@ -8337,7 +8337,7 @@
         <v>4.7</v>
       </c>
       <c r="C557">
-        <v>6.89</v>
+        <v>6.3</v>
       </c>
       <c r="D557">
         <v>4.55</v>
@@ -8351,7 +8351,7 @@
         <v>4.63</v>
       </c>
       <c r="C558">
-        <v>6.65</v>
+        <v>6.09</v>
       </c>
       <c r="D558">
         <v>4.4800000000000004</v>
@@ -8365,7 +8365,7 @@
         <v>4.59</v>
       </c>
       <c r="C559">
-        <v>6.44</v>
+        <v>5.91</v>
       </c>
       <c r="D559">
         <v>4.4400000000000004</v>
@@ -8379,7 +8379,7 @@
         <v>4.55</v>
       </c>
       <c r="C560">
-        <v>6.27</v>
+        <v>5.8</v>
       </c>
       <c r="D560">
         <v>4.4000000000000004</v>
@@ -8393,7 +8393,7 @@
         <v>4.49</v>
       </c>
       <c r="C561">
-        <v>6.17</v>
+        <v>5.79</v>
       </c>
       <c r="D561">
         <v>4.34</v>
@@ -8407,7 +8407,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C562">
-        <v>6.14</v>
+        <v>5.9</v>
       </c>
       <c r="D562">
         <v>4.25</v>
@@ -8421,7 +8421,7 @@
         <v>4.28</v>
       </c>
       <c r="C563">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="D563">
         <v>4.12</v>
@@ -8435,7 +8435,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="C564">
-        <v>6.16</v>
+        <v>6.36</v>
       </c>
       <c r="D564">
         <v>3.99</v>
@@ -8449,7 +8449,7 @@
         <v>4.04</v>
       </c>
       <c r="C565">
-        <v>6.22</v>
+        <v>6.58</v>
       </c>
       <c r="D565">
         <v>3.89</v>
@@ -8463,7 +8463,7 @@
         <v>3.99</v>
       </c>
       <c r="C566">
-        <v>6.27</v>
+        <v>6.72</v>
       </c>
       <c r="D566">
         <v>3.84</v>
@@ -8477,7 +8477,7 @@
         <v>3.97</v>
       </c>
       <c r="C567">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="D567">
         <v>3.82</v>
@@ -8491,7 +8491,7 @@
         <v>3.96</v>
       </c>
       <c r="C568">
-        <v>6.27</v>
+        <v>6.7</v>
       </c>
       <c r="D568">
         <v>3.81</v>
@@ -8505,7 +8505,7 @@
         <v>3.9</v>
       </c>
       <c r="C569">
-        <v>6.22</v>
+        <v>6.58</v>
       </c>
       <c r="D569">
         <v>3.74</v>
@@ -8519,7 +8519,7 @@
         <v>3.8</v>
       </c>
       <c r="C570">
-        <v>6.15</v>
+        <v>6.43</v>
       </c>
       <c r="D570">
         <v>3.64</v>
@@ -8533,7 +8533,7 @@
         <v>3.68</v>
       </c>
       <c r="C571">
-        <v>6.06</v>
+        <v>6.26</v>
       </c>
       <c r="D571">
         <v>3.53</v>
@@ -8547,7 +8547,7 @@
         <v>3.57</v>
       </c>
       <c r="C572">
-        <v>5.98</v>
+        <v>6.1</v>
       </c>
       <c r="D572">
         <v>3.41</v>
@@ -8561,7 +8561,7 @@
         <v>3.51</v>
       </c>
       <c r="C573">
-        <v>5.89</v>
+        <v>5.94</v>
       </c>
       <c r="D573">
         <v>3.36</v>
@@ -8589,7 +8589,7 @@
         <v>3.56</v>
       </c>
       <c r="C575">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="D575">
         <v>3.41</v>
@@ -8603,7 +8603,7 @@
         <v>3.57</v>
       </c>
       <c r="C576">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="D576">
         <v>3.42</v>
@@ -8617,7 +8617,7 @@
         <v>3.5</v>
       </c>
       <c r="C577">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="D577">
         <v>3.35</v>
@@ -8631,7 +8631,7 @@
         <v>3.34</v>
       </c>
       <c r="C578">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="D578">
         <v>3.19</v>
@@ -8645,7 +8645,7 @@
         <v>3.3</v>
       </c>
       <c r="C579">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="D579">
         <v>3.15</v>
@@ -8659,7 +8659,7 @@
         <v>3.46</v>
       </c>
       <c r="C580">
-        <v>5.84</v>
+        <v>5.72</v>
       </c>
       <c r="D580">
         <v>3.31</v>
@@ -8673,7 +8673,7 @@
         <v>3.57</v>
       </c>
       <c r="C581">
-        <v>5.89</v>
+        <v>5.71</v>
       </c>
       <c r="D581">
         <v>3.42</v>
@@ -8687,7 +8687,7 @@
         <v>3.47</v>
       </c>
       <c r="C582">
-        <v>5.93</v>
+        <v>5.69</v>
       </c>
       <c r="D582">
         <v>3.32</v>
@@ -8701,7 +8701,7 @@
         <v>3.08</v>
       </c>
       <c r="C583">
-        <v>5.92</v>
+        <v>5.66</v>
       </c>
       <c r="D583">
         <v>2.93</v>
@@ -8715,7 +8715,7 @@
         <v>2.31</v>
       </c>
       <c r="C584">
-        <v>5.85</v>
+        <v>5.61</v>
       </c>
       <c r="D584">
         <v>2.16</v>
@@ -8729,7 +8729,7 @@
         <v>1.37</v>
       </c>
       <c r="C585">
-        <v>5.77</v>
+        <v>5.54</v>
       </c>
       <c r="D585">
         <v>1.21</v>
@@ -8743,7 +8743,7 @@
         <v>0.39</v>
       </c>
       <c r="C586">
-        <v>5.68</v>
+        <v>5.47</v>
       </c>
       <c r="D586">
         <v>0.23</v>
@@ -8757,7 +8757,7 @@
         <v>-0.6</v>
       </c>
       <c r="C587">
-        <v>5.58</v>
+        <v>5.39</v>
       </c>
       <c r="D587">
         <v>-0.75</v>
@@ -8771,7 +8771,7 @@
         <v>-1.48</v>
       </c>
       <c r="C588">
-        <v>5.48</v>
+        <v>5.28</v>
       </c>
       <c r="D588">
         <v>-1.63</v>
@@ -8785,7 +8785,7 @@
         <v>-2.13</v>
       </c>
       <c r="C589">
-        <v>5.36</v>
+        <v>5.17</v>
       </c>
       <c r="D589">
         <v>-2.2799999999999998</v>
@@ -8799,7 +8799,7 @@
         <v>-2.5499999999999998</v>
       </c>
       <c r="C590">
-        <v>5.22</v>
+        <v>5.04</v>
       </c>
       <c r="D590">
         <v>-2.7</v>
@@ -8813,7 +8813,7 @@
         <v>-2.77</v>
       </c>
       <c r="C591">
-        <v>5.08</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D591">
         <v>-2.92</v>
@@ -8827,7 +8827,7 @@
         <v>-2.83</v>
       </c>
       <c r="C592">
-        <v>4.96</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D592">
         <v>-2.98</v>
@@ -8841,7 +8841,7 @@
         <v>-2.79</v>
       </c>
       <c r="C593">
-        <v>4.84</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="D593">
         <v>-2.95</v>
@@ -8855,7 +8855,7 @@
         <v>-2.68</v>
       </c>
       <c r="C594">
-        <v>4.74</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="D594">
         <v>-2.83</v>
@@ -8869,7 +8869,7 @@
         <v>-2.5099999999999998</v>
       </c>
       <c r="C595">
-        <v>4.6399999999999997</v>
+        <v>4.41</v>
       </c>
       <c r="D595">
         <v>-2.67</v>
@@ -8883,7 +8883,7 @@
         <v>-2.31</v>
       </c>
       <c r="C596">
-        <v>4.55</v>
+        <v>4.32</v>
       </c>
       <c r="D596">
         <v>-2.4700000000000002</v>
@@ -8897,7 +8897,7 @@
         <v>-2.08</v>
       </c>
       <c r="C597">
-        <v>4.45</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="D597">
         <v>-2.2400000000000002</v>
@@ -8911,7 +8911,7 @@
         <v>-1.84</v>
       </c>
       <c r="C598">
-        <v>4.3499999999999996</v>
+        <v>4.13</v>
       </c>
       <c r="D598">
         <v>-1.99</v>
@@ -8925,7 +8925,7 @@
         <v>-1.59</v>
       </c>
       <c r="C599">
-        <v>4.24</v>
+        <v>4.03</v>
       </c>
       <c r="D599">
         <v>-1.75</v>
@@ -8939,7 +8939,7 @@
         <v>-1.35</v>
       </c>
       <c r="C600">
-        <v>4.12</v>
+        <v>3.92</v>
       </c>
       <c r="D600">
         <v>-1.5</v>
@@ -8953,7 +8953,7 @@
         <v>-1.1100000000000001</v>
       </c>
       <c r="C601">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D601">
         <v>-1.26</v>
@@ -8967,7 +8967,7 @@
         <v>-0.87</v>
       </c>
       <c r="C602">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="D602">
         <v>-1.03</v>
@@ -8981,7 +8981,7 @@
         <v>-0.64</v>
       </c>
       <c r="C603">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="D603">
         <v>-0.79</v>
@@ -8995,7 +8995,7 @@
         <v>-0.38</v>
       </c>
       <c r="C604">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="D604">
         <v>-0.54</v>
@@ -9009,7 +9009,7 @@
         <v>-0.13</v>
       </c>
       <c r="C605">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="D605">
         <v>-0.28000000000000003</v>
@@ -9023,7 +9023,7 @@
         <v>0.11</v>
       </c>
       <c r="C606">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="D606">
         <v>-0.05</v>
@@ -9037,7 +9037,7 @@
         <v>0.31</v>
       </c>
       <c r="C607">
-        <v>3.23</v>
+        <v>3.03</v>
       </c>
       <c r="D607">
         <v>0.16</v>
@@ -9051,7 +9051,7 @@
         <v>0.48</v>
       </c>
       <c r="C608">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="D608">
         <v>0.33</v>
@@ -9065,7 +9065,7 @@
         <v>0.6</v>
       </c>
       <c r="C609">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="D609">
         <v>0.45</v>
@@ -9079,7 +9079,7 @@
         <v>0.68</v>
       </c>
       <c r="C610">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="D610">
         <v>0.53</v>
@@ -9093,7 +9093,7 @@
         <v>0.7</v>
       </c>
       <c r="C611">
-        <v>2.71</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D611">
         <v>0.55000000000000004</v>
@@ -9107,7 +9107,7 @@
         <v>0.68</v>
       </c>
       <c r="C612">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="D612">
         <v>0.53</v>
@@ -9121,7 +9121,7 @@
         <v>0.61</v>
       </c>
       <c r="C613">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="D613">
         <v>0.46</v>
@@ -9135,7 +9135,7 @@
         <v>0.5</v>
       </c>
       <c r="C614">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="D614">
         <v>0.35</v>
@@ -9149,7 +9149,7 @@
         <v>0.37</v>
       </c>
       <c r="C615">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="D615">
         <v>0.22</v>
@@ -9163,7 +9163,7 @@
         <v>0.23</v>
       </c>
       <c r="C616">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="D616">
         <v>0.08</v>
@@ -9177,7 +9177,7 @@
         <v>0.1</v>
       </c>
       <c r="C617">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="D617">
         <v>-0.05</v>
@@ -9191,7 +9191,7 @@
         <v>-0.02</v>
       </c>
       <c r="C618">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="D618">
         <v>-0.17</v>
@@ -9205,7 +9205,7 @@
         <v>-0.14000000000000001</v>
       </c>
       <c r="C619">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="D619">
         <v>-0.28999999999999998</v>
@@ -9219,7 +9219,7 @@
         <v>-0.25</v>
       </c>
       <c r="C620">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="D620">
         <v>-0.41</v>
@@ -9233,7 +9233,7 @@
         <v>-0.37</v>
       </c>
       <c r="C621">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="D621">
         <v>-0.52</v>
@@ -9247,7 +9247,7 @@
         <v>-0.49</v>
       </c>
       <c r="C622">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="D622">
         <v>-0.65</v>
@@ -9261,7 +9261,7 @@
         <v>-0.62</v>
       </c>
       <c r="C623">
-        <v>1.33</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D623">
         <v>-0.77</v>
@@ -9275,7 +9275,7 @@
         <v>-0.74</v>
       </c>
       <c r="C624">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="D624">
         <v>-0.89</v>
@@ -9289,7 +9289,7 @@
         <v>-0.86</v>
       </c>
       <c r="C625">
-        <v>1.0900000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="D625">
         <v>-1.01</v>
@@ -9303,7 +9303,7 @@
         <v>-0.97</v>
       </c>
       <c r="C626">
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
       <c r="D626">
         <v>-1.1200000000000001</v>
@@ -9317,7 +9317,7 @@
         <v>-1.07</v>
       </c>
       <c r="C627">
-        <v>0.77</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D627">
         <v>-1.22</v>
@@ -9331,7 +9331,7 @@
         <v>-1.2</v>
       </c>
       <c r="C628">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="D628">
         <v>-1.35</v>
@@ -9345,7 +9345,7 @@
         <v>-1.32</v>
       </c>
       <c r="C629">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="D629">
         <v>-1.47</v>
@@ -9359,7 +9359,7 @@
         <v>-1.45</v>
       </c>
       <c r="C630">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="D630">
         <v>-1.6</v>
@@ -9373,7 +9373,7 @@
         <v>-1.57</v>
       </c>
       <c r="C631">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="D631">
         <v>-1.72</v>
@@ -9387,7 +9387,7 @@
         <v>-1.69</v>
       </c>
       <c r="C632">
-        <v>0.03</v>
+        <v>-0.18</v>
       </c>
       <c r="D632">
         <v>-1.84</v>
@@ -9401,7 +9401,7 @@
         <v>-1.81</v>
       </c>
       <c r="C633">
-        <v>-0.16</v>
+        <v>-0.37</v>
       </c>
       <c r="D633">
         <v>-1.96</v>
@@ -9415,7 +9415,7 @@
         <v>-1.93</v>
       </c>
       <c r="C634">
-        <v>-0.36</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="D634">
         <v>-2.08</v>
@@ -9429,7 +9429,7 @@
         <v>-2.0499999999999998</v>
       </c>
       <c r="C635">
-        <v>-0.54</v>
+        <v>-0.75</v>
       </c>
       <c r="D635">
         <v>-2.2000000000000002</v>
@@ -9443,7 +9443,7 @@
         <v>-2.17</v>
       </c>
       <c r="C636">
-        <v>-0.73</v>
+        <v>-0.94</v>
       </c>
       <c r="D636">
         <v>-2.3199999999999998</v>
@@ -9457,7 +9457,7 @@
         <v>-2.2999999999999998</v>
       </c>
       <c r="C637">
-        <v>-0.92</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="D637">
         <v>-2.4500000000000002</v>
@@ -9471,7 +9471,7 @@
         <v>-2.42</v>
       </c>
       <c r="C638">
-        <v>-1.1200000000000001</v>
+        <v>-1.32</v>
       </c>
       <c r="D638">
         <v>-2.57</v>
@@ -9485,7 +9485,7 @@
         <v>-2.5499999999999998</v>
       </c>
       <c r="C639">
-        <v>-1.31</v>
+        <v>-1.52</v>
       </c>
       <c r="D639">
         <v>-2.7</v>
@@ -9499,7 +9499,7 @@
         <v>-2.68</v>
       </c>
       <c r="C640">
-        <v>-1.51</v>
+        <v>-1.72</v>
       </c>
       <c r="D640">
         <v>-2.83</v>
@@ -9513,7 +9513,7 @@
         <v>-2.8</v>
       </c>
       <c r="C641">
-        <v>-1.71</v>
+        <v>-1.92</v>
       </c>
       <c r="D641">
         <v>-2.96</v>
@@ -9527,7 +9527,7 @@
         <v>-2.93</v>
       </c>
       <c r="C642">
-        <v>-1.91</v>
+        <v>-2.12</v>
       </c>
       <c r="D642">
         <v>-3.08</v>
@@ -9541,7 +9541,7 @@
         <v>-3.06</v>
       </c>
       <c r="C643">
-        <v>-2.12</v>
+        <v>-2.33</v>
       </c>
       <c r="D643">
         <v>-3.21</v>
@@ -9555,7 +9555,7 @@
         <v>-3.19</v>
       </c>
       <c r="C644">
-        <v>-2.33</v>
+        <v>-2.54</v>
       </c>
       <c r="D644">
         <v>-3.34</v>
@@ -9569,7 +9569,7 @@
         <v>-3.33</v>
       </c>
       <c r="C645">
-        <v>-2.54</v>
+        <v>-2.75</v>
       </c>
       <c r="D645">
         <v>-3.48</v>
@@ -9583,7 +9583,7 @@
         <v>-3.46</v>
       </c>
       <c r="C646">
-        <v>-2.75</v>
+        <v>-2.96</v>
       </c>
       <c r="D646">
         <v>-3.61</v>
@@ -9597,7 +9597,7 @@
         <v>-3.59</v>
       </c>
       <c r="C647">
-        <v>-2.96</v>
+        <v>-3.17</v>
       </c>
       <c r="D647">
         <v>-3.74</v>
@@ -9611,7 +9611,7 @@
         <v>-3.72</v>
       </c>
       <c r="C648">
-        <v>-3.18</v>
+        <v>-3.39</v>
       </c>
       <c r="D648">
         <v>-3.87</v>
@@ -9625,7 +9625,7 @@
         <v>-3.86</v>
       </c>
       <c r="C649">
-        <v>-3.4</v>
+        <v>-3.61</v>
       </c>
       <c r="D649">
         <v>-4.01</v>
@@ -9639,7 +9639,7 @@
         <v>-3.99</v>
       </c>
       <c r="C650">
-        <v>-3.62</v>
+        <v>-3.83</v>
       </c>
       <c r="D650">
         <v>-4.1399999999999997</v>
@@ -9653,7 +9653,7 @@
         <v>-4.13</v>
       </c>
       <c r="C651">
-        <v>-3.85</v>
+        <v>-4.0599999999999996</v>
       </c>
       <c r="D651">
         <v>-4.28</v>
@@ -9667,7 +9667,7 @@
         <v>-4.2699999999999996</v>
       </c>
       <c r="C652">
-        <v>-4.07</v>
+        <v>-4.28</v>
       </c>
       <c r="D652">
         <v>-4.42</v>
@@ -9681,7 +9681,7 @@
         <v>-4.41</v>
       </c>
       <c r="C653">
-        <v>-4.3</v>
+        <v>-4.51</v>
       </c>
       <c r="D653">
         <v>-4.5599999999999996</v>
@@ -9695,7 +9695,7 @@
         <v>-4.54</v>
       </c>
       <c r="C654">
-        <v>-4.53</v>
+        <v>-4.74</v>
       </c>
       <c r="D654">
         <v>-4.6900000000000004</v>
@@ -9709,7 +9709,7 @@
         <v>-4.68</v>
       </c>
       <c r="C655">
-        <v>-4.7699999999999996</v>
+        <v>-4.9800000000000004</v>
       </c>
       <c r="D655">
         <v>-4.83</v>
@@ -9723,7 +9723,7 @@
         <v>-4.82</v>
       </c>
       <c r="C656">
-        <v>-5</v>
+        <v>-5.21</v>
       </c>
       <c r="D656">
         <v>-4.97</v>
@@ -9737,7 +9737,7 @@
         <v>-4.96</v>
       </c>
       <c r="C657">
-        <v>-5.24</v>
+        <v>-5.45</v>
       </c>
       <c r="D657">
         <v>-5.12</v>
@@ -9751,7 +9751,7 @@
         <v>-5.1100000000000003</v>
       </c>
       <c r="C658">
-        <v>-5.48</v>
+        <v>-5.69</v>
       </c>
       <c r="D658">
         <v>-5.26</v>
@@ -9765,7 +9765,7 @@
         <v>-5.25</v>
       </c>
       <c r="C659">
-        <v>-5.73</v>
+        <v>-5.93</v>
       </c>
       <c r="D659">
         <v>-5.4</v>
@@ -9779,7 +9779,7 @@
         <v>-5.39</v>
       </c>
       <c r="C660">
-        <v>-5.97</v>
+        <v>-6.18</v>
       </c>
       <c r="D660">
         <v>-5.54</v>
@@ -9793,7 +9793,7 @@
         <v>-5.54</v>
       </c>
       <c r="C661">
-        <v>-6.22</v>
+        <v>-6.43</v>
       </c>
       <c r="D661">
         <v>-5.69</v>
@@ -9807,7 +9807,7 @@
         <v>-5.68</v>
       </c>
       <c r="C662">
-        <v>-6.47</v>
+        <v>-6.68</v>
       </c>
       <c r="D662">
         <v>-5.83</v>
@@ -9821,7 +9821,7 @@
         <v>-5.83</v>
       </c>
       <c r="C663">
-        <v>-6.72</v>
+        <v>-6.93</v>
       </c>
       <c r="D663">
         <v>-5.98</v>
@@ -9835,7 +9835,7 @@
         <v>-5.98</v>
       </c>
       <c r="C664">
-        <v>-6.98</v>
+        <v>-7.19</v>
       </c>
       <c r="D664">
         <v>-6.13</v>
@@ -9849,7 +9849,7 @@
         <v>-6.12</v>
       </c>
       <c r="C665">
-        <v>-7.23</v>
+        <v>-7.44</v>
       </c>
       <c r="D665">
         <v>-6.27</v>
@@ -9863,7 +9863,7 @@
         <v>-6.27</v>
       </c>
       <c r="C666">
-        <v>-7.49</v>
+        <v>-7.7</v>
       </c>
       <c r="D666">
         <v>-6.42</v>
@@ -9877,7 +9877,7 @@
         <v>-6.42</v>
       </c>
       <c r="C667">
-        <v>-7.76</v>
+        <v>-7.97</v>
       </c>
       <c r="D667">
         <v>-6.57</v>
@@ -9891,7 +9891,7 @@
         <v>-6.57</v>
       </c>
       <c r="C668">
-        <v>-8.02</v>
+        <v>-8.23</v>
       </c>
       <c r="D668">
         <v>-6.72</v>
@@ -9905,7 +9905,7 @@
         <v>-6.72</v>
       </c>
       <c r="C669">
-        <v>-8.2899999999999991</v>
+        <v>-8.5</v>
       </c>
       <c r="D669">
         <v>-6.87</v>
@@ -9919,7 +9919,7 @@
         <v>-6.87</v>
       </c>
       <c r="C670">
-        <v>-8.56</v>
+        <v>-8.77</v>
       </c>
       <c r="D670">
         <v>-7.03</v>
@@ -9933,7 +9933,7 @@
         <v>-7.03</v>
       </c>
       <c r="C671">
-        <v>-8.83</v>
+        <v>-9.0399999999999991</v>
       </c>
       <c r="D671">
         <v>-7.18</v>
@@ -9947,7 +9947,7 @@
         <v>-7.18</v>
       </c>
       <c r="C672">
-        <v>-9.1</v>
+        <v>-9.31</v>
       </c>
       <c r="D672">
         <v>-7.33</v>
@@ -9961,7 +9961,7 @@
         <v>-7.34</v>
       </c>
       <c r="C673">
-        <v>-9.3800000000000008</v>
+        <v>-9.59</v>
       </c>
       <c r="D673">
         <v>-7.49</v>
@@ -9975,7 +9975,7 @@
         <v>-7.49</v>
       </c>
       <c r="C674">
-        <v>-9.66</v>
+        <v>-9.8699999999999992</v>
       </c>
       <c r="D674">
         <v>-7.64</v>
@@ -9989,7 +9989,7 @@
         <v>-7.65</v>
       </c>
       <c r="C675">
-        <v>-9.94</v>
+        <v>-10.15</v>
       </c>
       <c r="D675">
         <v>-7.8</v>
@@ -10003,7 +10003,7 @@
         <v>-7.8</v>
       </c>
       <c r="C676">
-        <v>-10.220000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="D676">
         <v>-7.95</v>
@@ -10017,7 +10017,7 @@
         <v>-7.96</v>
       </c>
       <c r="C677">
-        <v>-10.51</v>
+        <v>-10.72</v>
       </c>
       <c r="D677">
         <v>-8.11</v>
@@ -10031,7 +10031,7 @@
         <v>-8.1199999999999992</v>
       </c>
       <c r="C678">
-        <v>-10.8</v>
+        <v>-11.01</v>
       </c>
       <c r="D678">
         <v>-8.27</v>
@@ -10045,7 +10045,7 @@
         <v>-8.2799999999999994</v>
       </c>
       <c r="C679">
-        <v>-11.09</v>
+        <v>-11.3</v>
       </c>
       <c r="D679">
         <v>-8.43</v>
@@ -10059,7 +10059,7 @@
         <v>-8.44</v>
       </c>
       <c r="C680">
-        <v>-11.38</v>
+        <v>-11.59</v>
       </c>
       <c r="D680">
         <v>-8.59</v>
@@ -10073,7 +10073,7 @@
         <v>-8.6</v>
       </c>
       <c r="C681">
-        <v>-11.68</v>
+        <v>-11.88</v>
       </c>
       <c r="D681">
         <v>-8.75</v>
@@ -10087,7 +10087,7 @@
         <v>-8.76</v>
       </c>
       <c r="C682">
-        <v>-11.97</v>
+        <v>-12.18</v>
       </c>
       <c r="D682">
         <v>-8.91</v>
@@ -10101,7 +10101,7 @@
         <v>-8.92</v>
       </c>
       <c r="C683">
-        <v>-12.27</v>
+        <v>-12.48</v>
       </c>
       <c r="D683">
         <v>-9.07</v>
@@ -10115,7 +10115,7 @@
         <v>-9.09</v>
       </c>
       <c r="C684">
-        <v>-12.58</v>
+        <v>-12.79</v>
       </c>
       <c r="D684">
         <v>-9.24</v>
@@ -10129,7 +10129,7 @@
         <v>-9.25</v>
       </c>
       <c r="C685">
-        <v>-12.88</v>
+        <v>-13.09</v>
       </c>
       <c r="D685">
         <v>-9.4</v>
@@ -10143,7 +10143,7 @@
         <v>-9.42</v>
       </c>
       <c r="C686">
-        <v>-13.19</v>
+        <v>-13.4</v>
       </c>
       <c r="D686">
         <v>-9.57</v>
@@ -10157,7 +10157,7 @@
         <v>-9.58</v>
       </c>
       <c r="C687">
-        <v>-13.5</v>
+        <v>-13.71</v>
       </c>
       <c r="D687">
         <v>-9.73</v>
@@ -10171,7 +10171,7 @@
         <v>-9.75</v>
       </c>
       <c r="C688">
-        <v>-13.81</v>
+        <v>-14.02</v>
       </c>
       <c r="D688">
         <v>-9.9</v>
@@ -10185,7 +10185,7 @@
         <v>-9.92</v>
       </c>
       <c r="C689">
-        <v>-14.12</v>
+        <v>-14.33</v>
       </c>
       <c r="D689">
         <v>-10.07</v>
@@ -10199,7 +10199,7 @@
         <v>-10.08</v>
       </c>
       <c r="C690">
-        <v>-14.44</v>
+        <v>-14.65</v>
       </c>
       <c r="D690">
         <v>-10.23</v>
@@ -10213,7 +10213,7 @@
         <v>-10.25</v>
       </c>
       <c r="C691">
-        <v>-14.76</v>
+        <v>-14.97</v>
       </c>
       <c r="D691">
         <v>-10.4</v>
@@ -10227,7 +10227,7 @@
         <v>-10.42</v>
       </c>
       <c r="C692">
-        <v>-15.08</v>
+        <v>-15.29</v>
       </c>
       <c r="D692">
         <v>-10.57</v>
@@ -10241,7 +10241,7 @@
         <v>-10.59</v>
       </c>
       <c r="C693">
-        <v>-15.4</v>
+        <v>-15.61</v>
       </c>
       <c r="D693">
         <v>-10.74</v>
@@ -10255,7 +10255,7 @@
         <v>-10.77</v>
       </c>
       <c r="C694">
-        <v>-15.73</v>
+        <v>-15.94</v>
       </c>
       <c r="D694">
         <v>-10.92</v>
@@ -10269,7 +10269,7 @@
         <v>-10.94</v>
       </c>
       <c r="C695">
-        <v>-16.059999999999999</v>
+        <v>-16.27</v>
       </c>
       <c r="D695">
         <v>-11.09</v>
@@ -10283,7 +10283,7 @@
         <v>-11.11</v>
       </c>
       <c r="C696">
-        <v>-16.39</v>
+        <v>-16.600000000000001</v>
       </c>
       <c r="D696">
         <v>-11.26</v>
